--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44964</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>44169</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45212</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44124</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45645</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45771</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45512</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45307</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44904</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45428</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44130</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44804</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44082</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>44064</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44489</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45072</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45341</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44678</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45559</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>45714</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45517</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45701</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45526</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45301</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45137</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45842</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44830</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44421</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44796</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44062</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44064</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44365</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45586</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45446</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45205</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45611</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45513</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45645</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45594</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45803.67</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>44692</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45773</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44217</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>44207</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44075</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44509</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44677</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44215</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>44274</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44577</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44350</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44217</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>44090</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44671</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44120</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44216</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44350</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44414</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44313</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44809</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>44815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44165</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44187</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44168</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44274</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44054</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44286</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44648</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44617</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44439</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44464</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44865</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44204</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44609</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>44223</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44110</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>44158</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44671</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44182</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>44274</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44125</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44057</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44313</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44151</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>44358</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44796</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44378</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44749</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44484</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44174</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44722</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44182</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44313</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44438</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44217</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44530</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44480</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44099</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44648</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44480</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44414</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44565</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44473</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44566</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44182</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44182</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44062</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44617</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44529</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44293</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44356</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44596</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44648</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44795</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44489</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44734</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44565</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>44248</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>44439</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44116</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44356</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44635</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44671</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44566</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44566</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45453</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45639</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45672</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45686.42519675926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45099</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45771</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45752</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44299</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45748</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>44524</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45761</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45770</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45110</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45105</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44642</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45068</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45769</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45454</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>44900</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44833</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45686.42361111111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45425</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45625</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45646</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45766</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45772</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45358</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45356</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44298</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45210</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44110</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>44565</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45649</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45085</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44438</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44529</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44211</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44529</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45070</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44657</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44248</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45264</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44330</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45350</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45301</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45077</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45254</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45379</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44484</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44812</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45079</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45659</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45593</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45596</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45723</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45723</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45370</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45747.56875</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44127</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45429</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44477</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45338</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44910</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45749</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45035</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45632</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45232</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44558</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45341</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45653.46922453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44077</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>44883</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44833</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45152</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45254</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44935</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45456</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44441</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>44378</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45761</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45769</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45406</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45561</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>44489</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45419</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44908</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45244</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45099</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45351</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45516</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45732</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44391</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45672</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>44374</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45387</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45708</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>44127</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45589</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45553</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45764</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45764</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>45110</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45397</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45397</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45642</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44908</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45155</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45429</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45429</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45574</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45448</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>44994</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44529</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44110</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44648</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45205</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45204</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>44110</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44151</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>44901</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>44529</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>44529</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45156</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45518</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44983</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>44881</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45152</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45750</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45786</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45149</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44735</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45132</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>45013</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45591</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44609</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45653</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45653</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45226</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45161</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45161</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45232</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45758</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45761</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44445</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44795</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45379</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45483</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45216</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45596</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44120</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44120</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44566</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45645</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45643</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45774</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45478</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45793</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>44642</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44490</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45054</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45590</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45590</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45793</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45448</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45411</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45646</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45764</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45682</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45764</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>44628</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>44657</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>44994</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45798</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>44673</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45797</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45562</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45589</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45589</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45583</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45840</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>45212</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45687</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45770</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45840</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45674</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45803</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45803</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45625</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45761</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45803</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45804</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45590</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45685</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45505</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45639</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45608</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45608</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45704</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44903</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45608</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45460</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45645</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45212</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45161</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45152</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45237</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>44994</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45659</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>45232</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>45232</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45114</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45546</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45764</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45464</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45847.64745370371</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>44755</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45161</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44796</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44164</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45456</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45429</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45301</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45085</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45153</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45813</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45246</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45414</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45762</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45149</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45314</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45256</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>44484</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45446</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45818</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45254</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45818</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45770</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44648</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45264</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45323</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>45824</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44823</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45356</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>45824</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>44474</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>44568</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45300</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45824</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45260</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45826</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>44648</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>44386</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>44067</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45870.38011574074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45764</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45827</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45827</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45827</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44573</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45345</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45483</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45285</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45874</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45323</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45840</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45831</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>44970</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>45874.5525</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>45833</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45875.79864583333</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>45582</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45834</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45589</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>44356</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48130,7 +48130,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>44143</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>44124</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>44292</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44747</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44706</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44423</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44979</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>44931</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>44216</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45586</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>45187</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>45600</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45591</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>44925</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44378</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45091</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>45561.58791666666</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45001</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>44585</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>44847</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>44392</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45316</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>44552</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45470</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45587</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45114</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44566</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45685</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50621,7 +50621,7 @@
         <v>45246</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45762</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44964</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>44169</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>45212</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>44124</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45645</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45771</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45512</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>45049</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3287,7 +3287,7 @@
         <v>45307</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44904</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>45428</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44130</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44804</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44082</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>44064</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4844,7 +4844,7 @@
         <v>44489</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45072</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5025,7 +5025,7 @@
         <v>45341</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5116,7 +5116,7 @@
         <v>44678</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5207,7 +5207,7 @@
         <v>45559</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5298,7 +5298,7 @@
         <v>45714</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45517</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45701</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45526</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45301</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45137</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45842</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6123,7 +6123,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44830</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44421</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44796</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44062</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44064</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44365</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45586</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7481,7 +7481,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45446</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45205</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7750,7 +7750,7 @@
         <v>45611</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>45513</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45645</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8194,7 +8194,7 @@
         <v>45594</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8284,7 +8284,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8374,7 +8374,7 @@
         <v>45803.67</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8464,7 +8464,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>44692</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8644,7 +8644,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8734,7 +8734,7 @@
         <v>45773</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8824,7 +8824,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8914,7 +8914,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9004,7 +9004,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9089,7 +9089,7 @@
         <v>45538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9179,7 +9179,7 @@
         <v>44217</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9236,7 +9236,7 @@
         <v>44207</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>44075</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9350,7 +9350,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9407,7 +9407,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9464,7 +9464,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9521,7 +9521,7 @@
         <v>44509</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9578,7 +9578,7 @@
         <v>44677</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9635,7 +9635,7 @@
         <v>44215</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9692,7 +9692,7 @@
         <v>44274</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9749,7 +9749,7 @@
         <v>44577</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9806,7 +9806,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9863,7 +9863,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
         <v>44350</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>44217</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10034,7 +10034,7 @@
         <v>44090</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10091,7 +10091,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10153,7 +10153,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10210,7 +10210,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10272,7 +10272,7 @@
         <v>44671</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10329,7 +10329,7 @@
         <v>44120</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10386,7 +10386,7 @@
         <v>44852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10448,7 +10448,7 @@
         <v>44216</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10505,7 +10505,7 @@
         <v>44350</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10624,7 +10624,7 @@
         <v>44414</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10681,7 +10681,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10738,7 +10738,7 @@
         <v>44313</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10795,7 +10795,7 @@
         <v>44809</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10857,7 +10857,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10914,7 +10914,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10971,7 +10971,7 @@
         <v>44815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11033,7 +11033,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11095,7 +11095,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11157,7 +11157,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11214,7 +11214,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11271,7 +11271,7 @@
         <v>44165</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11328,7 +11328,7 @@
         <v>44187</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11385,7 +11385,7 @@
         <v>44168</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11442,7 +11442,7 @@
         <v>44274</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11499,7 +11499,7 @@
         <v>44054</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11561,7 +11561,7 @@
         <v>44286</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11618,7 +11618,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11675,7 +11675,7 @@
         <v>44648</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11737,7 +11737,7 @@
         <v>44617</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11794,7 +11794,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11856,7 +11856,7 @@
         <v>44439</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11913,7 +11913,7 @@
         <v>44464</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11970,7 +11970,7 @@
         <v>44865</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12032,7 +12032,7 @@
         <v>44204</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12089,7 +12089,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12146,7 +12146,7 @@
         <v>44609</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12203,7 +12203,7 @@
         <v>44223</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12260,7 +12260,7 @@
         <v>44110</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12322,7 +12322,7 @@
         <v>44158</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12379,7 +12379,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12436,7 +12436,7 @@
         <v>44671</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12493,7 +12493,7 @@
         <v>44182</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12550,7 +12550,7 @@
         <v>44274</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12607,7 +12607,7 @@
         <v>44125</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12783,7 +12783,7 @@
         <v>44057</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12840,7 +12840,7 @@
         <v>44313</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12897,7 +12897,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12954,7 +12954,7 @@
         <v>44151</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13016,7 +13016,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13078,7 +13078,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13140,7 +13140,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13197,7 +13197,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13254,7 +13254,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13316,7 +13316,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13373,7 +13373,7 @@
         <v>44721</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13430,7 +13430,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13487,7 +13487,7 @@
         <v>44358</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13544,7 +13544,7 @@
         <v>44796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13601,7 +13601,7 @@
         <v>44796</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13658,7 +13658,7 @@
         <v>44378</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13715,7 +13715,7 @@
         <v>44749</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13772,7 +13772,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13829,7 +13829,7 @@
         <v>44484</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13891,7 +13891,7 @@
         <v>44174</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13953,7 +13953,7 @@
         <v>44722</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14010,7 +14010,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14072,7 +14072,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14129,7 +14129,7 @@
         <v>44182</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14186,7 +14186,7 @@
         <v>44313</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14243,7 +14243,7 @@
         <v>44438</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14300,7 +14300,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14357,7 +14357,7 @@
         <v>44217</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14414,7 +14414,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14476,7 +14476,7 @@
         <v>44530</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>44480</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14590,7 +14590,7 @@
         <v>44099</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14647,7 +14647,7 @@
         <v>44648</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14709,7 +14709,7 @@
         <v>44480</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14766,7 +14766,7 @@
         <v>44414</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14823,7 +14823,7 @@
         <v>44565</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14880,7 +14880,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14942,7 +14942,7 @@
         <v>44473</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15004,7 +15004,7 @@
         <v>44566</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15061,7 +15061,7 @@
         <v>44182</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15118,7 +15118,7 @@
         <v>44182</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15175,7 +15175,7 @@
         <v>44062</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15232,7 +15232,7 @@
         <v>44617</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15289,7 +15289,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15351,7 +15351,7 @@
         <v>44529</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15408,7 +15408,7 @@
         <v>44293</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15470,7 +15470,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15527,7 +15527,7 @@
         <v>44356</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15584,7 +15584,7 @@
         <v>44596</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15646,7 +15646,7 @@
         <v>44648</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15708,7 +15708,7 @@
         <v>44795</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15770,7 +15770,7 @@
         <v>44489</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15827,7 +15827,7 @@
         <v>44734</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15884,7 +15884,7 @@
         <v>44565</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15941,7 +15941,7 @@
         <v>44248</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15998,7 +15998,7 @@
         <v>44439</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16055,7 +16055,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16112,7 +16112,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16174,7 +16174,7 @@
         <v>44116</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16231,7 +16231,7 @@
         <v>44356</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16288,7 +16288,7 @@
         <v>44635</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16350,7 +16350,7 @@
         <v>44671</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16407,7 +16407,7 @@
         <v>44566</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16464,7 +16464,7 @@
         <v>44566</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16521,7 +16521,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16583,7 +16583,7 @@
         <v>45453</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16640,7 +16640,7 @@
         <v>45639</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16697,7 +16697,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16754,7 +16754,7 @@
         <v>44445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16811,7 +16811,7 @@
         <v>45672</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16868,7 +16868,7 @@
         <v>45686.42519675926</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16925,7 +16925,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16982,7 +16982,7 @@
         <v>45099</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17039,7 +17039,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17153,7 +17153,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17210,7 +17210,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17267,7 +17267,7 @@
         <v>45771</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17324,7 +17324,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17381,7 +17381,7 @@
         <v>45752</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17438,7 +17438,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17500,7 +17500,7 @@
         <v>44299</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>45748</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17614,7 +17614,7 @@
         <v>44524</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17671,7 +17671,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17733,7 +17733,7 @@
         <v>45761</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17790,7 +17790,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17847,7 +17847,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17909,7 +17909,7 @@
         <v>45770</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17966,7 +17966,7 @@
         <v>45110</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18028,7 +18028,7 @@
         <v>45105</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18090,7 +18090,7 @@
         <v>44642</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18147,7 +18147,7 @@
         <v>45068</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18204,7 +18204,7 @@
         <v>45769</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18261,7 +18261,7 @@
         <v>45454</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18318,7 +18318,7 @@
         <v>44900</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18380,7 +18380,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18437,7 +18437,7 @@
         <v>44833</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18494,7 +18494,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18556,7 +18556,7 @@
         <v>45686.42361111111</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18670,7 +18670,7 @@
         <v>45425</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18727,7 +18727,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18784,7 +18784,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18846,7 +18846,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18903,7 +18903,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18965,7 +18965,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19022,7 +19022,7 @@
         <v>45625</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19079,7 +19079,7 @@
         <v>45646</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19136,7 +19136,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19193,7 +19193,7 @@
         <v>45766</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19255,7 +19255,7 @@
         <v>45772</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19312,7 +19312,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19369,7 +19369,7 @@
         <v>45358</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19426,7 +19426,7 @@
         <v>45356</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>44298</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45210</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19602,7 +19602,7 @@
         <v>44110</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19659,7 +19659,7 @@
         <v>44887</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19721,7 +19721,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19783,7 +19783,7 @@
         <v>44565</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19902,7 +19902,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19959,7 +19959,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20016,7 +20016,7 @@
         <v>45649</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20135,7 +20135,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20420,7 +20420,7 @@
         <v>45085</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20477,7 +20477,7 @@
         <v>44438</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20534,7 +20534,7 @@
         <v>44529</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20591,7 +20591,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44211</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>44529</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45070</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20943,7 +20943,7 @@
         <v>44657</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21000,7 +21000,7 @@
         <v>44248</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21057,7 +21057,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45264</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>44330</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45350</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21409,7 +21409,7 @@
         <v>45301</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21471,7 +21471,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21528,7 +21528,7 @@
         <v>45077</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21585,7 +21585,7 @@
         <v>45254</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21642,7 +21642,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21699,7 +21699,7 @@
         <v>45379</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21756,7 +21756,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21813,7 +21813,7 @@
         <v>44484</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21875,7 +21875,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21932,7 +21932,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21994,7 +21994,7 @@
         <v>44812</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22051,7 +22051,7 @@
         <v>45079</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22108,7 +22108,7 @@
         <v>45659</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22165,7 +22165,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22222,7 +22222,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22279,7 +22279,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22336,7 +22336,7 @@
         <v>45593</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22398,7 +22398,7 @@
         <v>45596</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22455,7 +22455,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22512,7 +22512,7 @@
         <v>45723</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22569,7 +22569,7 @@
         <v>45723</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22626,7 +22626,7 @@
         <v>45370</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22683,7 +22683,7 @@
         <v>45747.56875</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22740,7 +22740,7 @@
         <v>44127</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22797,7 +22797,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22854,7 +22854,7 @@
         <v>45429</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22911,7 +22911,7 @@
         <v>44477</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45338</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23025,7 +23025,7 @@
         <v>44910</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23087,7 +23087,7 @@
         <v>45749</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23144,7 +23144,7 @@
         <v>45035</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23201,7 +23201,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23258,7 +23258,7 @@
         <v>45632</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23315,7 +23315,7 @@
         <v>45232</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23377,7 +23377,7 @@
         <v>44558</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>45341</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23496,7 +23496,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23558,7 +23558,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23615,7 +23615,7 @@
         <v>44333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23672,7 +23672,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23729,7 +23729,7 @@
         <v>45653.46922453704</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23786,7 +23786,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23843,7 +23843,7 @@
         <v>44077</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23905,7 +23905,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23962,7 +23962,7 @@
         <v>44883</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24024,7 +24024,7 @@
         <v>44833</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24081,7 +24081,7 @@
         <v>45152</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24138,7 +24138,7 @@
         <v>45254</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24195,7 +24195,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>44935</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24309,7 +24309,7 @@
         <v>45456</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24366,7 +24366,7 @@
         <v>44441</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>44378</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24480,7 +24480,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24537,7 +24537,7 @@
         <v>45761</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24599,7 +24599,7 @@
         <v>45769</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24656,7 +24656,7 @@
         <v>45406</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24713,7 +24713,7 @@
         <v>45561</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24770,7 +24770,7 @@
         <v>44489</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24827,7 +24827,7 @@
         <v>45419</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24884,7 +24884,7 @@
         <v>44908</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24941,7 +24941,7 @@
         <v>45244</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25003,7 +25003,7 @@
         <v>45099</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25060,7 +25060,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25117,7 +25117,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25174,7 +25174,7 @@
         <v>45351</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25231,7 +25231,7 @@
         <v>45516</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25293,7 +25293,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25355,7 +25355,7 @@
         <v>45732</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25412,7 +25412,7 @@
         <v>44391</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25469,7 +25469,7 @@
         <v>45672</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25526,7 +25526,7 @@
         <v>44374</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25640,7 +25640,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25697,7 +25697,7 @@
         <v>45387</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25754,7 +25754,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25811,7 +25811,7 @@
         <v>45708</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25868,7 +25868,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25930,7 +25930,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25987,7 +25987,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26044,7 +26044,7 @@
         <v>44127</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26106,7 +26106,7 @@
         <v>45589</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26230,7 +26230,7 @@
         <v>45553</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45764</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26349,7 +26349,7 @@
         <v>45764</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26406,7 +26406,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>45110</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45397</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45397</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>45642</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26872,7 +26872,7 @@
         <v>45778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26991,7 +26991,7 @@
         <v>44908</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27048,7 +27048,7 @@
         <v>45155</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27110,7 +27110,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27167,7 +27167,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27224,7 +27224,7 @@
         <v>45429</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27281,7 +27281,7 @@
         <v>45429</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27338,7 +27338,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27395,7 +27395,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27457,7 +27457,7 @@
         <v>45574</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27519,7 +27519,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27576,7 +27576,7 @@
         <v>45448</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27638,7 +27638,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27700,7 +27700,7 @@
         <v>44994</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>44529</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27814,7 +27814,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27876,7 +27876,7 @@
         <v>44110</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27933,7 +27933,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27990,7 +27990,7 @@
         <v>44648</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28052,7 +28052,7 @@
         <v>45205</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28114,7 +28114,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28171,7 +28171,7 @@
         <v>45204</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28228,7 +28228,7 @@
         <v>44110</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28290,7 +28290,7 @@
         <v>44151</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>44901</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>44529</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>44529</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45156</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45518</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>44983</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>44881</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28989,7 +28989,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29051,7 +29051,7 @@
         <v>45152</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29108,7 +29108,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29165,7 +29165,7 @@
         <v>45750</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29227,7 +29227,7 @@
         <v>45786</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29289,7 +29289,7 @@
         <v>45149</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29346,7 +29346,7 @@
         <v>44735</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29408,7 +29408,7 @@
         <v>45132</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29465,7 +29465,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29522,7 +29522,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29579,7 +29579,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29636,7 +29636,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29693,7 +29693,7 @@
         <v>45013</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29750,7 +29750,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29807,7 +29807,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29864,7 +29864,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29926,7 +29926,7 @@
         <v>45591</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -29988,7 +29988,7 @@
         <v>44609</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30045,7 +30045,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>45653</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45653</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>45226</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30283,7 +30283,7 @@
         <v>45161</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45161</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30407,7 +30407,7 @@
         <v>45232</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30469,7 +30469,7 @@
         <v>45758</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30526,7 +30526,7 @@
         <v>45761</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30588,7 +30588,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30650,7 +30650,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30707,7 +30707,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30769,7 +30769,7 @@
         <v>44445</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30826,7 +30826,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30888,7 +30888,7 @@
         <v>44795</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30945,7 +30945,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31007,7 +31007,7 @@
         <v>45379</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31064,7 +31064,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31126,7 +31126,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31188,7 +31188,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31250,7 +31250,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31307,7 +31307,7 @@
         <v>45483</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31364,7 +31364,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31426,7 +31426,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31488,7 +31488,7 @@
         <v>45216</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31612,7 +31612,7 @@
         <v>45596</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31669,7 +31669,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31726,7 +31726,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31783,7 +31783,7 @@
         <v>44120</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31840,7 +31840,7 @@
         <v>44120</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31897,7 +31897,7 @@
         <v>44566</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31954,7 +31954,7 @@
         <v>45645</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32016,7 +32016,7 @@
         <v>44573</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>45643</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32197,7 +32197,7 @@
         <v>45774</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32259,7 +32259,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32316,7 +32316,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32378,7 +32378,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32435,7 +32435,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32492,7 +32492,7 @@
         <v>45478</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32549,7 +32549,7 @@
         <v>45793</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32611,7 +32611,7 @@
         <v>44642</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32673,7 +32673,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32730,7 +32730,7 @@
         <v>44490</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32792,7 +32792,7 @@
         <v>45054</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>45590</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32906,7 +32906,7 @@
         <v>45590</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32963,7 +32963,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45793</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33087,7 +33087,7 @@
         <v>45448</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33149,7 +33149,7 @@
         <v>44963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33206,7 +33206,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>45411</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33382,7 +33382,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33444,7 +33444,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33501,7 +33501,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33558,7 +33558,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33620,7 +33620,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33677,7 +33677,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33734,7 +33734,7 @@
         <v>45646</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33791,7 +33791,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33848,7 +33848,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33905,7 +33905,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33962,7 +33962,7 @@
         <v>45764</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34019,7 +34019,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34076,7 +34076,7 @@
         <v>45682</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34138,7 +34138,7 @@
         <v>45764</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34195,7 +34195,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34252,7 +34252,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34309,7 +34309,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34366,7 +34366,7 @@
         <v>44628</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34423,7 +34423,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34480,7 +34480,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34537,7 +34537,7 @@
         <v>44657</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34594,7 +34594,7 @@
         <v>44657</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34651,7 +34651,7 @@
         <v>44994</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34708,7 +34708,7 @@
         <v>45798</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34770,7 +34770,7 @@
         <v>44673</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34827,7 +34827,7 @@
         <v>45797</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34889,7 +34889,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34951,7 +34951,7 @@
         <v>45562</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35013,7 +35013,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35070,7 +35070,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35127,7 +35127,7 @@
         <v>45589</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35189,7 +35189,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35251,7 +35251,7 @@
         <v>45589</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35313,7 +35313,7 @@
         <v>45583</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35375,7 +35375,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35437,7 +35437,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35499,7 +35499,7 @@
         <v>45840</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35556,7 +35556,7 @@
         <v>45212</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35618,7 +35618,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35675,7 +35675,7 @@
         <v>45687</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35732,7 +35732,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35794,7 +35794,7 @@
         <v>45770</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35851,7 +35851,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35913,7 +35913,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35975,7 +35975,7 @@
         <v>45840</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36037,7 +36037,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36094,7 +36094,7 @@
         <v>45674</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36151,7 +36151,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36208,7 +36208,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36270,7 +36270,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36332,7 +36332,7 @@
         <v>45803</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36389,7 +36389,7 @@
         <v>45803</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36446,7 +36446,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36508,7 +36508,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36570,7 +36570,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36632,7 +36632,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36694,7 +36694,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36751,7 +36751,7 @@
         <v>45625</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36813,7 +36813,7 @@
         <v>45761</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36875,7 +36875,7 @@
         <v>45803</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36932,7 +36932,7 @@
         <v>45804</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36989,7 +36989,7 @@
         <v>45590</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37046,7 +37046,7 @@
         <v>45685</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37103,7 +37103,7 @@
         <v>45505</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37165,7 +37165,7 @@
         <v>45639</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37222,7 +37222,7 @@
         <v>45608</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37279,7 +37279,7 @@
         <v>45608</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37336,7 +37336,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37393,7 +37393,7 @@
         <v>45704</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37450,7 +37450,7 @@
         <v>44903</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37507,7 +37507,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37564,7 +37564,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37621,7 +37621,7 @@
         <v>45608</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37678,7 +37678,7 @@
         <v>45460</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37740,7 +37740,7 @@
         <v>45645</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37802,7 +37802,7 @@
         <v>45212</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37859,7 +37859,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37916,7 +37916,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37978,7 +37978,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38040,7 +38040,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38102,7 +38102,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38159,7 +38159,7 @@
         <v>45161</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38221,7 +38221,7 @@
         <v>45152</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38278,7 +38278,7 @@
         <v>45237</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38335,7 +38335,7 @@
         <v>44994</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38392,7 +38392,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38449,7 +38449,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38506,7 +38506,7 @@
         <v>45659</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38563,7 +38563,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38620,7 +38620,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38682,7 +38682,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38744,7 +38744,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38801,7 +38801,7 @@
         <v>45232</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38858,7 +38858,7 @@
         <v>45232</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38915,7 +38915,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -38977,7 +38977,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39034,7 +39034,7 @@
         <v>45114</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39091,7 +39091,7 @@
         <v>45546</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45764</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45464</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45847.64745370371</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>44755</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39396,7 +39396,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39453,7 +39453,7 @@
         <v>45161</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39510,7 +39510,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39572,7 +39572,7 @@
         <v>44796</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39629,7 +39629,7 @@
         <v>44164</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39691,7 +39691,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39748,7 +39748,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45456</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45429</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40038,7 +40038,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40095,7 +40095,7 @@
         <v>45301</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40152,7 +40152,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40214,7 +40214,7 @@
         <v>45603</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40271,7 +40271,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40328,7 +40328,7 @@
         <v>45085</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40385,7 +40385,7 @@
         <v>45153</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40442,7 +40442,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40504,7 +40504,7 @@
         <v>45813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40566,7 +40566,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40690,7 +40690,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40752,7 +40752,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40809,7 +40809,7 @@
         <v>45813</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45246</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45414</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45762</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45149</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41218,7 +41218,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41275,7 +41275,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45314</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>45256</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41808,7 +41808,7 @@
         <v>44484</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41865,7 +41865,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41927,7 +41927,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -41989,7 +41989,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42046,7 +42046,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42103,7 +42103,7 @@
         <v>45446</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42160,7 +42160,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42222,7 +42222,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42284,7 +42284,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42346,7 +42346,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42403,7 +42403,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42465,7 +42465,7 @@
         <v>45818</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42527,7 +42527,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42584,7 +42584,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42641,7 +42641,7 @@
         <v>45254</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42698,7 +42698,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42755,7 +42755,7 @@
         <v>45818</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42817,7 +42817,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42899,7 +42899,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42956,7 +42956,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43075,7 +43075,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45770</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44648</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43313,7 +43313,7 @@
         <v>45264</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43375,7 +43375,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43437,7 +43437,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43494,7 +43494,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43556,7 +43556,7 @@
         <v>45323</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43613,7 +43613,7 @@
         <v>45824</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43670,7 +43670,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43727,7 +43727,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44823</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43846,7 +43846,7 @@
         <v>45356</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43965,7 +43965,7 @@
         <v>45824</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>44474</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44141,7 +44141,7 @@
         <v>44568</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44198,7 +44198,7 @@
         <v>45300</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44255,7 +44255,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44317,7 +44317,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44374,7 +44374,7 @@
         <v>45824</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45260</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44602,7 +44602,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44664,7 +44664,7 @@
         <v>45826</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44783,7 +44783,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>44648</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44907,7 +44907,7 @@
         <v>44386</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44964,7 +44964,7 @@
         <v>44067</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45870.38011574074</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45202,7 +45202,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45764</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45440,7 +45440,7 @@
         <v>45827</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45502,7 +45502,7 @@
         <v>45827</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45827</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45626,7 +45626,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45750,7 +45750,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>44573</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45869,7 +45869,7 @@
         <v>45345</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45926,7 +45926,7 @@
         <v>45483</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45983,7 +45983,7 @@
         <v>45285</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45874</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46117,7 +46117,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46174,7 +46174,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46231,7 +46231,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46288,7 +46288,7 @@
         <v>45323</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45840</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46531,7 +46531,7 @@
         <v>45831</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46588,7 +46588,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46650,7 +46650,7 @@
         <v>44970</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46707,7 +46707,7 @@
         <v>45874.5525</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47007,7 +47007,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47069,7 +47069,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47131,7 +47131,7 @@
         <v>45833</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47188,7 +47188,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47250,7 +47250,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47307,7 +47307,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47369,7 +47369,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47426,7 +47426,7 @@
         <v>45875.79864583333</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47483,7 +47483,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>45582</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>45834</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47716,7 +47716,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47773,7 +47773,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47830,7 +47830,7 @@
         <v>45589</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47892,7 +47892,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47949,7 +47949,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48011,7 +48011,7 @@
         <v>44356</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48068,7 +48068,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48130,7 +48130,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48187,7 +48187,7 @@
         <v>44143</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48244,7 +48244,7 @@
         <v>44124</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48301,7 +48301,7 @@
         <v>44292</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48358,7 +48358,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48415,7 +48415,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48472,7 +48472,7 @@
         <v>44747</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48529,7 +48529,7 @@
         <v>44706</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48586,7 +48586,7 @@
         <v>44423</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48643,7 +48643,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48700,7 +48700,7 @@
         <v>44979</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48762,7 +48762,7 @@
         <v>44931</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48819,7 +48819,7 @@
         <v>44216</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48876,7 +48876,7 @@
         <v>45586</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48938,7 +48938,7 @@
         <v>45187</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49000,7 +49000,7 @@
         <v>45600</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49057,7 +49057,7 @@
         <v>45591</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49119,7 +49119,7 @@
         <v>44925</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49176,7 +49176,7 @@
         <v>44378</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49233,7 +49233,7 @@
         <v>45091</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49290,7 +49290,7 @@
         <v>45561.58791666666</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49352,7 +49352,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49409,7 +49409,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49466,7 +49466,7 @@
         <v>45001</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49523,7 +49523,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49580,7 +49580,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49642,7 +49642,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49699,7 +49699,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49756,7 +49756,7 @@
         <v>44585</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49813,7 +49813,7 @@
         <v>44847</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49932,7 +49932,7 @@
         <v>44392</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49989,7 +49989,7 @@
         <v>45316</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>44552</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50103,7 +50103,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50160,7 +50160,7 @@
         <v>45470</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50222,7 +50222,7 @@
         <v>45587</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50279,7 +50279,7 @@
         <v>45114</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50336,7 +50336,7 @@
         <v>44566</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50393,7 +50393,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50450,7 +50450,7 @@
         <v>45685</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50507,7 +50507,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50564,7 +50564,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50621,7 +50621,7 @@
         <v>45246</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45762</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50797,7 +50797,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50854,7 +50854,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44124</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44889</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45819</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45212</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45771</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44795</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44904</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44130</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44082</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44064</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44165</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44489</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44804</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45341</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44678</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45714</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45301</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>45842</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45559</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45701</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45526</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44830</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>45072</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44796</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44062</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44064</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44365</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45611</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45803.67</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45594</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45446</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45205</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44692</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45513</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45538</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45773</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45586</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>44217</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>44207</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>44075</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>44158</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44158</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44509</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44677</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44215</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44274</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44577</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>44414</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44350</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>44090</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44671</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44120</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44313</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44216</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44350</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44809</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44414</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44648</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44138</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44130</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44165</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>44187</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44168</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44274</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44286</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44617</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44439</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44464</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44865</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44204</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44609</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44223</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44110</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44158</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44671</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44182</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44125</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44151</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44721</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44358</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44796</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>44749</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44174</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44722</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>44484</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44182</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44438</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44217</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44313</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44530</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44099</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44648</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44414</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44480</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44565</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44473</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44566</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44182</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44182</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44617</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44062</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44529</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44596</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44293</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44648</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44356</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44734</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44489</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44248</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44565</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44116</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44439</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44356</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44566</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44566</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44635</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44671</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44274</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44489</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45358</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44313</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45672</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45771</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44908</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45099</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44211</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45708</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44299</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45387</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45764</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45764</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45105</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>45301</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45397</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45397</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45642</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45068</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45254</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>44833</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45110</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45778</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45155</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45574</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44529</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45156</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44983</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45786</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45149</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45152</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44735</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45591</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44609</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45379</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45370</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45161</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45161</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45758</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45429</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45761</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>44795</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>44477</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45483</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45793</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45216</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45596</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45590</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45590</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45793</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44120</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44120</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44566</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45645</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44573</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45643</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45774</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45798</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45478</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45803</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45411</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45646</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45803</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45804</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45590</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45682</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44628</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45608</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45608</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45608</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44558</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45583</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>44333</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44077</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45212</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45687</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44883</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45456</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45770</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44378</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45674</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45419</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45546</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45464</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45847.64745370371</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45516</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44391</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45685</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>44374</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45505</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45639</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45456</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45429</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44127</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45460</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45589</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45553</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45152</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45813</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45237</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45813</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45446</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44908</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45429</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45429</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45764</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44755</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45818</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45448</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45161</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45818</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44994</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>44164</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44110</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44648</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45205</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45204</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45301</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44110</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>44151</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>44889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44901</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45824</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45824</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45824</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45246</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45414</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44529</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44529</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45826</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45762</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45314</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>44881</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45256</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>44484</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45827</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45827</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45827</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45750</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45132</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45254</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45013</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45770</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45874</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44648</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45264</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45653</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45653</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45226</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45831</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45323</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45356</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45232</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45833</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44474</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45300</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45260</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45834</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45870</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45803</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45874</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45345</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45483</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45285</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>44445</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45323</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45686.42519675926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44970</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45840</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45747.56875</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45840</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45884.39142361111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45582</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45589</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45882</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45882</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45882</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44356</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>44642</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45875</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45840</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44490</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45054</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45448</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>44963</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44143</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>44124</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45764</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>44292</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45764</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>44657</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>44657</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44994</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44673</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45562</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45589</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45589</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44747</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44706</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44423</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44979</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44931</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44216</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45586</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45187</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45625</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45600</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>45591</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>44903</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44925</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44378</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45561.58791666666</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45645</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45212</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45001</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>44994</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45232</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45232</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>44585</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45114</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44847</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44796</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44392</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45316</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44552</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45470</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45603</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45085</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45587</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45153</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45114</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>44566</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45149</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45685</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45246</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45762</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44823</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44568</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45453</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45639</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44648</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>44386</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44067</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45099</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>45764</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>45770</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45454</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>44445</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45425</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45672</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45625</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45646</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45766</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45752</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45649</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45748</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44524</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45761</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>44529</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>44642</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>45769</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>44657</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>44900</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45264</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>44330</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45350</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45772</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>44298</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45379</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>45210</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>44110</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>44887</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>44484</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44565</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>45659</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45596</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45723</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45723</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45085</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>44438</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>44529</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45070</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>44248</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45749</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45035</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45077</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45632</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45341</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>44812</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45079</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45653.46922453704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45593</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>44833</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>45152</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45254</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>44127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>44935</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45338</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>44910</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45232</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45244</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45769</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>45406</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45561</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45351</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45732</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44124</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>44889</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1834,7 +1834,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45819</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45212</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45771</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44795</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44904</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>44130</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4026,7 +4026,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44082</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44064</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4662,7 +4662,7 @@
         <v>44165</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4753,7 +4753,7 @@
         <v>44489</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
         <v>44804</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45341</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44678</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45714</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45301</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5384,7 +5384,7 @@
         <v>45842</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5475,7 +5475,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5570,7 +5570,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         <v>45559</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5756,7 +5756,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5842,7 +5842,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45701</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6114,7 +6114,7 @@
         <v>45526</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6205,7 +6205,7 @@
         <v>45137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>44830</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>45072</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6575,7 +6575,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44796</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6938,7 +6938,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7028,7 +7028,7 @@
         <v>44062</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7207,7 +7207,7 @@
         <v>44064</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7301,7 +7301,7 @@
         <v>44365</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7391,7 +7391,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7476,7 +7476,7 @@
         <v>45611</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7566,7 +7566,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7656,7 +7656,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7745,7 +7745,7 @@
         <v>45645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45803.67</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8015,7 +8015,7 @@
         <v>45594</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8105,7 +8105,7 @@
         <v>45446</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8195,7 +8195,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         <v>45205</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8473,7 +8473,7 @@
         <v>44692</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8563,7 +8563,7 @@
         <v>45513</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8738,7 +8738,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8828,7 +8828,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8918,7 +8918,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9003,7 +9003,7 @@
         <v>45538</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9093,7 +9093,7 @@
         <v>45773</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9183,7 +9183,7 @@
         <v>45586</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         <v>44217</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9330,7 +9330,7 @@
         <v>44207</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9387,7 +9387,7 @@
         <v>44075</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9444,7 +9444,7 @@
         <v>44158</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9501,7 +9501,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9558,7 +9558,7 @@
         <v>44158</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9615,7 +9615,7 @@
         <v>44509</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9672,7 +9672,7 @@
         <v>44677</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
         <v>44215</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9786,7 +9786,7 @@
         <v>44274</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9843,7 +9843,7 @@
         <v>44577</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9900,7 +9900,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9957,7 +9957,7 @@
         <v>44414</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10014,7 +10014,7 @@
         <v>44350</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10071,7 +10071,7 @@
         <v>44090</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10128,7 +10128,7 @@
         <v>44217</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10185,7 +10185,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44671</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10366,7 +10366,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10423,7 +10423,7 @@
         <v>44852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10485,7 +10485,7 @@
         <v>44120</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10542,7 +10542,7 @@
         <v>44313</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44216</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44350</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10713,7 +10713,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44809</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10951,7 +10951,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11008,7 +11008,7 @@
         <v>44414</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44815</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44648</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11189,7 +11189,7 @@
         <v>44138</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
         <v>44130</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11308,7 +11308,7 @@
         <v>44165</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>44187</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11479,7 +11479,7 @@
         <v>44168</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         <v>44274</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11593,7 +11593,7 @@
         <v>44286</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11650,7 +11650,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11707,7 +11707,7 @@
         <v>44617</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11764,7 +11764,7 @@
         <v>44648</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11888,7 +11888,7 @@
         <v>44439</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11945,7 +11945,7 @@
         <v>44464</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44865</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12064,7 +12064,7 @@
         <v>44204</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44609</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12235,7 +12235,7 @@
         <v>44223</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12292,7 +12292,7 @@
         <v>44110</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44158</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44671</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12525,7 +12525,7 @@
         <v>44182</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12582,7 +12582,7 @@
         <v>44125</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44151</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12763,7 +12763,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12882,7 +12882,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12944,7 +12944,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13001,7 +13001,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13063,7 +13063,7 @@
         <v>44721</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13120,7 +13120,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13177,7 +13177,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44358</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44796</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>44749</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13576,7 +13576,7 @@
         <v>44174</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44722</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>44484</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13876,7 +13876,7 @@
         <v>44182</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13933,7 +13933,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13990,7 +13990,7 @@
         <v>44438</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14047,7 +14047,7 @@
         <v>44217</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14104,7 +14104,7 @@
         <v>44238</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14161,7 +14161,7 @@
         <v>44313</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14218,7 +14218,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14280,7 +14280,7 @@
         <v>44530</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14337,7 +14337,7 @@
         <v>44480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14394,7 +14394,7 @@
         <v>44099</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44648</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14513,7 +14513,7 @@
         <v>44414</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44480</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14627,7 +14627,7 @@
         <v>44565</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14684,7 +14684,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44473</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14808,7 +14808,7 @@
         <v>44566</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14865,7 +14865,7 @@
         <v>44182</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44182</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44617</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15036,7 +15036,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44062</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44529</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15212,7 +15212,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15269,7 +15269,7 @@
         <v>44596</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44293</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15393,7 +15393,7 @@
         <v>44648</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15455,7 +15455,7 @@
         <v>44356</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15512,7 +15512,7 @@
         <v>44734</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15569,7 +15569,7 @@
         <v>44795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15631,7 +15631,7 @@
         <v>44489</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15688,7 +15688,7 @@
         <v>44248</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15745,7 +15745,7 @@
         <v>44565</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15802,7 +15802,7 @@
         <v>44116</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15859,7 +15859,7 @@
         <v>44439</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15916,7 +15916,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15978,7 +15978,7 @@
         <v>44356</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16035,7 +16035,7 @@
         <v>44566</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16092,7 +16092,7 @@
         <v>44566</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16149,7 +16149,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16211,7 +16211,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16268,7 +16268,7 @@
         <v>44635</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16330,7 +16330,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16387,7 +16387,7 @@
         <v>44671</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16444,7 +16444,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16501,7 +16501,7 @@
         <v>44274</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16558,7 +16558,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16615,7 +16615,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16677,7 +16677,7 @@
         <v>44489</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16734,7 +16734,7 @@
         <v>45358</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16791,7 +16791,7 @@
         <v>45356</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16848,7 +16848,7 @@
         <v>44313</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16905,7 +16905,7 @@
         <v>45672</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16962,7 +16962,7 @@
         <v>45771</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17019,7 +17019,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17081,7 +17081,7 @@
         <v>44908</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17138,7 +17138,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17200,7 +17200,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17257,7 +17257,7 @@
         <v>45099</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17314,7 +17314,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17371,7 +17371,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17428,7 +17428,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17490,7 +17490,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17547,7 +17547,7 @@
         <v>44211</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>45708</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17780,7 +17780,7 @@
         <v>44299</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17894,7 +17894,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17956,7 +17956,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18018,7 +18018,7 @@
         <v>45387</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18075,7 +18075,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18132,7 +18132,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18194,7 +18194,7 @@
         <v>45764</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18251,7 +18251,7 @@
         <v>45764</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18308,7 +18308,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18365,7 +18365,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18422,7 +18422,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18479,7 +18479,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18536,7 +18536,7 @@
         <v>45105</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18598,7 +18598,7 @@
         <v>45301</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18660,7 +18660,7 @@
         <v>45397</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18717,7 +18717,7 @@
         <v>45397</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18774,7 +18774,7 @@
         <v>45642</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18831,7 +18831,7 @@
         <v>45068</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18888,7 +18888,7 @@
         <v>45254</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18945,7 +18945,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19002,7 +19002,7 @@
         <v>44833</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19059,7 +19059,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19121,7 +19121,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19178,7 +19178,7 @@
         <v>45110</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19240,7 +19240,7 @@
         <v>45778</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19302,7 +19302,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19359,7 +19359,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19421,7 +19421,7 @@
         <v>45155</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19483,7 +19483,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19540,7 +19540,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19597,7 +19597,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19654,7 +19654,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19716,7 +19716,7 @@
         <v>45574</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19778,7 +19778,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19840,7 +19840,7 @@
         <v>44529</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19897,7 +19897,7 @@
         <v>45156</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19954,7 +19954,7 @@
         <v>44983</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20011,7 +20011,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20073,7 +20073,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20130,7 +20130,7 @@
         <v>45786</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20192,7 +20192,7 @@
         <v>45149</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20249,7 +20249,7 @@
         <v>45152</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20306,7 +20306,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20363,7 +20363,7 @@
         <v>44735</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20425,7 +20425,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20482,7 +20482,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20539,7 +20539,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20596,7 +20596,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20653,7 +20653,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20710,7 +20710,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20772,7 +20772,7 @@
         <v>45591</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20834,7 +20834,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20896,7 +20896,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20958,7 +20958,7 @@
         <v>44609</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21015,7 +21015,7 @@
         <v>45379</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21072,7 +21072,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21134,7 +21134,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21196,7 +21196,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21258,7 +21258,7 @@
         <v>45370</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21315,7 +21315,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21377,7 +21377,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21439,7 +21439,7 @@
         <v>45161</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21501,7 +21501,7 @@
         <v>45161</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21563,7 +21563,7 @@
         <v>45758</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21620,7 +21620,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21677,7 +21677,7 @@
         <v>45429</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21734,7 +21734,7 @@
         <v>45761</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21796,7 +21796,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21858,7 +21858,7 @@
         <v>44795</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21915,7 +21915,7 @@
         <v>44477</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21972,7 +21972,7 @@
         <v>45483</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22029,7 +22029,7 @@
         <v>45793</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22091,7 +22091,7 @@
         <v>45216</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45596</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22324,7 +22324,7 @@
         <v>45590</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22381,7 +22381,7 @@
         <v>45590</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22438,7 +22438,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45793</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22562,7 +22562,7 @@
         <v>44120</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22619,7 +22619,7 @@
         <v>44120</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22676,7 +22676,7 @@
         <v>44566</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22733,7 +22733,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22795,7 +22795,7 @@
         <v>45645</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22857,7 +22857,7 @@
         <v>44573</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22981,7 +22981,7 @@
         <v>45643</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23043,7 +23043,7 @@
         <v>45774</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23105,7 +23105,7 @@
         <v>45798</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23167,7 +23167,7 @@
         <v>45797</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23229,7 +23229,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23410,7 +23410,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23472,7 +23472,7 @@
         <v>45478</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23529,7 +23529,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23591,7 +23591,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23653,7 +23653,7 @@
         <v>45803</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23710,7 +23710,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23772,7 +23772,7 @@
         <v>45411</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23829,7 +23829,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23891,7 +23891,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23953,7 +23953,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24010,7 +24010,7 @@
         <v>45646</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24067,7 +24067,7 @@
         <v>45803</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24124,7 +24124,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24181,7 +24181,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24238,7 +24238,7 @@
         <v>45804</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24295,7 +24295,7 @@
         <v>45590</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24352,7 +24352,7 @@
         <v>45682</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24414,7 +24414,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24471,7 +24471,7 @@
         <v>44628</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24528,7 +24528,7 @@
         <v>45608</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24585,7 +24585,7 @@
         <v>45608</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24642,7 +24642,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24699,7 +24699,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24756,7 +24756,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24813,7 +24813,7 @@
         <v>45608</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24870,7 +24870,7 @@
         <v>44558</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24927,7 +24927,7 @@
         <v>45583</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24989,7 +24989,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25051,7 +25051,7 @@
         <v>44333</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25108,7 +25108,7 @@
         <v>44077</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25232,7 +25232,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25289,7 +25289,7 @@
         <v>45212</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25351,7 +25351,7 @@
         <v>45687</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25408,7 +25408,7 @@
         <v>44883</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25470,7 +25470,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25532,7 +25532,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25589,7 +25589,7 @@
         <v>45456</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25646,7 +25646,7 @@
         <v>45770</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25703,7 +25703,7 @@
         <v>44441</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25760,7 +25760,7 @@
         <v>44378</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25817,7 +25817,7 @@
         <v>45674</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25874,7 +25874,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25936,7 +25936,7 @@
         <v>45419</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25993,7 +25993,7 @@
         <v>45546</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>45464</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>45847.64745370371</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45516</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26241,7 +26241,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26303,7 +26303,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26360,7 +26360,7 @@
         <v>44391</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26417,7 +26417,7 @@
         <v>45685</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26474,7 +26474,7 @@
         <v>44374</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26531,7 +26531,7 @@
         <v>45505</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26593,7 +26593,7 @@
         <v>45639</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26650,7 +26650,7 @@
         <v>45456</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26707,7 +26707,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26764,7 +26764,7 @@
         <v>45429</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>45704</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44127</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27168,7 +27168,7 @@
         <v>45460</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27230,7 +27230,7 @@
         <v>45589</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27292,7 +27292,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27349,7 +27349,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27411,7 +27411,7 @@
         <v>45553</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27473,7 +27473,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27535,7 +27535,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27597,7 +27597,7 @@
         <v>45152</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27654,7 +27654,7 @@
         <v>45813</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45237</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27835,7 +27835,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27897,7 +27897,7 @@
         <v>45813</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27959,7 +27959,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28021,7 +28021,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28083,7 +28083,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28145,7 +28145,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28202,7 +28202,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28264,7 +28264,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28388,7 +28388,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28450,7 +28450,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28512,7 +28512,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28569,7 +28569,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28626,7 +28626,7 @@
         <v>45446</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28683,7 +28683,7 @@
         <v>44908</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28740,7 +28740,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28802,7 +28802,7 @@
         <v>45429</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28859,7 +28859,7 @@
         <v>45429</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28916,7 +28916,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28973,7 +28973,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29035,7 +29035,7 @@
         <v>45764</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29092,7 +29092,7 @@
         <v>44755</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29154,7 +29154,7 @@
         <v>45818</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29216,7 +29216,7 @@
         <v>45448</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29278,7 +29278,7 @@
         <v>45161</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29335,7 +29335,7 @@
         <v>45818</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29397,7 +29397,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29479,7 +29479,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29536,7 +29536,7 @@
         <v>44994</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29593,7 +29593,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29655,7 +29655,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29717,7 +29717,7 @@
         <v>44164</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29779,7 +29779,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29841,7 +29841,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29898,7 +29898,7 @@
         <v>44110</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29955,7 +29955,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30012,7 +30012,7 @@
         <v>44648</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30074,7 +30074,7 @@
         <v>45205</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30136,7 +30136,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30193,7 +30193,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30250,7 +30250,7 @@
         <v>45204</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30307,7 +30307,7 @@
         <v>45301</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30364,7 +30364,7 @@
         <v>44110</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30426,7 +30426,7 @@
         <v>44151</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30488,7 +30488,7 @@
         <v>44889</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30545,7 +30545,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30607,7 +30607,7 @@
         <v>44901</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30664,7 +30664,7 @@
         <v>45824</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30721,7 +30721,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30783,7 +30783,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>45824</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30964,7 +30964,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31021,7 +31021,7 @@
         <v>45824</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31078,7 +31078,7 @@
         <v>45246</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31135,7 +31135,7 @@
         <v>45414</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31306,7 +31306,7 @@
         <v>44529</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31363,7 +31363,7 @@
         <v>44529</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31420,7 +31420,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31482,7 +31482,7 @@
         <v>45826</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31544,7 +31544,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>45518</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31663,7 +31663,7 @@
         <v>45762</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31720,7 +31720,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31782,7 +31782,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31844,7 +31844,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31901,7 +31901,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31958,7 +31958,7 @@
         <v>45314</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32015,7 +32015,7 @@
         <v>44881</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32072,7 +32072,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45256</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>44484</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45827</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45827</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32434,7 +32434,7 @@
         <v>45827</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32496,7 +32496,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32558,7 +32558,7 @@
         <v>45750</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32620,7 +32620,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32677,7 +32677,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32739,7 +32739,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32801,7 +32801,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32858,7 +32858,7 @@
         <v>45132</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32915,7 +32915,7 @@
         <v>45254</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32972,7 +32972,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33029,7 +33029,7 @@
         <v>45013</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33086,7 +33086,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33143,7 +33143,7 @@
         <v>45770</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33200,7 +33200,7 @@
         <v>45874</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33396,7 +33396,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33453,7 +33453,7 @@
         <v>44648</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33515,7 +33515,7 @@
         <v>45264</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33577,7 +33577,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33639,7 +33639,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33763,7 +33763,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33825,7 +33825,7 @@
         <v>45653</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33882,7 +33882,7 @@
         <v>45653</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33939,7 +33939,7 @@
         <v>45226</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45831</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34120,7 +34120,7 @@
         <v>45323</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34177,7 +34177,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34234,7 +34234,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45356</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34467,7 +34467,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34529,7 +34529,7 @@
         <v>45232</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34591,7 +34591,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34653,7 +34653,7 @@
         <v>45833</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34710,7 +34710,7 @@
         <v>44474</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34767,7 +34767,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34891,7 +34891,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34948,7 +34948,7 @@
         <v>45300</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35067,7 +35067,7 @@
         <v>45260</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35124,7 +35124,7 @@
         <v>45834</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35181,7 +35181,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35238,7 +35238,7 @@
         <v>44573</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45870</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35362,7 +35362,7 @@
         <v>45803</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35419,7 +35419,7 @@
         <v>45874</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35481,7 +35481,7 @@
         <v>45345</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35538,7 +35538,7 @@
         <v>45483</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35595,7 +35595,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35652,7 +35652,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35714,7 +35714,7 @@
         <v>45285</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35771,7 +35771,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35828,7 +35828,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35890,7 +35890,7 @@
         <v>44445</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35947,7 +35947,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -36004,7 +36004,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36066,7 +36066,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36123,7 +36123,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45323</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>45686.42519675926</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>44970</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36703,7 +36703,7 @@
         <v>45840</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36760,7 +36760,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36817,7 +36817,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36874,7 +36874,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36936,7 +36936,7 @@
         <v>45747.56875</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36993,7 +36993,7 @@
         <v>45840</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37055,7 +37055,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37112,7 +37112,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37174,7 +37174,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37231,7 +37231,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37288,7 +37288,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37350,7 +37350,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37407,7 +37407,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37464,7 +37464,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37526,7 +37526,7 @@
         <v>45884.39142361111</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37588,7 +37588,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37645,7 +37645,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37702,7 +37702,7 @@
         <v>45582</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37759,7 +37759,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37816,7 +37816,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37873,7 +37873,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37930,7 +37930,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37987,7 +37987,7 @@
         <v>45589</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38049,7 +38049,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38106,7 +38106,7 @@
         <v>45882</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38163,7 +38163,7 @@
         <v>45882</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38220,7 +38220,7 @@
         <v>45882</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38277,7 +38277,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38339,7 +38339,7 @@
         <v>44356</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38396,7 +38396,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38458,7 +38458,7 @@
         <v>44642</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38520,7 +38520,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38577,7 +38577,7 @@
         <v>45875</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38634,7 +38634,7 @@
         <v>45840</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38696,7 +38696,7 @@
         <v>44490</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38758,7 +38758,7 @@
         <v>45054</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38815,7 +38815,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38877,7 +38877,7 @@
         <v>45448</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38939,7 +38939,7 @@
         <v>44963</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38996,7 +38996,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39053,7 +39053,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39110,7 +39110,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39167,7 +39167,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39229,7 +39229,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39286,7 +39286,7 @@
         <v>44143</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39343,7 +39343,7 @@
         <v>44124</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39400,7 +39400,7 @@
         <v>45764</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39457,7 +39457,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39514,7 +39514,7 @@
         <v>44292</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39571,7 +39571,7 @@
         <v>45764</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39628,7 +39628,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39685,7 +39685,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39742,7 +39742,7 @@
         <v>44657</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39799,7 +39799,7 @@
         <v>44657</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39856,7 +39856,7 @@
         <v>44994</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39913,7 +39913,7 @@
         <v>44673</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39970,7 +39970,7 @@
         <v>45562</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40032,7 +40032,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40089,7 +40089,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40146,7 +40146,7 @@
         <v>45589</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40208,7 +40208,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40270,7 +40270,7 @@
         <v>45589</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40332,7 +40332,7 @@
         <v>44747</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40389,7 +40389,7 @@
         <v>44706</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40446,7 +40446,7 @@
         <v>44423</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40503,7 +40503,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40560,7 +40560,7 @@
         <v>44979</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40622,7 +40622,7 @@
         <v>44931</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40679,7 +40679,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40736,7 +40736,7 @@
         <v>44216</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40793,7 +40793,7 @@
         <v>45586</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40855,7 +40855,7 @@
         <v>45187</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40917,7 +40917,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40979,7 +40979,7 @@
         <v>45625</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41041,7 +41041,7 @@
         <v>45600</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41098,7 +41098,7 @@
         <v>45591</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41160,7 +41160,7 @@
         <v>44903</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41217,7 +41217,7 @@
         <v>44925</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41274,7 +41274,7 @@
         <v>44378</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41331,7 +41331,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41388,7 +41388,7 @@
         <v>45091</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41445,7 +41445,7 @@
         <v>45561.58791666666</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41507,7 +41507,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41564,7 +41564,7 @@
         <v>45645</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41626,7 +41626,7 @@
         <v>45212</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41683,7 +41683,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41740,7 +41740,7 @@
         <v>45001</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41797,7 +41797,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41854,7 +41854,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41916,7 +41916,7 @@
         <v>45161</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41978,7 +41978,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42035,7 +42035,7 @@
         <v>44994</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42092,7 +42092,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42149,7 +42149,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42206,7 +42206,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42263,7 +42263,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42320,7 +42320,7 @@
         <v>45232</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42377,7 +42377,7 @@
         <v>45232</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42434,7 +42434,7 @@
         <v>44585</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42491,7 +42491,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42553,7 +42553,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42610,7 +42610,7 @@
         <v>45114</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42667,7 +42667,7 @@
         <v>44847</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42724,7 +42724,7 @@
         <v>44796</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42781,7 +42781,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42843,7 +42843,7 @@
         <v>44392</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42900,7 +42900,7 @@
         <v>45316</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42957,7 +42957,7 @@
         <v>44552</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43014,7 +43014,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43071,7 +43071,7 @@
         <v>45470</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43133,7 +43133,7 @@
         <v>45603</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43190,7 +43190,7 @@
         <v>45085</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43247,7 +43247,7 @@
         <v>45587</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43304,7 +43304,7 @@
         <v>45153</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43361,7 +43361,7 @@
         <v>45114</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43418,7 +43418,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43475,7 +43475,7 @@
         <v>44566</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43532,7 +43532,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43589,7 +43589,7 @@
         <v>45149</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43646,7 +43646,7 @@
         <v>45685</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43703,7 +43703,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43760,7 +43760,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43817,7 +43817,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43874,7 +43874,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43931,7 +43931,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43988,7 +43988,7 @@
         <v>45246</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44045,7 +44045,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44107,7 +44107,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44164,7 +44164,7 @@
         <v>45762</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44221,7 +44221,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44278,7 +44278,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44335,7 +44335,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44823</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44511,7 +44511,7 @@
         <v>44568</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>45453</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>45639</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>44648</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44858,7 +44858,7 @@
         <v>44386</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44915,7 +44915,7 @@
         <v>44067</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44972,7 +44972,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45029,7 +45029,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45086,7 +45086,7 @@
         <v>45099</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45143,7 +45143,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45438,7 +45438,7 @@
         <v>45764</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45495,7 +45495,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45557,7 +45557,7 @@
         <v>45770</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>45454</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45671,7 +45671,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45728,7 +45728,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45790,7 +45790,7 @@
         <v>44445</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45847,7 +45847,7 @@
         <v>45425</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45904,7 +45904,7 @@
         <v>45672</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45961,7 +45961,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46018,7 +46018,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46080,7 +46080,7 @@
         <v>45625</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46137,7 +46137,7 @@
         <v>45646</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46194,7 +46194,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46251,7 +46251,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46308,7 +46308,7 @@
         <v>45766</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46370,7 +46370,7 @@
         <v>45752</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46427,7 +46427,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45649</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45748</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44524</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45761</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46945,7 +46945,7 @@
         <v>44529</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47059,7 +47059,7 @@
         <v>45110</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>44642</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47178,7 +47178,7 @@
         <v>45769</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47235,7 +47235,7 @@
         <v>44657</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47292,7 +47292,7 @@
         <v>44900</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>45264</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47587,7 +47587,7 @@
         <v>44330</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47644,7 +47644,7 @@
         <v>45350</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45772</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>44298</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45379</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>45210</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47991,7 +47991,7 @@
         <v>44110</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>44887</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48110,7 +48110,7 @@
         <v>44484</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48172,7 +48172,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48229,7 +48229,7 @@
         <v>44565</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>45659</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48405,7 +48405,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48462,7 +48462,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>45596</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45723</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45723</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48747,7 +48747,7 @@
         <v>45085</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48804,7 +48804,7 @@
         <v>44438</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48861,7 +48861,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48923,7 +48923,7 @@
         <v>44529</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48980,7 +48980,7 @@
         <v>45070</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49037,7 +49037,7 @@
         <v>44248</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49094,7 +49094,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49156,7 +49156,7 @@
         <v>45749</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49213,7 +49213,7 @@
         <v>45035</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49270,7 +49270,7 @@
         <v>45077</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49327,7 +49327,7 @@
         <v>45632</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49384,7 +49384,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49441,7 +49441,7 @@
         <v>45341</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49503,7 +49503,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49622,7 +49622,7 @@
         <v>44812</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49679,7 +49679,7 @@
         <v>45079</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49736,7 +49736,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49793,7 +49793,7 @@
         <v>45653.46922453704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49850,7 +49850,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49907,7 +49907,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49964,7 +49964,7 @@
         <v>45593</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50026,7 +50026,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50083,7 +50083,7 @@
         <v>44833</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50140,7 +50140,7 @@
         <v>45152</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50197,7 +50197,7 @@
         <v>45254</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50254,7 +50254,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50311,7 +50311,7 @@
         <v>44127</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50368,7 +50368,7 @@
         <v>44935</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50425,7 +50425,7 @@
         <v>45338</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50482,7 +50482,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50539,7 +50539,7 @@
         <v>44910</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50601,7 +50601,7 @@
         <v>45232</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50663,7 +50663,7 @@
         <v>45244</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50725,7 +50725,7 @@
         <v>45769</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50782,7 +50782,7 @@
         <v>45406</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50839,7 +50839,7 @@
         <v>45561</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50896,7 +50896,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50953,7 +50953,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51010,7 +51010,7 @@
         <v>45351</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51067,7 +51067,7 @@
         <v>45732</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>45237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44124</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45212</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45819</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44889</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45771</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45645</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45622</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45512</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44869</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>44158</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44904</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44130</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44804</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44082</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>44489</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45072</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45526</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44678</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45341</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45714</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45137</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45701</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45559</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45301</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45842</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44830</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44648</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44853</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44840</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44421</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44796</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44088</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44365</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45538</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>45773</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45513</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45645</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45205</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>45446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45803.67</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45611</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44692</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45594</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45586</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>44217</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44075</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44158</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>44158</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>44509</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>44677</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44215</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>44274</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>44577</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44414</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44350</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44090</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44217</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44671</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44120</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44216</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>44313</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44350</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44414</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44809</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44815</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44165</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44187</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44168</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44274</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44286</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44617</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44274</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44648</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44439</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44284</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44464</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44865</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44204</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44609</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44223</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44110</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44158</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44671</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44182</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44125</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44274</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44313</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44313</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44151</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44721</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44358</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44796</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44749</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44484</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44722</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44174</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44238</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44313</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44438</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44217</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44182</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44530</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44480</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44099</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44480</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>44414</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44565</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44566</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44617</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44182</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44648</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44596</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44473</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44529</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44293</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44182</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44356</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44795</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44489</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44565</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44439</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44648</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44671</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44734</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45301</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>44356</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44248</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44423</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45411</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>44635</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45761</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>44833</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45646</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44552</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45674</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45750</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>44292</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>44566</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44566</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45769</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45762</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44378</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44609</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45379</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44994</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44881</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>44568</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44330</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45639</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45764</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45764</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>44903</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45643</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45770</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45682</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45672</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44127</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>44298</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45752</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45591</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45591</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45586</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45425</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44248</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44657</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44392</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44847</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44489</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44812</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44823</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45419</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45625</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>44573</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45708</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45723</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45723</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45152</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44925</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45749</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45013</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>44585</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45254</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45114</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45314</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45161</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45774</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45589</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45582</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45204</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45687</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45603</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44963</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45370</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44441</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45505</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45769</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44120</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44120</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45764</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44979</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44391</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45345</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44374</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45470</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45338</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45653</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44558</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44529</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45766</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45453</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45574</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44164</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45478</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44386</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45226</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45764</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44529</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>44529</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44211</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44067</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44970</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45232</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45596</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45285</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44642</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45077</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>44910</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45254</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45553</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45397</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45397</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>44796</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45764</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45448</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45149</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45232</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45232</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44983</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45786</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45149</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45054</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45429</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45758</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45085</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45379</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45205</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45793</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45793</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44127</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45260</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45639</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45583</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44484</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45761</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45264</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45264</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45590</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45590</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>44077</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45210</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44833</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45797</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44524</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44935</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44445</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44529</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45212</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45589</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45659</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44673</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45246</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45448</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45798</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>44657</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>44657</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45244</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45155</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45748</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45803</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45803</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44110</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45645</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45608</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45608</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>45608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>45590</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45110</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45301</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45429</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45464</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45646</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45456</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44648</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45232</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45546</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45672</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45764</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45429</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45429</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45085</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44900</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45254</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45483</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45561.58791666666</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45153</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45813</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45414</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45256</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45562</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45653.46922453704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45387</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45483</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>44143</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45156</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44755</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45446</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44628</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45110</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45161</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45161</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>44642</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45070</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44901</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>45246</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45356</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>44299</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45358</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45300</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45824</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45316</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45649</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45824</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45625</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44529</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45824</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45589</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39755,7 +39755,7 @@
         <v>45589</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45827</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45827</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>44648</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>45152</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>45212</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45827</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45460</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45826</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>45831</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45350</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>44474</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>44566</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>44908</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45216</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>44477</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45833</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44566</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45132</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45770</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45870</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45356</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45704</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>45114</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45323</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44438</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45099</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44124</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44994</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45068</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45834</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>44795</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45874</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45803</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44445</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45341</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45161</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45686.42519675926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45747.56875</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45875</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45840</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45596</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45882</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45840</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45456</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45772</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45645</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>44151</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45685</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45187</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44378</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44887</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45868</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45653</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>44110</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>45351</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>44994</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45884</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45887</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45323</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45685</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44931</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45882</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45882</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45001</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45887</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45732</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45891.51008101852</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45890.61597222222</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>44110</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>44889</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45632</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45406</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44735</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45035</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>44356</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45152</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>44883</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45771</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45587</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>44484</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45561</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44573</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45454</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45079</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>44648</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45762</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>44565</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>44216</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>45642</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>45237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,7 +1742,7 @@
         <v>44124</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45212</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>45819</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>44889</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45771</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>45645</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45622</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45512</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2900,7 +2900,7 @@
         <v>45819</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44869</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>44158</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44904</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44130</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4213,7 +4213,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4299,7 +4299,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4385,7 +4385,7 @@
         <v>44804</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4567,7 +4567,7 @@
         <v>44082</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4658,7 +4658,7 @@
         <v>44489</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4744,7 +4744,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4835,7 +4835,7 @@
         <v>45072</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4930,7 +4930,7 @@
         <v>45526</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5021,7 +5021,7 @@
         <v>44678</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5112,7 +5112,7 @@
         <v>45341</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5203,7 +5203,7 @@
         <v>45517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45714</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45137</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45701</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>45559</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45301</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5747,7 +5747,7 @@
         <v>45842</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5933,7 +5933,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6028,7 +6028,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44830</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44648</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6480,7 +6480,7 @@
         <v>44853</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6574,7 +6574,7 @@
         <v>44840</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6664,7 +6664,7 @@
         <v>44421</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6754,7 +6754,7 @@
         <v>44796</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44088</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7022,7 +7022,7 @@
         <v>44365</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7112,7 +7112,7 @@
         <v>45538</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>45773</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7377,7 +7377,7 @@
         <v>45513</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7462,7 +7462,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7547,7 +7547,7 @@
         <v>45645</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7637,7 +7637,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7727,7 +7727,7 @@
         <v>45205</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7821,7 +7821,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7910,7 +7910,7 @@
         <v>45446</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8000,7 +8000,7 @@
         <v>45803.67</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8090,7 +8090,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8180,7 +8180,7 @@
         <v>45611</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8270,7 +8270,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8360,7 +8360,7 @@
         <v>44692</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8450,7 +8450,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8540,7 +8540,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8720,7 +8720,7 @@
         <v>45594</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8810,7 +8810,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8989,7 +8989,7 @@
         <v>45586</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9079,7 +9079,7 @@
         <v>44217</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9193,7 +9193,7 @@
         <v>44075</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9250,7 +9250,7 @@
         <v>44158</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9307,7 +9307,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9364,7 +9364,7 @@
         <v>44158</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9421,7 +9421,7 @@
         <v>44509</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>44677</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9535,7 +9535,7 @@
         <v>44215</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9592,7 +9592,7 @@
         <v>44274</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9649,7 +9649,7 @@
         <v>44577</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9706,7 +9706,7 @@
         <v>44414</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9763,7 +9763,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9820,7 +9820,7 @@
         <v>44350</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9877,7 +9877,7 @@
         <v>44090</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9934,7 +9934,7 @@
         <v>44217</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10053,7 +10053,7 @@
         <v>44671</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10167,7 +10167,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10229,7 +10229,7 @@
         <v>44120</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10286,7 +10286,7 @@
         <v>44852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
         <v>44216</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10405,7 +10405,7 @@
         <v>44313</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10462,7 +10462,7 @@
         <v>44350</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10519,7 +10519,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10581,7 +10581,7 @@
         <v>44414</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10638,7 +10638,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10695,7 +10695,7 @@
         <v>44809</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10757,7 +10757,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10814,7 +10814,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10871,7 +10871,7 @@
         <v>44815</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10933,7 +10933,7 @@
         <v>44648</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -10995,7 +10995,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11052,7 +11052,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11114,7 +11114,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11171,7 +11171,7 @@
         <v>44165</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11228,7 +11228,7 @@
         <v>44187</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11285,7 +11285,7 @@
         <v>44168</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11342,7 +11342,7 @@
         <v>44274</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11399,7 +11399,7 @@
         <v>44286</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11456,7 +11456,7 @@
         <v>44617</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11513,7 +11513,7 @@
         <v>44274</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11570,7 +11570,7 @@
         <v>44648</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11632,7 +11632,7 @@
         <v>44439</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11689,7 +11689,7 @@
         <v>44284</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44464</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44865</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44204</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44609</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44223</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44110</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44158</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12217,7 +12217,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12274,7 +12274,7 @@
         <v>44671</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44182</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12388,7 +12388,7 @@
         <v>44125</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44274</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12740,7 +12740,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44313</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12859,7 +12859,7 @@
         <v>44313</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12916,7 +12916,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44151</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44721</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44358</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13382,7 +13382,7 @@
         <v>44796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13439,7 +13439,7 @@
         <v>44796</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13496,7 +13496,7 @@
         <v>44749</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13553,7 +13553,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13610,7 +13610,7 @@
         <v>44484</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44722</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>44174</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44238</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44313</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13967,7 +13967,7 @@
         <v>44438</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14024,7 +14024,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44217</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14143,7 +14143,7 @@
         <v>44182</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14200,7 +14200,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14257,7 +14257,7 @@
         <v>44530</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14314,7 +14314,7 @@
         <v>44480</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14371,7 +14371,7 @@
         <v>44099</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14428,7 +14428,7 @@
         <v>44480</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14485,7 +14485,7 @@
         <v>44414</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>44565</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14661,7 +14661,7 @@
         <v>44566</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14718,7 +14718,7 @@
         <v>44617</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14775,7 +14775,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14837,7 +14837,7 @@
         <v>44182</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14894,7 +14894,7 @@
         <v>44648</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>44596</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>44473</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15137,7 +15137,7 @@
         <v>44529</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>44293</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15256,7 +15256,7 @@
         <v>44182</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15313,7 +15313,7 @@
         <v>44356</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44795</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>44489</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44565</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>44439</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>44648</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15784,7 +15784,7 @@
         <v>44671</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>44734</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15960,7 +15960,7 @@
         <v>45301</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16022,7 +16022,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16084,7 +16084,7 @@
         <v>44356</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16141,7 +16141,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16198,7 +16198,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16255,7 +16255,7 @@
         <v>44248</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16312,7 +16312,7 @@
         <v>44423</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16369,7 +16369,7 @@
         <v>45411</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16426,7 +16426,7 @@
         <v>44635</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16488,7 +16488,7 @@
         <v>45761</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16545,7 +16545,7 @@
         <v>44116</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16602,7 +16602,7 @@
         <v>44833</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16659,7 +16659,7 @@
         <v>45518</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16716,7 +16716,7 @@
         <v>45646</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>44552</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16830,7 +16830,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16887,7 +16887,7 @@
         <v>45674</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16944,7 +16944,7 @@
         <v>45750</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17006,7 +17006,7 @@
         <v>44292</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17063,7 +17063,7 @@
         <v>44566</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17120,7 +17120,7 @@
         <v>44566</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17177,7 +17177,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17239,7 +17239,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17296,7 +17296,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17358,7 +17358,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17415,7 +17415,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17472,7 +17472,7 @@
         <v>45769</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17529,7 +17529,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17586,7 +17586,7 @@
         <v>45762</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17700,7 +17700,7 @@
         <v>44378</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17757,7 +17757,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17819,7 +17819,7 @@
         <v>44609</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17876,7 +17876,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17938,7 +17938,7 @@
         <v>45379</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -17995,7 +17995,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18052,7 +18052,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18109,7 +18109,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18166,7 +18166,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18223,7 +18223,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18280,7 +18280,7 @@
         <v>44994</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18337,7 +18337,7 @@
         <v>44881</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18394,7 +18394,7 @@
         <v>44568</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18451,7 +18451,7 @@
         <v>44330</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18508,7 +18508,7 @@
         <v>45639</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18627,7 +18627,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18684,7 +18684,7 @@
         <v>45764</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18741,7 +18741,7 @@
         <v>45764</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18798,7 +18798,7 @@
         <v>44903</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18855,7 +18855,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18917,7 +18917,7 @@
         <v>45643</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18979,7 +18979,7 @@
         <v>45770</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19036,7 +19036,7 @@
         <v>45682</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19098,7 +19098,7 @@
         <v>45672</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19155,7 +19155,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19212,7 +19212,7 @@
         <v>44127</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19274,7 +19274,7 @@
         <v>44298</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19331,7 +19331,7 @@
         <v>45752</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19388,7 +19388,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45591</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45591</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45586</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45425</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19750,7 +19750,7 @@
         <v>44248</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19807,7 +19807,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19864,7 +19864,7 @@
         <v>44657</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19921,7 +19921,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19983,7 +19983,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20040,7 +20040,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44392</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>44847</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>44489</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20330,7 +20330,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20387,7 +20387,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20444,7 +20444,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>44812</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44823</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20682,7 +20682,7 @@
         <v>45419</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20739,7 +20739,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20796,7 +20796,7 @@
         <v>45625</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20858,7 +20858,7 @@
         <v>44573</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20920,7 +20920,7 @@
         <v>45708</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20977,7 +20977,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21034,7 +21034,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21091,7 +21091,7 @@
         <v>45723</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21148,7 +21148,7 @@
         <v>45723</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45152</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21438,7 +21438,7 @@
         <v>44925</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21495,7 +21495,7 @@
         <v>45749</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21552,7 +21552,7 @@
         <v>45013</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21609,7 +21609,7 @@
         <v>44585</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21666,7 +21666,7 @@
         <v>45254</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21723,7 +21723,7 @@
         <v>45114</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21780,7 +21780,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21837,7 +21837,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21894,7 +21894,7 @@
         <v>45314</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -21951,7 +21951,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22008,7 +22008,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22070,7 +22070,7 @@
         <v>45161</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22132,7 +22132,7 @@
         <v>45774</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22194,7 +22194,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22256,7 +22256,7 @@
         <v>45589</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22318,7 +22318,7 @@
         <v>45582</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22375,7 +22375,7 @@
         <v>45091</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22432,7 +22432,7 @@
         <v>45204</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22489,7 +22489,7 @@
         <v>45687</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22546,7 +22546,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22603,7 +22603,7 @@
         <v>45603</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22660,7 +22660,7 @@
         <v>44963</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22717,7 +22717,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22774,7 +22774,7 @@
         <v>45370</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22831,7 +22831,7 @@
         <v>44441</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45505</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45769</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23007,7 +23007,7 @@
         <v>44120</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23064,7 +23064,7 @@
         <v>44120</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23121,7 +23121,7 @@
         <v>45764</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>44979</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>44391</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23297,7 +23297,7 @@
         <v>45237</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23354,7 +23354,7 @@
         <v>45345</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23411,7 +23411,7 @@
         <v>44374</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23468,7 +23468,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23525,7 +23525,7 @@
         <v>45470</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23587,7 +23587,7 @@
         <v>45338</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23644,7 +23644,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23701,7 +23701,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23758,7 +23758,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23815,7 +23815,7 @@
         <v>45653</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23872,7 +23872,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -23929,7 +23929,7 @@
         <v>44558</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -23986,7 +23986,7 @@
         <v>44529</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24043,7 +24043,7 @@
         <v>45766</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24105,7 +24105,7 @@
         <v>45453</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24162,7 +24162,7 @@
         <v>45574</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24224,7 +24224,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24281,7 +24281,7 @@
         <v>44164</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24343,7 +24343,7 @@
         <v>45478</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24400,7 +24400,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24457,7 +24457,7 @@
         <v>44386</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24514,7 +24514,7 @@
         <v>45226</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24576,7 +24576,7 @@
         <v>45764</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24633,7 +24633,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24690,7 +24690,7 @@
         <v>44529</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24747,7 +24747,7 @@
         <v>44529</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24804,7 +24804,7 @@
         <v>45600</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24861,7 +24861,7 @@
         <v>44211</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -24918,7 +24918,7 @@
         <v>44067</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -24975,7 +24975,7 @@
         <v>45778</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25037,7 +25037,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25094,7 +25094,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25151,7 +25151,7 @@
         <v>44970</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25208,7 +25208,7 @@
         <v>45232</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25270,7 +25270,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25327,7 +25327,7 @@
         <v>45596</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25384,7 +25384,7 @@
         <v>45285</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25441,7 +25441,7 @@
         <v>44642</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25498,7 +25498,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25560,7 +25560,7 @@
         <v>45077</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25617,7 +25617,7 @@
         <v>44910</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25679,7 +25679,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25736,7 +25736,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25793,7 +25793,7 @@
         <v>45254</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25850,7 +25850,7 @@
         <v>45553</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -25912,7 +25912,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -25974,7 +25974,7 @@
         <v>45397</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26031,7 +26031,7 @@
         <v>45397</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26088,7 +26088,7 @@
         <v>44796</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26145,7 +26145,7 @@
         <v>45764</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26202,7 +26202,7 @@
         <v>45448</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26264,7 +26264,7 @@
         <v>45149</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26321,7 +26321,7 @@
         <v>45232</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26378,7 +26378,7 @@
         <v>45232</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26435,7 +26435,7 @@
         <v>44983</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26492,7 +26492,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26554,7 +26554,7 @@
         <v>45786</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26616,7 +26616,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26678,7 +26678,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26735,7 +26735,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26797,7 +26797,7 @@
         <v>45149</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26854,7 +26854,7 @@
         <v>45054</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -26911,7 +26911,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -26968,7 +26968,7 @@
         <v>45429</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27025,7 +27025,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27082,7 +27082,7 @@
         <v>45758</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27139,7 +27139,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27201,7 +27201,7 @@
         <v>45085</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27258,7 +27258,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27315,7 +27315,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27377,7 +27377,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27434,7 +27434,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27496,7 +27496,7 @@
         <v>45379</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27553,7 +27553,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27615,7 +27615,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27672,7 +27672,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27729,7 +27729,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27791,7 +27791,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -27853,7 +27853,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -27915,7 +27915,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -27977,7 +27977,7 @@
         <v>45205</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28039,7 +28039,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28153,7 +28153,7 @@
         <v>45793</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28215,7 +28215,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28277,7 +28277,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28339,7 +28339,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28401,7 +28401,7 @@
         <v>45793</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28463,7 +28463,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28525,7 +28525,7 @@
         <v>44127</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28582,7 +28582,7 @@
         <v>45260</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28639,7 +28639,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28696,7 +28696,7 @@
         <v>45639</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28753,7 +28753,7 @@
         <v>45583</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28815,7 +28815,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -28877,7 +28877,7 @@
         <v>44484</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -28939,7 +28939,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -28996,7 +28996,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29053,7 +29053,7 @@
         <v>45761</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29115,7 +29115,7 @@
         <v>45264</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45264</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29239,7 +29239,7 @@
         <v>45590</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29296,7 +29296,7 @@
         <v>45590</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29353,7 +29353,7 @@
         <v>44077</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29415,7 +29415,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29477,7 +29477,7 @@
         <v>45210</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29539,7 +29539,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29596,7 +29596,7 @@
         <v>44833</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29653,7 +29653,7 @@
         <v>45516</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29715,7 +29715,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29777,7 +29777,7 @@
         <v>45797</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -29901,7 +29901,7 @@
         <v>44524</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -29958,7 +29958,7 @@
         <v>44935</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30015,7 +30015,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30077,7 +30077,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30139,7 +30139,7 @@
         <v>44445</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30196,7 +30196,7 @@
         <v>44529</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30253,7 +30253,7 @@
         <v>45212</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30315,7 +30315,7 @@
         <v>45589</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30377,7 +30377,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30434,7 +30434,7 @@
         <v>45659</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30491,7 +30491,7 @@
         <v>44706</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30548,7 +30548,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30605,7 +30605,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30662,7 +30662,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30724,7 +30724,7 @@
         <v>44747</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30781,7 +30781,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30843,7 +30843,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -30905,7 +30905,7 @@
         <v>44673</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -30962,7 +30962,7 @@
         <v>45246</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31019,7 +31019,7 @@
         <v>45448</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31081,7 +31081,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>44333</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45798</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31319,7 +31319,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31376,7 +31376,7 @@
         <v>44657</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31433,7 +31433,7 @@
         <v>44657</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31490,7 +31490,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31552,7 +31552,7 @@
         <v>45244</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45155</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31738,7 +31738,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31795,7 +31795,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -31857,7 +31857,7 @@
         <v>45748</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -31914,7 +31914,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -31976,7 +31976,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32038,7 +32038,7 @@
         <v>45803</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32095,7 +32095,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32157,7 +32157,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32219,7 +32219,7 @@
         <v>45803</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32276,7 +32276,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32338,7 +32338,7 @@
         <v>44110</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32395,7 +32395,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32457,7 +32457,7 @@
         <v>45645</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45608</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45608</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>45608</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>45590</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45804</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>45110</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -32980,7 +32980,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33037,7 +33037,7 @@
         <v>45301</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33094,7 +33094,7 @@
         <v>45593</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33156,7 +33156,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33213,7 +33213,7 @@
         <v>45429</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33270,7 +33270,7 @@
         <v>45464</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33332,7 +33332,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33389,7 +33389,7 @@
         <v>45646</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33446,7 +33446,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33503,7 +33503,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33560,7 +33560,7 @@
         <v>45456</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33617,7 +33617,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33674,7 +33674,7 @@
         <v>44648</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33736,7 +33736,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33793,7 +33793,7 @@
         <v>45232</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -33855,7 +33855,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -33912,7 +33912,7 @@
         <v>45546</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -33974,7 +33974,7 @@
         <v>45672</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34031,7 +34031,7 @@
         <v>45764</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34088,7 +34088,7 @@
         <v>45429</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34145,7 +34145,7 @@
         <v>45429</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34202,7 +34202,7 @@
         <v>45085</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34259,7 +34259,7 @@
         <v>44900</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34321,7 +34321,7 @@
         <v>45254</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34378,7 +34378,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34435,7 +34435,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34492,7 +34492,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34549,7 +34549,7 @@
         <v>45483</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34606,7 +34606,7 @@
         <v>45561.58791666666</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34668,7 +34668,7 @@
         <v>45153</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34725,7 +34725,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34782,7 +34782,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -34839,7 +34839,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -34896,7 +34896,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -34953,7 +34953,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45813</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35077,7 +35077,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35139,7 +35139,7 @@
         <v>45813</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35201,7 +35201,7 @@
         <v>45414</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35258,7 +35258,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35315,7 +35315,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35377,7 +35377,7 @@
         <v>45256</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35434,7 +35434,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35496,7 +35496,7 @@
         <v>45562</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45653.46922453704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>45387</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -35905,7 +35905,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -35962,7 +35962,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36019,7 +36019,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36076,7 +36076,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36133,7 +36133,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36190,7 +36190,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36252,7 +36252,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36314,7 +36314,7 @@
         <v>45483</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36371,7 +36371,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
         <v>44490</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36490,7 +36490,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36547,7 +36547,7 @@
         <v>44143</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36604,7 +36604,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36666,7 +36666,7 @@
         <v>45156</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36723,7 +36723,7 @@
         <v>44755</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36785,7 +36785,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36847,7 +36847,7 @@
         <v>45446</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -36904,7 +36904,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -36961,7 +36961,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37018,7 +37018,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37075,7 +37075,7 @@
         <v>44628</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37132,7 +37132,7 @@
         <v>45110</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37194,7 +37194,7 @@
         <v>45161</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37256,7 +37256,7 @@
         <v>45161</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37318,7 +37318,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37380,7 +37380,7 @@
         <v>44642</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37442,7 +37442,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37499,7 +37499,7 @@
         <v>45070</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37556,7 +37556,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37618,7 +37618,7 @@
         <v>44901</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37675,7 +37675,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37732,7 +37732,7 @@
         <v>45246</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37789,7 +37789,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37851,7 +37851,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -37908,7 +37908,7 @@
         <v>45818</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -37970,7 +37970,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38027,7 +38027,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38089,7 +38089,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38151,7 +38151,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38213,7 +38213,7 @@
         <v>45818</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38275,7 +38275,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38357,7 +38357,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38414,7 +38414,7 @@
         <v>45356</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38471,7 +38471,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38533,7 +38533,7 @@
         <v>44299</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38590,7 +38590,7 @@
         <v>45358</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38647,7 +38647,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38709,7 +38709,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38771,7 +38771,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38833,7 +38833,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38890,7 +38890,7 @@
         <v>45300</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -38947,7 +38947,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39004,7 +39004,7 @@
         <v>45824</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39061,7 +39061,7 @@
         <v>45316</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39118,7 +39118,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39175,7 +39175,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39232,7 +39232,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39289,7 +39289,7 @@
         <v>45649</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39346,7 +39346,7 @@
         <v>45824</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39403,7 +39403,7 @@
         <v>45770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39460,7 +39460,7 @@
         <v>45625</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39517,7 +39517,7 @@
         <v>44529</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39574,7 +39574,7 @@
         <v>45824</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39631,7 +39631,7 @@
         <v>45589</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39693,7 +39693,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39755,7 +39755,7 @@
         <v>45589</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39817,7 +39817,7 @@
         <v>45827</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39879,7 +39879,7 @@
         <v>45827</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -39941,7 +39941,7 @@
         <v>44648</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40003,7 +40003,7 @@
         <v>45152</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40060,7 +40060,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40117,7 +40117,7 @@
         <v>45212</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40174,7 +40174,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40236,7 +40236,7 @@
         <v>45827</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40298,7 +40298,7 @@
         <v>45460</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40360,7 +40360,7 @@
         <v>45826</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40422,7 +40422,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40484,7 +40484,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40541,7 +40541,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40598,7 +40598,7 @@
         <v>45831</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40655,7 +40655,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40717,7 +40717,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40774,7 +40774,7 @@
         <v>45350</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40831,7 +40831,7 @@
         <v>44474</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40888,7 +40888,7 @@
         <v>44566</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -40945,7 +40945,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41069,7 +41069,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41126,7 +41126,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41183,7 +41183,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41240,7 +41240,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41302,7 +41302,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41364,7 +41364,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41426,7 +41426,7 @@
         <v>44908</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41483,7 +41483,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41545,7 +41545,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41607,7 +41607,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41669,7 +41669,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45216</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41793,7 +41793,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41850,7 +41850,7 @@
         <v>44477</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41907,7 +41907,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -41964,7 +41964,7 @@
         <v>45833</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42021,7 +42021,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42078,7 +42078,7 @@
         <v>44566</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42135,7 +42135,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42192,7 +42192,7 @@
         <v>45132</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42249,7 +42249,7 @@
         <v>45874</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42326,7 +42326,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42383,7 +42383,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42445,7 +42445,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42507,7 +42507,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42564,7 +42564,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42626,7 +42626,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42683,7 +42683,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42745,7 +42745,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42807,7 +42807,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42864,7 +42864,7 @@
         <v>45770</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42921,7 +42921,7 @@
         <v>45870</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -42983,7 +42983,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43045,7 +43045,7 @@
         <v>45356</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43102,7 +43102,7 @@
         <v>45704</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43159,7 +43159,7 @@
         <v>45114</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43216,7 +43216,7 @@
         <v>45323</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43273,7 +43273,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43330,7 +43330,7 @@
         <v>44438</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43387,7 +43387,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43444,7 +43444,7 @@
         <v>45099</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43501,7 +43501,7 @@
         <v>44124</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43558,7 +43558,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43615,7 +43615,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43672,7 +43672,7 @@
         <v>44994</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43729,7 +43729,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43786,7 +43786,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43848,7 +43848,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43905,7 +43905,7 @@
         <v>45068</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -43962,7 +43962,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44019,7 +44019,7 @@
         <v>45834</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44076,7 +44076,7 @@
         <v>44795</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44133,7 +44133,7 @@
         <v>45874</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44195,7 +44195,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44257,7 +44257,7 @@
         <v>45803</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44314,7 +44314,7 @@
         <v>44445</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44371,7 +44371,7 @@
         <v>45341</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44433,7 +44433,7 @@
         <v>45161</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44490,7 +44490,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44552,7 +44552,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44609,7 +44609,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44666,7 +44666,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44723,7 +44723,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44780,7 +44780,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44837,7 +44837,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44894,7 +44894,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -44951,7 +44951,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45008,7 +45008,7 @@
         <v>45840</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45065,7 +45065,7 @@
         <v>45686.42519675926</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45122,7 +45122,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45184,7 +45184,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45241,7 +45241,7 @@
         <v>45747.56875</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45298,7 +45298,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45355,7 +45355,7 @@
         <v>45875</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45412,7 +45412,7 @@
         <v>45840</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45474,7 +45474,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45531,7 +45531,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45588,7 +45588,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45645,7 +45645,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45702,7 +45702,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45759,7 +45759,7 @@
         <v>45596</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45816,7 +45816,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45873,7 +45873,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -45930,7 +45930,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -45992,7 +45992,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46049,7 +46049,7 @@
         <v>45882</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46106,7 +46106,7 @@
         <v>45840</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46168,7 +46168,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46349,7 +46349,7 @@
         <v>44908</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46406,7 +46406,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46463,7 +46463,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46520,7 +46520,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46577,7 +46577,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46639,7 +46639,7 @@
         <v>45456</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46696,7 +46696,7 @@
         <v>45772</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46753,7 +46753,7 @@
         <v>45645</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46815,7 +46815,7 @@
         <v>44151</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -46877,7 +46877,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -46939,7 +46939,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47001,7 +47001,7 @@
         <v>45685</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47058,7 +47058,7 @@
         <v>45187</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>44378</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>44887</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47239,7 +47239,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47301,7 +47301,7 @@
         <v>45868</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47363,7 +47363,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47425,7 +47425,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47487,7 +47487,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47549,7 +47549,7 @@
         <v>45653</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47606,7 +47606,7 @@
         <v>44110</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>45351</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>44994</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -47901,7 +47901,7 @@
         <v>45884</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45887</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48025,7 +48025,7 @@
         <v>45323</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48082,7 +48082,7 @@
         <v>45685</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48139,7 +48139,7 @@
         <v>44931</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48196,7 +48196,7 @@
         <v>45882</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48253,7 +48253,7 @@
         <v>45882</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48310,7 +48310,7 @@
         <v>45001</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48367,7 +48367,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45887</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48486,7 +48486,7 @@
         <v>45732</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48543,7 +48543,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48600,7 +48600,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48657,7 +48657,7 @@
         <v>45891.51008101852</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48719,7 +48719,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48776,7 +48776,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48838,7 +48838,7 @@
         <v>45890.61597222222</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48900,7 +48900,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -48957,7 +48957,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49014,7 +49014,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49076,7 +49076,7 @@
         <v>44110</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49133,7 +49133,7 @@
         <v>44889</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49190,7 +49190,7 @@
         <v>45632</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49247,7 +49247,7 @@
         <v>45406</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49304,7 +49304,7 @@
         <v>44735</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49366,7 +49366,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49423,7 +49423,7 @@
         <v>45105</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49485,7 +49485,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49547,7 +49547,7 @@
         <v>45035</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49604,7 +49604,7 @@
         <v>44356</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49661,7 +49661,7 @@
         <v>45152</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49718,7 +49718,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49775,7 +49775,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49837,7 +49837,7 @@
         <v>44883</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49899,7 +49899,7 @@
         <v>45771</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -49956,7 +49956,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50013,7 +50013,7 @@
         <v>45587</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50070,7 +50070,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50127,7 +50127,7 @@
         <v>45099</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50184,7 +50184,7 @@
         <v>44484</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50241,7 +50241,7 @@
         <v>45561</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50298,7 +50298,7 @@
         <v>44573</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50360,7 +50360,7 @@
         <v>45454</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50417,7 +50417,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50474,7 +50474,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50531,7 +50531,7 @@
         <v>45079</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50588,7 +50588,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50650,7 +50650,7 @@
         <v>44648</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50712,7 +50712,7 @@
         <v>45762</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50769,7 +50769,7 @@
         <v>44565</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50826,7 +50826,7 @@
         <v>44216</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50883,7 +50883,7 @@
         <v>45642</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -50940,7 +50940,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51002,7 +51002,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51059,7 +51059,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51116,7 +51116,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>44124</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45212</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45771</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44904</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45893</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44130</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44322</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44166</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44804</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44082</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44489</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45341</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44678</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45714</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45301</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45842</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45559</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>45701</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45526</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>45137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44830</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45072</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44796</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44365</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45611</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45645</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45803.67</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>45205</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45513</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45594</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44692</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45773</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45586</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44217</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44207</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44075</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44509</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44677</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44215</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44274</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44577</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44350</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44090</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44217</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44671</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44120</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44216</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44313</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44350</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44809</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44165</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44187</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44168</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44274</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44286</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44617</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44648</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44439</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44464</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44865</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44204</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44609</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44223</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44110</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>44158</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44671</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44182</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44125</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44313</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44721</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44358</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44151</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44796</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44174</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44722</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44484</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44182</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44438</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44217</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44530</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44238</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44313</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44099</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44414</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44565</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44648</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44480</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44566</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44473</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44182</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44617</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44596</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44529</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44182</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44648</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44734</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44293</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44356</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44248</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44489</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44565</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44116</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44439</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44356</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44566</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44566</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44635</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44299</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44671</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44274</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45105</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45068</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44489</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44833</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45672</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45771</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44908</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45358</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45099</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45356</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45708</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45764</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45764</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45397</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45397</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45642</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45387</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45778</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45301</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45254</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45110</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45370</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45429</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44477</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45155</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44558</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45574</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44333</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44077</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44529</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44883</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45786</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45149</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>44441</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>44378</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45156</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>44983</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45419</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45152</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45379</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44735</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45591</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44609</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44391</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44374</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45161</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45161</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45758</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45793</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45590</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45590</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45793</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45761</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44127</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45589</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45553</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44795</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45798</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45797</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45483</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45216</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45596</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>44120</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>44566</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45645</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>44573</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45643</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45774</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>44908</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45803</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45429</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45429</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45448</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45804</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45590</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44994</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45608</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45608</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44110</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45478</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45608</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44648</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45205</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45204</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>44110</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44151</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>44889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44901</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44529</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>44529</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45411</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45646</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45546</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45464</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45682</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44628</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45429</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45518</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45813</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>44881</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45583</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>45813</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45212</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45750</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45687</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45132</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45013</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45446</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45770</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45818</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45818</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45653</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45653</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45226</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45674</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45232</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45824</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44445</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45824</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45824</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45826</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45685</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45505</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45639</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45827</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45827</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44642</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>44490</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45054</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45448</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>44963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45460</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45874</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45831</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45764</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45152</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45237</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45764</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44657</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44657</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45833</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44994</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44673</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45562</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45764</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>44755</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45589</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45589</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45161</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44164</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45834</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45301</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45870</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45803</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45874</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45840</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>45625</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45246</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45414</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45840</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45762</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45314</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45256</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44484</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44903</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45254</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45882</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45645</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45770</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45875</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45212</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45840</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44648</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45264</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45882</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45882</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45884</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45868</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45161</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45323</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45456</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45887</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44994</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45356</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>44474</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45887</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45300</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45114</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45890.61597222222</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45260</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44796</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>44573</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45345</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45483</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>45894.64185185185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45893.46916666667</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45285</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45894.51857638889</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45891.51008101852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>45803</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>45894.36493055556</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45893</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45603</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45085</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45323</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45153</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>44970</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45895.345</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45895.44861111111</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45149</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45897.48153935185</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45894</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45897.48422453704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45582</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45589</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44356</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44823</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44568</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44648</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>44386</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44143</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44124</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45764</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>44292</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>44445</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45672</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44747</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>44706</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>44423</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45752</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>44979</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44931</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45748</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44524</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45761</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>45110</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44642</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>44216</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45586</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45769</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>44900</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45187</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>45600</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45591</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>44925</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45772</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>44378</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>44298</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>45210</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>45091</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>44110</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>44887</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44565</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>45085</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45861,7 +45861,7 @@
         <v>45001</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>44438</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>44529</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>44248</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45077</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44585</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>44812</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45079</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>44847</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>44127</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45338</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>44910</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44392</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45316</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44552</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45232</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45470</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45587</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45769</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45406</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45561</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45114</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44566</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45685</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45246</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48181,7 +48181,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>45762</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45453</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45639</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45770</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45454</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45425</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45625</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45646</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45766</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45649</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>44529</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>44657</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45264</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44330</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45350</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45379</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>44484</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45659</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45596</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45723</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45723</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45749</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>45035</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45341</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>44833</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45152</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>44935</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51299,7 +51299,7 @@
         <v>45244</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45351</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>45732</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>44124</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45212</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45771</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3380,7 +3380,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44904</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3747,7 +3747,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3838,7 +3838,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45893</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>44130</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4122,7 +4122,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44322</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44166</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44804</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44082</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4754,7 +4754,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4845,7 +4845,7 @@
         <v>44489</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45341</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>44678</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45714</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45517</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
         <v>45301</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45842</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45559</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5567,7 +5567,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5662,7 +5662,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5757,7 +5757,7 @@
         <v>45701</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5843,7 +5843,7 @@
         <v>45526</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6020,7 +6020,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6111,7 +6111,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>45137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44830</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
         <v>45072</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44796</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>44421</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44365</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45446</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45611</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7473,7 +7473,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7563,7 +7563,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7652,7 +7652,7 @@
         <v>45645</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7742,7 +7742,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7832,7 +7832,7 @@
         <v>45803.67</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7922,7 +7922,7 @@
         <v>45205</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8016,7 +8016,7 @@
         <v>45513</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45594</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8281,7 +8281,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
         <v>44692</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8645,7 +8645,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45773</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45586</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9085,7 +9085,7 @@
         <v>45538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9175,7 +9175,7 @@
         <v>44217</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9232,7 +9232,7 @@
         <v>44207</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9289,7 +9289,7 @@
         <v>44075</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9346,7 +9346,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9403,7 +9403,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9460,7 +9460,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9517,7 +9517,7 @@
         <v>44509</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9574,7 +9574,7 @@
         <v>44677</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9631,7 +9631,7 @@
         <v>44215</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9688,7 +9688,7 @@
         <v>44274</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9745,7 +9745,7 @@
         <v>44577</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9802,7 +9802,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9859,7 +9859,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9916,7 +9916,7 @@
         <v>44350</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9973,7 +9973,7 @@
         <v>44090</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10030,7 +10030,7 @@
         <v>44217</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10087,7 +10087,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10149,7 +10149,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10206,7 +10206,7 @@
         <v>44671</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10263,7 +10263,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44852</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10387,7 +10387,7 @@
         <v>44120</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10444,7 +10444,7 @@
         <v>44216</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10501,7 +10501,7 @@
         <v>44313</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10558,7 +10558,7 @@
         <v>44350</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10615,7 +10615,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10677,7 +10677,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10734,7 +10734,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10791,7 +10791,7 @@
         <v>44809</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10853,7 +10853,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10910,7 +10910,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10967,7 +10967,7 @@
         <v>44815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11029,7 +11029,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11091,7 +11091,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11153,7 +11153,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11210,7 +11210,7 @@
         <v>44165</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11267,7 +11267,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11324,7 +11324,7 @@
         <v>44187</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11381,7 +11381,7 @@
         <v>44168</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11438,7 +11438,7 @@
         <v>44274</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11495,7 +11495,7 @@
         <v>44286</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11552,7 +11552,7 @@
         <v>44617</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11609,7 +11609,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11666,7 +11666,7 @@
         <v>44648</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11728,7 +11728,7 @@
         <v>44439</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11785,7 +11785,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>44464</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11904,7 +11904,7 @@
         <v>44865</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11966,7 +11966,7 @@
         <v>44204</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>44609</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12080,7 +12080,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12137,7 +12137,7 @@
         <v>44223</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12194,7 +12194,7 @@
         <v>44110</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12256,7 +12256,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12313,7 +12313,7 @@
         <v>44158</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12370,7 +12370,7 @@
         <v>44671</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>44182</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12484,7 +12484,7 @@
         <v>44125</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12546,7 +12546,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12603,7 +12603,7 @@
         <v>44313</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12660,7 +12660,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12722,7 +12722,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12779,7 +12779,7 @@
         <v>44721</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12836,7 +12836,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12893,7 +12893,7 @@
         <v>44358</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12950,7 +12950,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13012,7 +13012,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13074,7 +13074,7 @@
         <v>44151</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13136,7 +13136,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13193,7 +13193,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13250,7 +13250,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13307,7 +13307,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13364,7 +13364,7 @@
         <v>44749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13421,7 +13421,7 @@
         <v>44796</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13478,7 +13478,7 @@
         <v>44796</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13535,7 +13535,7 @@
         <v>44174</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13597,7 +13597,7 @@
         <v>44722</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13654,7 +13654,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13711,7 +13711,7 @@
         <v>44484</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13835,7 +13835,7 @@
         <v>44182</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13892,7 +13892,7 @@
         <v>44438</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13949,7 +13949,7 @@
         <v>44217</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14063,7 +14063,7 @@
         <v>44530</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14120,7 +14120,7 @@
         <v>44238</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14177,7 +14177,7 @@
         <v>44313</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14234,7 +14234,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14296,7 +14296,7 @@
         <v>44480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14353,7 +14353,7 @@
         <v>44099</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14410,7 +14410,7 @@
         <v>44414</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14467,7 +14467,7 @@
         <v>44565</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14524,7 +14524,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>44648</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14648,7 +14648,7 @@
         <v>44480</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14705,7 +14705,7 @@
         <v>44566</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14762,7 +14762,7 @@
         <v>44473</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14824,7 +14824,7 @@
         <v>44182</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14881,7 +14881,7 @@
         <v>44617</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14938,7 +14938,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15000,7 +15000,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15057,7 +15057,7 @@
         <v>44596</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15119,7 +15119,7 @@
         <v>44529</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15176,7 +15176,7 @@
         <v>44182</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15233,7 +15233,7 @@
         <v>44648</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15295,7 +15295,7 @@
         <v>44734</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15352,7 +15352,7 @@
         <v>44293</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15414,7 +15414,7 @@
         <v>44356</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15471,7 +15471,7 @@
         <v>44248</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15528,7 +15528,7 @@
         <v>44795</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15652,7 +15652,7 @@
         <v>44489</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>44565</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>44116</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>44439</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>44356</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44566</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>44566</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16113,7 +16113,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16170,7 +16170,7 @@
         <v>44635</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16232,7 +16232,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16289,7 +16289,7 @@
         <v>44299</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16346,7 +16346,7 @@
         <v>44671</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16403,7 +16403,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16465,7 +16465,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16522,7 +16522,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16579,7 +16579,7 @@
         <v>44274</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16636,7 +16636,7 @@
         <v>45105</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16698,7 +16698,7 @@
         <v>45068</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16755,7 +16755,7 @@
         <v>44489</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16812,7 +16812,7 @@
         <v>44833</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16869,7 +16869,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16926,7 +16926,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16988,7 +16988,7 @@
         <v>45672</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17045,7 +17045,7 @@
         <v>45771</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17102,7 +17102,7 @@
         <v>44908</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17159,7 +17159,7 @@
         <v>45358</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17216,7 +17216,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17278,7 +17278,7 @@
         <v>45099</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17335,7 +17335,7 @@
         <v>45356</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17392,7 +17392,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17506,7 +17506,7 @@
         <v>45708</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17563,7 +17563,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17625,7 +17625,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17687,7 +17687,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17749,7 +17749,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17806,7 +17806,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17868,7 +17868,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17925,7 +17925,7 @@
         <v>45764</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17982,7 +17982,7 @@
         <v>45764</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18039,7 +18039,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18096,7 +18096,7 @@
         <v>44211</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18153,7 +18153,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18210,7 +18210,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18267,7 +18267,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18329,7 +18329,7 @@
         <v>45397</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18386,7 +18386,7 @@
         <v>45397</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18443,7 +18443,7 @@
         <v>45642</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18500,7 +18500,7 @@
         <v>45387</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18557,7 +18557,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18614,7 +18614,7 @@
         <v>45778</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18676,7 +18676,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18733,7 +18733,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18790,7 +18790,7 @@
         <v>45301</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18852,7 +18852,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18909,7 +18909,7 @@
         <v>45254</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18966,7 +18966,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19023,7 +19023,7 @@
         <v>45110</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19147,7 +19147,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19204,7 +19204,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19261,7 +19261,7 @@
         <v>45370</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19318,7 +19318,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19375,7 +19375,7 @@
         <v>45429</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19432,7 +19432,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>44477</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>45155</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19613,7 +19613,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19670,7 +19670,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19784,7 +19784,7 @@
         <v>44558</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19841,7 +19841,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19903,7 +19903,7 @@
         <v>45574</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19965,7 +19965,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20027,7 +20027,7 @@
         <v>44333</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20084,7 +20084,7 @@
         <v>44077</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20146,7 +20146,7 @@
         <v>44529</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20203,7 +20203,7 @@
         <v>44883</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20265,7 +20265,7 @@
         <v>45786</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>45149</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>44441</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>44378</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>45156</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>44983</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20674,7 +20674,7 @@
         <v>45419</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20731,7 +20731,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20793,7 +20793,7 @@
         <v>45152</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20850,7 +20850,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20912,7 +20912,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45379</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21212,7 +21212,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>44735</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21336,7 +21336,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21393,7 +21393,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21507,7 +21507,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21564,7 +21564,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21688,7 +21688,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21745,7 +21745,7 @@
         <v>45591</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21807,7 +21807,7 @@
         <v>44609</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21864,7 +21864,7 @@
         <v>45516</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21926,7 +21926,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21988,7 +21988,7 @@
         <v>44391</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22045,7 +22045,7 @@
         <v>44374</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22102,7 +22102,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22164,7 +22164,7 @@
         <v>45161</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22226,7 +22226,7 @@
         <v>45161</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22288,7 +22288,7 @@
         <v>45758</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22345,7 +22345,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22402,7 +22402,7 @@
         <v>45793</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22464,7 +22464,7 @@
         <v>45590</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>45590</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22640,7 +22640,7 @@
         <v>45793</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22702,7 +22702,7 @@
         <v>45761</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22764,7 +22764,7 @@
         <v>44127</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22826,7 +22826,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22888,7 +22888,7 @@
         <v>45589</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22950,7 +22950,7 @@
         <v>45553</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23012,7 +23012,7 @@
         <v>44795</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23069,7 +23069,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23131,7 +23131,7 @@
         <v>45798</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23193,7 +23193,7 @@
         <v>45797</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23255,7 +23255,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23317,7 +23317,7 @@
         <v>45483</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23374,7 +23374,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23431,7 +23431,7 @@
         <v>45216</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23493,7 +23493,7 @@
         <v>45596</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23550,7 +23550,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>44120</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23778,7 +23778,7 @@
         <v>44566</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23835,7 +23835,7 @@
         <v>45645</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23897,7 +23897,7 @@
         <v>44573</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24021,7 +24021,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24083,7 +24083,7 @@
         <v>45643</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24145,7 +24145,7 @@
         <v>45774</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24207,7 +24207,7 @@
         <v>44908</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24264,7 +24264,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24326,7 +24326,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24388,7 +24388,7 @@
         <v>45803</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24445,7 +24445,7 @@
         <v>45429</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>45429</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24559,7 +24559,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24616,7 +24616,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24678,7 +24678,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24735,7 +24735,7 @@
         <v>45448</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24797,7 +24797,7 @@
         <v>45804</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24854,7 +24854,7 @@
         <v>45590</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24911,7 +24911,7 @@
         <v>44994</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24968,7 +24968,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25030,7 +25030,7 @@
         <v>45608</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25087,7 +25087,7 @@
         <v>45608</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25144,7 +25144,7 @@
         <v>44110</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25201,7 +25201,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25258,7 +25258,7 @@
         <v>45478</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25315,7 +25315,7 @@
         <v>45608</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>44648</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25434,7 +25434,7 @@
         <v>45205</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25496,7 +25496,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25553,7 +25553,7 @@
         <v>45204</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25610,7 +25610,7 @@
         <v>44110</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25672,7 +25672,7 @@
         <v>44151</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25734,7 +25734,7 @@
         <v>44889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25791,7 +25791,7 @@
         <v>44901</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25848,7 +25848,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25905,7 +25905,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25962,7 +25962,7 @@
         <v>44529</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26019,7 +26019,7 @@
         <v>44529</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26076,7 +26076,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26133,7 +26133,7 @@
         <v>45411</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26190,7 +26190,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26252,7 +26252,7 @@
         <v>45646</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26309,7 +26309,7 @@
         <v>45546</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26371,7 +26371,7 @@
         <v>45464</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26433,7 +26433,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26490,7 +26490,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26547,7 +26547,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26604,7 +26604,7 @@
         <v>45682</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26666,7 +26666,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26723,7 +26723,7 @@
         <v>44628</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26780,7 +26780,7 @@
         <v>45456</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26837,7 +26837,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26894,7 +26894,7 @@
         <v>45429</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26951,7 +26951,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27008,7 +27008,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27065,7 +27065,7 @@
         <v>45518</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27184,7 +27184,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27246,7 +27246,7 @@
         <v>45813</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27308,7 +27308,7 @@
         <v>44881</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27365,7 +27365,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27427,7 +27427,7 @@
         <v>45583</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27489,7 +27489,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27551,7 +27551,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27613,7 +27613,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>45813</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27737,7 +27737,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27799,7 +27799,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27856,7 +27856,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27918,7 +27918,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27980,7 +27980,7 @@
         <v>45212</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28042,7 +28042,7 @@
         <v>45750</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28104,7 +28104,7 @@
         <v>45687</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28161,7 +28161,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28223,7 +28223,7 @@
         <v>45132</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28280,7 +28280,7 @@
         <v>45013</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28337,7 +28337,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28399,7 +28399,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28461,7 +28461,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28518,7 +28518,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28575,7 +28575,7 @@
         <v>45446</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28632,7 +28632,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45770</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28932,7 +28932,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28994,7 +28994,7 @@
         <v>45818</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29056,7 +29056,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29118,7 +29118,7 @@
         <v>45818</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29180,7 +29180,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29262,7 +29262,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29319,7 +29319,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29381,7 +29381,7 @@
         <v>45653</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45653</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29495,7 +29495,7 @@
         <v>45226</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>45674</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>45232</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45824</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44445</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45824</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30390,7 +30390,7 @@
         <v>45824</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30447,7 +30447,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30509,7 +30509,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30571,7 +30571,7 @@
         <v>45826</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30633,7 +30633,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>45685</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>45505</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>45639</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31218,7 +31218,7 @@
         <v>45704</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31275,7 +31275,7 @@
         <v>45827</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31337,7 +31337,7 @@
         <v>45827</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44642</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31523,7 +31523,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31585,7 +31585,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31642,7 +31642,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31699,7 +31699,7 @@
         <v>44490</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31761,7 +31761,7 @@
         <v>45054</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31818,7 +31818,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>45448</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31937,7 +31937,7 @@
         <v>44963</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>45460</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32056,7 +32056,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>45874</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32190,7 +32190,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32247,7 +32247,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32309,7 +32309,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32366,7 +32366,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32428,7 +32428,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32490,7 +32490,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32552,7 +32552,7 @@
         <v>45831</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32609,7 +32609,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32671,7 +32671,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32728,7 +32728,7 @@
         <v>45764</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32785,7 +32785,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32842,7 +32842,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32899,7 +32899,7 @@
         <v>45152</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32956,7 +32956,7 @@
         <v>45237</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33013,7 +33013,7 @@
         <v>45764</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33070,7 +33070,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33127,7 +33127,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33308,7 +33308,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33370,7 +33370,7 @@
         <v>44657</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44657</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>45833</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44994</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33779,7 +33779,7 @@
         <v>44673</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33836,7 +33836,7 @@
         <v>45562</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33898,7 +33898,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>45764</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34017,7 +34017,7 @@
         <v>44755</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34079,7 +34079,7 @@
         <v>45589</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34203,7 +34203,7 @@
         <v>45589</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>45161</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44164</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34384,7 +34384,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34441,7 +34441,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34503,7 +34503,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>45834</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45301</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>45870</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34736,7 +34736,7 @@
         <v>45803</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34793,7 +34793,7 @@
         <v>45874</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34855,7 +34855,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34912,7 +34912,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35217,7 +35217,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35331,7 +35331,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35388,7 +35388,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35445,7 +35445,7 @@
         <v>45840</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35502,7 +35502,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35678,7 +35678,7 @@
         <v>45625</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35740,7 +35740,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35802,7 +35802,7 @@
         <v>45246</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35859,7 +35859,7 @@
         <v>45414</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35916,7 +35916,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35973,7 +35973,7 @@
         <v>45840</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36035,7 +36035,7 @@
         <v>45762</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36092,7 +36092,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36149,7 +36149,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36211,7 +36211,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36268,7 +36268,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36330,7 +36330,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36387,7 +36387,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36444,7 +36444,7 @@
         <v>45314</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36501,7 +36501,7 @@
         <v>45256</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36558,7 +36558,7 @@
         <v>44484</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36615,7 +36615,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36677,7 +36677,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36739,7 +36739,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44903</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36853,7 +36853,7 @@
         <v>45254</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36910,7 +36910,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36967,7 +36967,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37024,7 +37024,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37081,7 +37081,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45882</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45645</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37257,7 +37257,7 @@
         <v>45770</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37314,7 +37314,7 @@
         <v>45875</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37371,7 +37371,7 @@
         <v>45212</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37428,7 +37428,7 @@
         <v>45840</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37552,7 +37552,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37609,7 +37609,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37666,7 +37666,7 @@
         <v>44648</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37728,7 +37728,7 @@
         <v>45264</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>45882</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37909,7 +37909,7 @@
         <v>45882</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45884</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45868</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38090,7 +38090,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38152,7 +38152,7 @@
         <v>45161</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38214,7 +38214,7 @@
         <v>45323</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38271,7 +38271,7 @@
         <v>45456</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38328,7 +38328,7 @@
         <v>45887</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38390,7 +38390,7 @@
         <v>44994</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38447,7 +38447,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38618,7 +38618,7 @@
         <v>45356</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38675,7 +38675,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38732,7 +38732,7 @@
         <v>44474</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38789,7 +38789,7 @@
         <v>45887</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38851,7 +38851,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39037,7 +39037,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45300</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45114</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45890.61597222222</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>45260</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39327,7 +39327,7 @@
         <v>44796</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39384,7 +39384,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39441,7 +39441,7 @@
         <v>44573</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39503,7 +39503,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39560,7 +39560,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39617,7 +39617,7 @@
         <v>45345</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39674,7 +39674,7 @@
         <v>45483</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>45894</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39793,7 +39793,7 @@
         <v>45894.64185185185</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39855,7 +39855,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39912,7 +39912,7 @@
         <v>45893.46916666667</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45285</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45894.51857638889</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45891.51008101852</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40150,7 +40150,7 @@
         <v>45803</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>45894.36493055556</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40269,7 +40269,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40326,7 +40326,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40383,7 +40383,7 @@
         <v>45893</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40445,7 +40445,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40502,7 +40502,7 @@
         <v>45603</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40559,7 +40559,7 @@
         <v>45085</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40616,7 +40616,7 @@
         <v>45323</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45153</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>44970</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45895.345</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45895.44861111111</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45149</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41201,7 +41201,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41263,7 +41263,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45897.48153935185</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>45894</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>45897.48422453704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41781,7 +41781,7 @@
         <v>45582</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41952,7 +41952,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42009,7 +42009,7 @@
         <v>45589</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42185,7 +42185,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44356</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42361,7 +42361,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44823</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44568</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>44648</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>44386</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42951,7 +42951,7 @@
         <v>44143</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43008,7 +43008,7 @@
         <v>44124</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>45764</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>44292</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43298,7 +43298,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>44445</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43417,7 +43417,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43474,7 +43474,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43531,7 +43531,7 @@
         <v>45672</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43588,7 +43588,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43645,7 +43645,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43702,7 +43702,7 @@
         <v>44747</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43759,7 +43759,7 @@
         <v>44706</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43816,7 +43816,7 @@
         <v>44423</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43873,7 +43873,7 @@
         <v>45752</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43930,7 +43930,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43987,7 +43987,7 @@
         <v>44979</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44049,7 +44049,7 @@
         <v>44931</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44106,7 +44106,7 @@
         <v>45748</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44163,7 +44163,7 @@
         <v>44524</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44220,7 +44220,7 @@
         <v>45761</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44277,7 +44277,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44339,7 +44339,7 @@
         <v>45110</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44401,7 +44401,7 @@
         <v>44642</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44458,7 +44458,7 @@
         <v>44216</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44515,7 +44515,7 @@
         <v>45586</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44577,7 +44577,7 @@
         <v>45769</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44634,7 +44634,7 @@
         <v>44900</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44696,7 +44696,7 @@
         <v>45187</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44758,7 +44758,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44815,7 +44815,7 @@
         <v>45600</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44872,7 +44872,7 @@
         <v>45591</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44934,7 +44934,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44991,7 +44991,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45048,7 +45048,7 @@
         <v>44925</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45105,7 +45105,7 @@
         <v>45772</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45162,7 +45162,7 @@
         <v>44378</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45219,7 +45219,7 @@
         <v>44298</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45276,7 +45276,7 @@
         <v>45210</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45338,7 +45338,7 @@
         <v>45091</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45395,7 +45395,7 @@
         <v>44110</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45452,7 +45452,7 @@
         <v>44887</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45514,7 +45514,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45571,7 +45571,7 @@
         <v>44565</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45628,7 +45628,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45690,7 +45690,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45747,7 +45747,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45804,7 +45804,7 @@
         <v>45085</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45861,7 +45861,7 @@
         <v>45001</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45918,7 +45918,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45975,7 +45975,7 @@
         <v>44438</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46032,7 +46032,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46094,7 +46094,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46156,7 +46156,7 @@
         <v>44529</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46213,7 +46213,7 @@
         <v>45070</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46270,7 +46270,7 @@
         <v>44248</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46327,7 +46327,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46389,7 +46389,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46446,7 +46446,7 @@
         <v>45077</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46503,7 +46503,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46560,7 +46560,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46617,7 +46617,7 @@
         <v>44585</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46674,7 +46674,7 @@
         <v>44812</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46731,7 +46731,7 @@
         <v>45079</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46788,7 +46788,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46845,7 +46845,7 @@
         <v>45593</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46907,7 +46907,7 @@
         <v>44847</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46964,7 +46964,7 @@
         <v>44127</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47021,7 +47021,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47083,7 +47083,7 @@
         <v>45338</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47140,7 +47140,7 @@
         <v>44910</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47202,7 +47202,7 @@
         <v>44392</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47259,7 +47259,7 @@
         <v>45316</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47316,7 +47316,7 @@
         <v>44552</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47373,7 +47373,7 @@
         <v>45232</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47435,7 +47435,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47492,7 +47492,7 @@
         <v>45470</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47554,7 +47554,7 @@
         <v>45587</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47611,7 +47611,7 @@
         <v>45769</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47668,7 +47668,7 @@
         <v>45406</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47725,7 +47725,7 @@
         <v>45561</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47782,7 +47782,7 @@
         <v>45114</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47839,7 +47839,7 @@
         <v>44566</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47896,7 +47896,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47953,7 +47953,7 @@
         <v>45685</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48010,7 +48010,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48067,7 +48067,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48124,7 +48124,7 @@
         <v>45246</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48181,7 +48181,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48243,7 +48243,7 @@
         <v>45762</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48300,7 +48300,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48357,7 +48357,7 @@
         <v>45453</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48414,7 +48414,7 @@
         <v>45639</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48471,7 +48471,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48528,7 +48528,7 @@
         <v>45099</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48585,7 +48585,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48642,7 +48642,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48699,7 +48699,7 @@
         <v>45770</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48756,7 +48756,7 @@
         <v>45454</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48813,7 +48813,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48870,7 +48870,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48932,7 +48932,7 @@
         <v>45425</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -48989,7 +48989,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49046,7 +49046,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>45625</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>45646</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>45766</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45649</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>44529</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49683,7 +49683,7 @@
         <v>44657</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49740,7 +49740,7 @@
         <v>45264</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>44330</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>45350</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45379</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>44484</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45659</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>45596</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45723</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45723</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45749</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>45035</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50605,7 +50605,7 @@
         <v>45341</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50667,7 +50667,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>44833</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45152</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45254</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51128,7 +51128,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51185,7 +51185,7 @@
         <v>44935</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51242,7 +51242,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51299,7 +51299,7 @@
         <v>45244</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51418,7 +51418,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51475,7 +51475,7 @@
         <v>45351</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51532,7 +51532,7 @@
         <v>45732</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1443,7 +1443,7 @@
         <v>45237</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44124</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1737,7 +1737,7 @@
         <v>45212</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1838,7 +1838,7 @@
         <v>45819</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>44889</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2032,7 +2032,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45645</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45622</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         <v>45771</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44795</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>45512</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>44869</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3190,7 +3190,7 @@
         <v>45307</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>44158</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3371,7 +3371,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
         <v>44084</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3564,7 +3564,7 @@
         <v>44082</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3656,7 +3656,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,7 +3752,7 @@
         <v>45428</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3843,7 +3843,7 @@
         <v>44904</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
         <v>45893</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4126,7 +4126,7 @@
         <v>44130</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
         <v>44322</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4395,7 +4395,7 @@
         <v>44166</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4572,7 +4572,7 @@
         <v>44082</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4663,7 +4663,7 @@
         <v>44489</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4749,7 +4749,7 @@
         <v>44165</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4840,7 +4840,7 @@
         <v>44804</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4931,7 +4931,7 @@
         <v>45341</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45714</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45137</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5299,7 +5299,7 @@
         <v>45301</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>45559</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5480,7 +5480,7 @@
         <v>45842</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45701</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5657,7 +5657,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5847,7 +5847,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5938,7 +5938,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6033,7 +6033,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6119,7 +6119,7 @@
         <v>44830</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6209,7 +6209,7 @@
         <v>45072</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6304,7 +6304,7 @@
         <v>45526</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44678</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6486,7 +6486,7 @@
         <v>44648</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6576,7 +6576,7 @@
         <v>44853</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6670,7 +6670,7 @@
         <v>44840</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6760,7 +6760,7 @@
         <v>44421</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6850,7 +6850,7 @@
         <v>44796</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6939,7 +6939,7 @@
         <v>44088</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7029,7 +7029,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7118,7 +7118,7 @@
         <v>44365</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7208,7 +7208,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7293,7 +7293,7 @@
         <v>45645</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7383,7 +7383,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7558,7 +7558,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7647,7 +7647,7 @@
         <v>45205</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45446</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7831,7 +7831,7 @@
         <v>45803.67</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8101,7 +8101,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8285,7 +8285,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45901.40067129629</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8550,7 +8550,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8640,7 +8640,7 @@
         <v>45611</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44692</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8820,7 +8820,7 @@
         <v>45594</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
         <v>45586</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>45773</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>45538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9180,7 +9180,7 @@
         <v>45513</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9265,7 +9265,7 @@
         <v>44217</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9322,7 +9322,7 @@
         <v>44207</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9379,7 +9379,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9436,7 +9436,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9493,7 +9493,7 @@
         <v>44158</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9550,7 +9550,7 @@
         <v>44509</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9607,7 +9607,7 @@
         <v>44677</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9664,7 +9664,7 @@
         <v>44215</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
         <v>44274</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9778,7 +9778,7 @@
         <v>44577</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9835,7 +9835,7 @@
         <v>44414</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9892,7 +9892,7 @@
         <v>44414</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9949,7 +9949,7 @@
         <v>44350</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10006,7 +10006,7 @@
         <v>44217</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10063,7 +10063,7 @@
         <v>44090</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10182,7 +10182,7 @@
         <v>44671</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>44120</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10477,7 +10477,7 @@
         <v>44216</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10534,7 +10534,7 @@
         <v>44313</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10591,7 +10591,7 @@
         <v>44350</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10648,7 +10648,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10710,7 +10710,7 @@
         <v>44414</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10767,7 +10767,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10824,7 +10824,7 @@
         <v>44809</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>44414</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11000,7 +11000,7 @@
         <v>44815</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44648</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44138</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11186,7 +11186,7 @@
         <v>44130</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11243,7 +11243,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11300,7 +11300,7 @@
         <v>44165</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11357,7 +11357,7 @@
         <v>44187</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11414,7 +11414,7 @@
         <v>44168</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11471,7 +11471,7 @@
         <v>44274</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>44286</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11585,7 +11585,7 @@
         <v>44617</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44274</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44648</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44439</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44284</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11880,7 +11880,7 @@
         <v>44464</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44865</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11999,7 +11999,7 @@
         <v>44204</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12056,7 +12056,7 @@
         <v>44609</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12113,7 +12113,7 @@
         <v>44609</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12170,7 +12170,7 @@
         <v>44223</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12227,7 +12227,7 @@
         <v>44110</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>44158</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12346,7 +12346,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44671</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44182</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44125</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12579,7 +12579,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12636,7 +12636,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12693,7 +12693,7 @@
         <v>44151</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12755,7 +12755,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44721</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12936,7 +12936,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12998,7 +12998,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13055,7 +13055,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13112,7 +13112,7 @@
         <v>44313</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13169,7 +13169,7 @@
         <v>44313</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13226,7 +13226,7 @@
         <v>44378</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13283,7 +13283,7 @@
         <v>44358</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44174</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13402,7 +13402,7 @@
         <v>44749</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13459,7 +13459,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44796</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44796</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13630,7 +13630,7 @@
         <v>44722</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13687,7 +13687,7 @@
         <v>44484</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44182</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13868,7 +13868,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13925,7 +13925,7 @@
         <v>44438</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13982,7 +13982,7 @@
         <v>44217</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14039,7 +14039,7 @@
         <v>44530</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14096,7 +14096,7 @@
         <v>44480</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14153,7 +14153,7 @@
         <v>44648</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44099</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>44414</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>44473</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44565</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14510,7 +14510,7 @@
         <v>44182</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14567,7 +14567,7 @@
         <v>44238</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14624,7 +14624,7 @@
         <v>44313</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14743,7 +14743,7 @@
         <v>44566</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>44617</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14919,7 +14919,7 @@
         <v>44480</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>44596</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44182</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44529</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15209,7 +15209,7 @@
         <v>44293</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44356</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15390,7 +15390,7 @@
         <v>44795</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15452,7 +15452,7 @@
         <v>44489</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
         <v>44565</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15566,7 +15566,7 @@
         <v>44439</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15623,7 +15623,7 @@
         <v>44648</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15685,7 +15685,7 @@
         <v>44734</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15742,7 +15742,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15799,7 +15799,7 @@
         <v>44248</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15856,7 +15856,7 @@
         <v>44356</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>44635</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44671</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44116</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45643</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>44566</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44566</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16327,7 +16327,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16384,7 +16384,7 @@
         <v>45682</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16446,7 +16446,7 @@
         <v>44274</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16503,7 +16503,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16565,7 +16565,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16622,7 +16622,7 @@
         <v>44298</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16679,7 +16679,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16741,7 +16741,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16798,7 +16798,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16855,7 +16855,7 @@
         <v>44423</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16912,7 +16912,7 @@
         <v>45411</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16969,7 +16969,7 @@
         <v>44833</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17026,7 +17026,7 @@
         <v>45518</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17083,7 +17083,7 @@
         <v>45091</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44963</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>44552</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>45370</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>44441</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>44313</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17482,7 +17482,7 @@
         <v>44248</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17539,7 +17539,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17596,7 +17596,7 @@
         <v>45505</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17658,7 +17658,7 @@
         <v>45769</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17715,7 +17715,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17772,7 +17772,7 @@
         <v>45338</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17829,7 +17829,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>44979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17953,7 +17953,7 @@
         <v>45453</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18010,7 +18010,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18067,7 +18067,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45478</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18300,7 +18300,7 @@
         <v>44374</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>44392</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18414,7 +18414,7 @@
         <v>45778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45470</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>44489</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45783.29137731482</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18880,7 +18880,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18937,7 +18937,7 @@
         <v>45419</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18994,7 +18994,7 @@
         <v>45653</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19051,7 +19051,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19108,7 +19108,7 @@
         <v>45254</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19165,7 +19165,7 @@
         <v>45114</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19222,7 +19222,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19279,7 +19279,7 @@
         <v>44529</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19336,7 +19336,7 @@
         <v>45762</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19393,7 +19393,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19450,7 +19450,7 @@
         <v>45161</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19512,7 +19512,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19574,7 +19574,7 @@
         <v>45589</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19636,7 +19636,7 @@
         <v>45582</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19693,7 +19693,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19755,7 +19755,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19812,7 +19812,7 @@
         <v>45574</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19874,7 +19874,7 @@
         <v>44609</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19931,7 +19931,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19988,7 +19988,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20045,7 +20045,7 @@
         <v>45764</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20102,7 +20102,7 @@
         <v>45600</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20159,7 +20159,7 @@
         <v>44211</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20216,7 +20216,7 @@
         <v>45149</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20273,7 +20273,7 @@
         <v>45786</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20335,7 +20335,7 @@
         <v>45237</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20392,7 +20392,7 @@
         <v>44881</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20449,7 +20449,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20506,7 +20506,7 @@
         <v>45345</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20563,7 +20563,7 @@
         <v>44330</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20620,7 +20620,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20677,7 +20677,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20734,7 +20734,7 @@
         <v>45596</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20791,7 +20791,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20848,7 +20848,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20910,7 +20910,7 @@
         <v>44642</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20967,7 +20967,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21029,7 +21029,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21086,7 +21086,7 @@
         <v>44558</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21143,7 +21143,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21205,7 +21205,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21267,7 +21267,7 @@
         <v>45379</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21324,7 +21324,7 @@
         <v>45077</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21381,7 +21381,7 @@
         <v>45766</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21443,7 +21443,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21500,7 +21500,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21562,7 +21562,7 @@
         <v>45254</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21619,7 +21619,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21681,7 +21681,7 @@
         <v>44164</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21743,7 +21743,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21805,7 +21805,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21862,7 +21862,7 @@
         <v>44796</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21919,7 +21919,7 @@
         <v>44386</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21976,7 +21976,7 @@
         <v>45226</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22038,7 +22038,7 @@
         <v>45793</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22100,7 +22100,7 @@
         <v>45448</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22162,7 +22162,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22224,7 +22224,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22286,7 +22286,7 @@
         <v>44529</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22343,7 +22343,7 @@
         <v>44529</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22400,7 +22400,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22462,7 +22462,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22524,7 +22524,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22581,7 +22581,7 @@
         <v>45793</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22643,7 +22643,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22705,7 +22705,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22767,7 +22767,7 @@
         <v>45149</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22824,7 +22824,7 @@
         <v>45054</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22881,7 +22881,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22938,7 +22938,7 @@
         <v>45429</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22995,7 +22995,7 @@
         <v>45590</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23052,7 +23052,7 @@
         <v>45590</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23109,7 +23109,7 @@
         <v>45085</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23166,7 +23166,7 @@
         <v>44970</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23223,7 +23223,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23280,7 +23280,7 @@
         <v>45232</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23342,7 +23342,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23399,7 +23399,7 @@
         <v>45285</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23456,7 +23456,7 @@
         <v>45797</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23518,7 +23518,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23580,7 +23580,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23642,7 +23642,7 @@
         <v>45205</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23704,7 +23704,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23766,7 +23766,7 @@
         <v>44910</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23828,7 +23828,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23890,7 +23890,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23952,7 +23952,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24009,7 +24009,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24071,7 +24071,7 @@
         <v>45397</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24128,7 +24128,7 @@
         <v>45397</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24185,7 +24185,7 @@
         <v>45764</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24242,7 +24242,7 @@
         <v>45639</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24299,7 +24299,7 @@
         <v>45583</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24361,7 +24361,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24423,7 +24423,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24485,7 +24485,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24542,7 +24542,7 @@
         <v>45798</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24604,7 +24604,7 @@
         <v>44983</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24661,7 +24661,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24718,7 +24718,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24780,7 +24780,7 @@
         <v>45210</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24842,7 +24842,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24899,7 +24899,7 @@
         <v>44833</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24956,7 +24956,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25013,7 +25013,7 @@
         <v>45758</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25070,7 +25070,7 @@
         <v>45803</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25127,7 +25127,7 @@
         <v>44524</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25184,7 +25184,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25246,7 +25246,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25308,7 +25308,7 @@
         <v>44445</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25365,7 +25365,7 @@
         <v>45212</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25427,7 +25427,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>44706</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>44747</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>44673</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>44127</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45608</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45608</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>45260</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45608</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44484</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45590</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>44333</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45264</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26644,7 +26644,7 @@
         <v>45264</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44657</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44657</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26820,7 +26820,7 @@
         <v>45804</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26877,7 +26877,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26934,7 +26934,7 @@
         <v>45155</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26996,7 +26996,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27058,7 +27058,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27120,7 +27120,7 @@
         <v>45516</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27182,7 +27182,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27301,7 +27301,7 @@
         <v>45429</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27358,7 +27358,7 @@
         <v>45464</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27420,7 +27420,7 @@
         <v>44935</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27477,7 +27477,7 @@
         <v>44529</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27534,7 +27534,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27596,7 +27596,7 @@
         <v>44110</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27653,7 +27653,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27710,7 +27710,7 @@
         <v>45645</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27772,7 +27772,7 @@
         <v>45589</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>45546</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28124,7 +28124,7 @@
         <v>45301</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45593</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28243,7 +28243,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28300,7 +28300,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28357,7 +28357,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28419,7 +28419,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28476,7 +28476,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28538,7 +28538,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28595,7 +28595,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28657,7 +28657,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28719,7 +28719,7 @@
         <v>45813</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45813</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45246</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29024,7 +29024,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29086,7 +29086,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29143,7 +29143,7 @@
         <v>45429</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29200,7 +29200,7 @@
         <v>45429</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29257,7 +29257,7 @@
         <v>45085</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29314,7 +29314,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29376,7 +29376,7 @@
         <v>44900</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29438,7 +29438,7 @@
         <v>45448</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29562,7 +29562,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29624,7 +29624,7 @@
         <v>45446</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29681,7 +29681,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>45483</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>45244</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29981,7 +29981,7 @@
         <v>45153</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30095,7 +30095,7 @@
         <v>45818</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30281,7 +30281,7 @@
         <v>45818</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30343,7 +30343,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30425,7 +30425,7 @@
         <v>45748</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30482,7 +30482,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30539,7 +30539,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30601,7 +30601,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30663,7 +30663,7 @@
         <v>45414</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30720,7 +30720,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30777,7 +30777,7 @@
         <v>45256</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30834,7 +30834,7 @@
         <v>45562</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30896,7 +30896,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30953,7 +30953,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31010,7 +31010,7 @@
         <v>45824</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31067,7 +31067,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31124,7 +31124,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31181,7 +31181,7 @@
         <v>45824</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31238,7 +31238,7 @@
         <v>45824</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31295,7 +31295,7 @@
         <v>45827</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31357,7 +31357,7 @@
         <v>45827</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31419,7 +31419,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31481,7 +31481,7 @@
         <v>45827</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31543,7 +31543,7 @@
         <v>45826</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31605,7 +31605,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31667,7 +31667,7 @@
         <v>45831</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31724,7 +31724,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31786,7 +31786,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31848,7 +31848,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31905,7 +31905,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31967,7 +31967,7 @@
         <v>45870.37630787037</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32029,7 +32029,7 @@
         <v>45110</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32091,7 +32091,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32153,7 +32153,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32215,7 +32215,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32272,7 +32272,7 @@
         <v>45833</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32329,7 +32329,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32386,7 +32386,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32443,7 +32443,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32500,7 +32500,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32562,7 +32562,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32624,7 +32624,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32686,7 +32686,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32748,7 +32748,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32805,7 +32805,7 @@
         <v>45870</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32867,7 +32867,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32929,7 +32929,7 @@
         <v>45834</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32986,7 +32986,7 @@
         <v>45803</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33043,7 +33043,7 @@
         <v>45483</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33100,7 +33100,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33157,7 +33157,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33219,7 +33219,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33276,7 +33276,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33333,7 +33333,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33390,7 +33390,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33447,7 +33447,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33504,7 +33504,7 @@
         <v>45840</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33561,7 +33561,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33623,7 +33623,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33680,7 +33680,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33737,7 +33737,7 @@
         <v>45840</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33799,7 +33799,7 @@
         <v>45646</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33856,7 +33856,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33913,7 +33913,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33970,7 +33970,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34027,7 +34027,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>45840.38418981482</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34141,7 +34141,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34198,7 +34198,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34260,7 +34260,7 @@
         <v>45882</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34317,7 +34317,7 @@
         <v>45840</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>45456</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34555,7 +34555,7 @@
         <v>44490</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44143</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>45156</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44755</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34907,7 +34907,7 @@
         <v>45868</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34969,7 +34969,7 @@
         <v>44648</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35093,7 +35093,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35155,7 +35155,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35212,7 +35212,7 @@
         <v>45110</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35274,7 +35274,7 @@
         <v>45884</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35336,7 +35336,7 @@
         <v>45887</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35398,7 +35398,7 @@
         <v>45882</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35455,7 +35455,7 @@
         <v>45882</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35512,7 +35512,7 @@
         <v>44642</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35574,7 +35574,7 @@
         <v>45887</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35636,7 +35636,7 @@
         <v>45070</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35693,7 +35693,7 @@
         <v>44901</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35750,7 +35750,7 @@
         <v>45232</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35812,7 +35812,7 @@
         <v>45891.51008101852</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35874,7 +35874,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35931,7 +35931,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35988,7 +35988,7 @@
         <v>45894.51857638889</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36045,7 +36045,7 @@
         <v>45894</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36107,7 +36107,7 @@
         <v>45893</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45672</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36340,7 +36340,7 @@
         <v>45803</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36397,7 +36397,7 @@
         <v>45893.46916666667</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45894.36493055556</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>45764</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>45895.44861111111</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45897.48153935185</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45897.48422453704</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45894</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37044,7 +37044,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45254</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37163,7 +37163,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37220,7 +37220,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37277,7 +37277,7 @@
         <v>45896</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>45901.65390046296</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37401,7 +37401,7 @@
         <v>45901.37751157407</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37463,7 +37463,7 @@
         <v>45895</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37525,7 +37525,7 @@
         <v>45901.65690972222</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37587,7 +37587,7 @@
         <v>45901.62032407407</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45901.64849537037</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37711,7 +37711,7 @@
         <v>45901.41519675926</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37773,7 +37773,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37835,7 +37835,7 @@
         <v>45674</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37892,7 +37892,7 @@
         <v>45902.32747685185</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37954,7 +37954,7 @@
         <v>45875</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38011,7 +38011,7 @@
         <v>45901</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38068,7 +38068,7 @@
         <v>44124</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38125,7 +38125,7 @@
         <v>45874</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38187,7 +38187,7 @@
         <v>45894</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38249,7 +38249,7 @@
         <v>45890</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38311,7 +38311,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38373,7 +38373,7 @@
         <v>45903</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38435,7 +38435,7 @@
         <v>45774</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38497,7 +38497,7 @@
         <v>45300</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38554,7 +38554,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38611,7 +38611,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45902.40394675926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38735,7 +38735,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38792,7 +38792,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38906,7 +38906,7 @@
         <v>45649</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38963,7 +38963,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39020,7 +39020,7 @@
         <v>45625</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39077,7 +39077,7 @@
         <v>45589</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>45589</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39263,7 +39263,7 @@
         <v>45902</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39325,7 +39325,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45905.42783564814</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39449,7 +39449,7 @@
         <v>45874</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39526,7 +39526,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39588,7 +39588,7 @@
         <v>45761</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39650,7 +39650,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39707,7 +39707,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39769,7 +39769,7 @@
         <v>45902</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39831,7 +39831,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39888,7 +39888,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39945,7 +39945,7 @@
         <v>45460</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -40007,7 +40007,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40069,7 +40069,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40126,7 +40126,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40183,7 +40183,7 @@
         <v>45350</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40240,7 +40240,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40297,7 +40297,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40354,7 +40354,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40416,7 +40416,7 @@
         <v>44908</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40473,7 +40473,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40530,7 +40530,7 @@
         <v>44628</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40587,7 +40587,7 @@
         <v>45216</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40649,7 +40649,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40706,7 +40706,7 @@
         <v>45161</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40768,7 +40768,7 @@
         <v>45161</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40830,7 +40830,7 @@
         <v>44566</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40887,7 +40887,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40944,7 +40944,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -41001,7 +41001,7 @@
         <v>45246</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41058,7 +41058,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41115,7 +41115,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41177,7 +41177,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41239,7 +41239,7 @@
         <v>45356</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41296,7 +41296,7 @@
         <v>44299</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41353,7 +41353,7 @@
         <v>45356</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41410,7 +41410,7 @@
         <v>45358</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41467,7 +41467,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41524,7 +41524,7 @@
         <v>45114</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41581,7 +41581,7 @@
         <v>45316</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41638,7 +41638,7 @@
         <v>45323</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41695,7 +41695,7 @@
         <v>45770</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41752,7 +41752,7 @@
         <v>44438</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41809,7 +41809,7 @@
         <v>44529</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41866,7 +41866,7 @@
         <v>44648</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41928,7 +41928,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41985,7 +41985,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42042,7 +42042,7 @@
         <v>45152</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42099,7 +42099,7 @@
         <v>45212</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42156,7 +42156,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42213,7 +42213,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42384,7 +42384,7 @@
         <v>44474</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42441,7 +42441,7 @@
         <v>44566</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42498,7 +42498,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42560,7 +42560,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42617,7 +42617,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42679,7 +42679,7 @@
         <v>44795</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42736,7 +42736,7 @@
         <v>44477</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42793,7 +42793,7 @@
         <v>45132</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42850,7 +42850,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42907,7 +42907,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42964,7 +42964,7 @@
         <v>45770</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43021,7 +43021,7 @@
         <v>45704</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43078,7 +43078,7 @@
         <v>45161</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43135,7 +43135,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43192,7 +43192,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43249,7 +43249,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43306,7 +43306,7 @@
         <v>45099</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43363,7 +43363,7 @@
         <v>44994</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43420,7 +43420,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43477,7 +43477,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43539,7 +43539,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43596,7 +43596,7 @@
         <v>45068</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43653,7 +43653,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43715,7 +43715,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43772,7 +43772,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43834,7 +43834,7 @@
         <v>44908</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43891,7 +43891,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43953,7 +43953,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44010,7 +44010,7 @@
         <v>45772</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44067,7 +44067,7 @@
         <v>44445</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45341</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44186,7 +44186,7 @@
         <v>44151</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44248,7 +44248,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44310,7 +44310,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44372,7 +44372,7 @@
         <v>45187</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44434,7 +44434,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44491,7 +44491,7 @@
         <v>44887</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44553,7 +44553,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44615,7 +44615,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44677,7 +44677,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44734,7 +44734,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44796,7 +44796,7 @@
         <v>45653</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44853,7 +44853,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44910,7 +44910,7 @@
         <v>45351</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44967,7 +44967,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45024,7 +45024,7 @@
         <v>45323</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45081,7 +45081,7 @@
         <v>45596</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45138,7 +45138,7 @@
         <v>44931</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45195,7 +45195,7 @@
         <v>45001</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45252,7 +45252,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45309,7 +45309,7 @@
         <v>45732</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45366,7 +45366,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45423,7 +45423,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45480,7 +45480,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45537,7 +45537,7 @@
         <v>45645</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45599,7 +45599,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45656,7 +45656,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45718,7 +45718,7 @@
         <v>45685</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45775,7 +45775,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45837,7 +45837,7 @@
         <v>44110</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45894,7 +45894,7 @@
         <v>44378</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45951,7 +45951,7 @@
         <v>44110</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46013,7 +46013,7 @@
         <v>44994</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46070,7 +46070,7 @@
         <v>45685</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46127,7 +46127,7 @@
         <v>45105</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46189,7 +46189,7 @@
         <v>45035</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46246,7 +46246,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46303,7 +46303,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46360,7 +46360,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46422,7 +46422,7 @@
         <v>44883</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46484,7 +46484,7 @@
         <v>45771</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46541,7 +46541,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46598,7 +46598,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46655,7 +46655,7 @@
         <v>44889</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46712,7 +46712,7 @@
         <v>45099</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46769,7 +46769,7 @@
         <v>44484</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46826,7 +46826,7 @@
         <v>45561</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46883,7 +46883,7 @@
         <v>45406</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46940,7 +46940,7 @@
         <v>44573</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47002,7 +47002,7 @@
         <v>44735</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47064,7 +47064,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47121,7 +47121,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47183,7 +47183,7 @@
         <v>45454</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47240,7 +47240,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47297,7 +47297,7 @@
         <v>45079</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47354,7 +47354,7 @@
         <v>45762</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47411,7 +47411,7 @@
         <v>45646</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47468,7 +47468,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47525,7 +47525,7 @@
         <v>44356</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47582,7 +47582,7 @@
         <v>45152</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47639,7 +47639,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47701,7 +47701,7 @@
         <v>45769</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47758,7 +47758,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47815,7 +47815,7 @@
         <v>45587</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47872,7 +47872,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>44378</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48043,7 +48043,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45379</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>44648</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48286,7 +48286,7 @@
         <v>44565</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48343,7 +48343,7 @@
         <v>44216</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45642</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>44994</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48514,7 +48514,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>44568</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45301</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45764</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48990,7 +48990,7 @@
         <v>45764</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49047,7 +49047,7 @@
         <v>45761</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49104,7 +49104,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45750</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49228,7 +49228,7 @@
         <v>44292</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49285,7 +49285,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49342,7 +49342,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49399,7 +49399,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49456,7 +49456,7 @@
         <v>44812</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49513,7 +49513,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49570,7 +49570,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44823</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49689,7 +49689,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>45625</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49865,7 +49865,7 @@
         <v>45723</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49922,7 +49922,7 @@
         <v>45723</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49979,7 +49979,7 @@
         <v>45639</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50036,7 +50036,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50093,7 +50093,7 @@
         <v>45152</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50150,7 +50150,7 @@
         <v>44903</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50207,7 +50207,7 @@
         <v>45013</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50264,7 +50264,7 @@
         <v>44585</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50321,7 +50321,7 @@
         <v>45770</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50378,7 +50378,7 @@
         <v>45672</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50435,7 +50435,7 @@
         <v>44127</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50497,7 +50497,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50559,7 +50559,7 @@
         <v>45752</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50616,7 +50616,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50678,7 +50678,7 @@
         <v>45591</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50740,7 +50740,7 @@
         <v>45591</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50802,7 +50802,7 @@
         <v>45586</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50864,7 +50864,7 @@
         <v>45425</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50921,7 +50921,7 @@
         <v>45204</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50978,7 +50978,7 @@
         <v>45687</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51035,7 +51035,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51092,7 +51092,7 @@
         <v>44657</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51149,7 +51149,7 @@
         <v>44120</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51206,7 +51206,7 @@
         <v>44120</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51263,7 +51263,7 @@
         <v>45764</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51320,7 +51320,7 @@
         <v>44391</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51377,7 +51377,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51434,7 +51434,7 @@
         <v>44847</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51491,7 +51491,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51553,7 +51553,7 @@
         <v>44573</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51615,7 +51615,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51672,7 +51672,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51734,7 +51734,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51791,7 +51791,7 @@
         <v>44925</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51848,7 +51848,7 @@
         <v>45749</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51905,7 +51905,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51962,7 +51962,7 @@
         <v>45314</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52019,7 +52019,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>44124</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45212</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45771</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45912.40692129629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45512</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45307</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>44904</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45428</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44130</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45893</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44804</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>44489</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44165</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45341</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>44678</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45155</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45714</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45301</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45559</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45842</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45701</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45526</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45137</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44830</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45072</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44648</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44853</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>44840</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44796</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44088</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44365</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>45611</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45645</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45803.67</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45205</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45594</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45513</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44692</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45773</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45586</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45901.40067129629</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45538</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44217</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44158</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44509</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>44677</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44215</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44274</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44577</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44414</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>44414</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44350</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44090</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44217</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44671</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44120</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44313</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44350</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>44414</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44414</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44216</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44809</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44648</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44138</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44165</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44168</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44187</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44274</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44286</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44617</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44648</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44274</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44439</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44284</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44464</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44865</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44204</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44609</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44223</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44110</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44158</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44671</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44182</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44125</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44313</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44151</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44358</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44721</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44796</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44378</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44749</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44484</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44722</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44174</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44438</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44313</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44313</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44217</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44182</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44530</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44099</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44648</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44414</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44565</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44473</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44566</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44182</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44182</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44617</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44293</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44356</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44596</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44795</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>44489</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>44648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44734</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44248</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44671</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44116</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44238</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44299</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44313</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44566</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44566</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45105</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45068</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44833</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44274</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44480</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45358</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45356</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45771</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44211</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44489</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45672</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44908</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>45099</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45764</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45764</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45397</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45397</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45642</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45301</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45254</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45110</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44529</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45370</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45429</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>44477</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45574</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44529</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44558</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44333</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45156</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44983</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44883</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45786</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45149</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45152</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44441</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44378</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44565</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44735</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44439</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45419</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45591</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44609</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45379</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44356</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45516</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45758</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44391</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44374</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44635</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>44795</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45483</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44127</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45589</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45216</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45596</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45793</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44120</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44120</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44566</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45590</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45590</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45793</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45645</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44573</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45643</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45798</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45797</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45478</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45411</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44908</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45803</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45646</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45429</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45429</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45682</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45804</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45590</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>44628</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45448</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45608</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45608</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>44994</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44110</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45608</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45583</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>44648</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45205</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45204</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>44110</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>44151</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45212</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44901</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45687</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>44529</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>44529</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45770</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45518</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45546</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45464</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>44881</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45429</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45750</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45132</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45013</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45813</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45685</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45505</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45639</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45653</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45446</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45653</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45226</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45818</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45460</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45818</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>44445</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45152</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45237</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45824</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45824</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>45764</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45824</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>44755</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45161</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45826</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44164</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45301</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45827</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45827</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45827</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44642</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44490</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45054</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45246</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45414</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45831</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45762</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45833</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45314</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45256</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>44484</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45764</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45764</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44657</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44657</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>44994</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>44673</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45562</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45589</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45589</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45803</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45254</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45264</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45625</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45323</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45356</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44903</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45645</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45212</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44474</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45840</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>45300</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45260</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45161</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45840</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45114</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>44796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>44573</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45345</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45085</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45483</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45285</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45153</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45149</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>45323</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44970</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45882</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>44568</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>44648</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>44386</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45840</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45764</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45672</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45752</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45582</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45748</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44524</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45761</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>44642</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44900</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>45772</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>44298</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45589</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45210</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44110</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44887</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44565</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45085</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>44438</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44529</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45070</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44356</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44248</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>45882</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45882</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45077</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44812</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45079</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45887</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>44127</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>44143</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45338</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45887</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>44292</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45232</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45769</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45406</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45561</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>44747</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44706</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44423</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45893.46916666667</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>44979</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>44931</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45894.36493055556</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45893</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44216</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45586</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45895.44861111111</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45187</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45600</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45591</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45897.48153935185</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>44925</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>44378</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>45091</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>45897.48422453704</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45901.65390046296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45901.41519675926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45902.32747685185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45901</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45894</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45901.65690972222</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>45901.37751157407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45902.40394675926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45901.62032407407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45901.64849537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45895</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44585</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45674</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45902</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45875</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>44124</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45874</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45774</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>44847</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45903</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45902</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45906.71304398148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45906.71729166667</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45874</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45905.42783564814</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45906.68483796297</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45907.34451388889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44392</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45316</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>44552</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45761</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45470</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45587</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45910.44831018519</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45114</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45910.63275462963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45910.64707175926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>44566</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45910.65401620371</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45685</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45912.63472222222</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45912.40695601852</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45912.42748842593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45894</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45834</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>45894</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45890</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45868</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45870</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45870</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45456</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45884</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45891</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45246</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45912.40694444445</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45911.3857175926</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45762</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45453</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45639</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45099</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45770</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45454</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45425</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45625</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45646</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45766</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45649</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>44529</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50589,7 +50589,7 @@
         <v>44657</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>44330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>45350</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>45379</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>44484</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45596</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45723</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45723</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45749</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45035</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>45341</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51635,7 +51635,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51692,7 +51692,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>44833</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51863,7 +51863,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>45254</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>44935</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45244</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52153,7 +52153,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45351</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45732</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>44853</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
         <v>44169</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>44964</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1341,7 +1341,7 @@
         <v>45237</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1438,7 +1438,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1540,7 +1540,7 @@
         <v>44859</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1641,7 +1641,7 @@
         <v>44889</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1738,7 +1738,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1839,7 +1839,7 @@
         <v>44124</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1935,7 +1935,7 @@
         <v>45212</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>45295</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>45622</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2323,7 +2323,7 @@
         <v>45771</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2422,7 +2422,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2517,7 +2517,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2615,7 +2615,7 @@
         <v>44795</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2713,7 +2713,7 @@
         <v>45049</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2802,7 +2802,7 @@
         <v>45819</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2896,7 +2896,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2994,7 +2994,7 @@
         <v>44869</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3092,7 +3092,7 @@
         <v>45912.40692129629</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3185,7 +3185,7 @@
         <v>45512</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3283,7 +3283,7 @@
         <v>45307</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
         <v>44158</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3561,7 +3561,7 @@
         <v>44904</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3652,7 +3652,7 @@
         <v>45428</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3743,7 +3743,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3839,7 +3839,7 @@
         <v>44130</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45893</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4027,7 +4027,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4123,7 +4123,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
         <v>44322</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4300,7 +4300,7 @@
         <v>44166</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4386,7 +4386,7 @@
         <v>44804</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4477,7 +4477,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4568,7 +4568,7 @@
         <v>44489</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4654,7 +4654,7 @@
         <v>44165</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>45341</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4836,7 +4836,7 @@
         <v>44678</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4927,7 +4927,7 @@
         <v>45155</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5022,7 +5022,7 @@
         <v>45714</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5113,7 +5113,7 @@
         <v>45517</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5204,7 +5204,7 @@
         <v>45301</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5294,7 +5294,7 @@
         <v>45559</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5385,7 +5385,7 @@
         <v>45842</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5571,7 +5571,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>45701</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5752,7 +5752,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5838,7 +5838,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5929,7 +5929,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>45526</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6115,7 +6115,7 @@
         <v>45137</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6210,7 +6210,7 @@
         <v>44830</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>45072</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44648</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>44853</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6579,7 +6579,7 @@
         <v>44840</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6669,7 +6669,7 @@
         <v>44796</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6758,7 +6758,7 @@
         <v>44088</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6848,7 +6848,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6937,7 +6937,7 @@
         <v>44421</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44365</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7117,7 +7117,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7202,7 +7202,7 @@
         <v>45611</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7292,7 +7292,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7382,7 +7382,7 @@
         <v>45645</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7472,7 +7472,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>45803.67</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7741,7 +7741,7 @@
         <v>45205</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>45594</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7925,7 +7925,7 @@
         <v>45513</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8010,7 +8010,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8100,7 +8100,7 @@
         <v>44692</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8190,7 +8190,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8280,7 +8280,7 @@
         <v>45773</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
         <v>45586</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8460,7 +8460,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8639,7 +8639,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8729,7 +8729,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>45901.40067129629</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8904,7 +8904,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8994,7 +8994,7 @@
         <v>45538</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9084,7 +9084,7 @@
         <v>44217</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         <v>44207</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9198,7 +9198,7 @@
         <v>44158</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9255,7 +9255,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9312,7 +9312,7 @@
         <v>44158</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9369,7 +9369,7 @@
         <v>44509</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9426,7 +9426,7 @@
         <v>44677</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9483,7 +9483,7 @@
         <v>44215</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9540,7 +9540,7 @@
         <v>44274</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9597,7 +9597,7 @@
         <v>44577</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9654,7 +9654,7 @@
         <v>44414</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9711,7 +9711,7 @@
         <v>44414</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9768,7 +9768,7 @@
         <v>44350</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -9825,7 +9825,7 @@
         <v>44090</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
         <v>44217</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -9939,7 +9939,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10001,7 +10001,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10058,7 +10058,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10120,7 +10120,7 @@
         <v>44671</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10177,7 +10177,7 @@
         <v>44852</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10239,7 +10239,7 @@
         <v>44120</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>44313</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10353,7 +10353,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>44350</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10472,7 +10472,7 @@
         <v>44414</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10529,7 +10529,7 @@
         <v>44414</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10586,7 +10586,7 @@
         <v>44216</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10643,7 +10643,7 @@
         <v>44809</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10705,7 +10705,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10762,7 +10762,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -10819,7 +10819,7 @@
         <v>44815</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -10881,7 +10881,7 @@
         <v>44648</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -10943,7 +10943,7 @@
         <v>44138</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11005,7 +11005,7 @@
         <v>44130</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11062,7 +11062,7 @@
         <v>44165</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11119,7 +11119,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11176,7 +11176,7 @@
         <v>44168</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11233,7 +11233,7 @@
         <v>44187</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11290,7 +11290,7 @@
         <v>44274</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11347,7 +11347,7 @@
         <v>44286</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11404,7 +11404,7 @@
         <v>44617</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11461,7 +11461,7 @@
         <v>44648</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44274</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44439</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44284</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44464</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44865</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44204</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44609</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -11932,7 +11932,7 @@
         <v>44609</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -11989,7 +11989,7 @@
         <v>44223</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44110</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44158</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44671</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44182</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44125</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12398,7 +12398,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44313</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44151</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44358</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44721</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44796</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44796</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -12978,7 +12978,7 @@
         <v>44378</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13035,7 +13035,7 @@
         <v>44749</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44484</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44722</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44174</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44438</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13449,7 +13449,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13511,7 +13511,7 @@
         <v>44313</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13568,7 +13568,7 @@
         <v>44313</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13625,7 +13625,7 @@
         <v>44217</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13682,7 +13682,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13744,7 +13744,7 @@
         <v>44182</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13801,7 +13801,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>44530</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44099</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14086,7 +14086,7 @@
         <v>44648</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>44414</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>44565</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44473</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>44566</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44182</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>44182</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>44617</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>44293</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14795,7 +14795,7 @@
         <v>44356</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -14852,7 +14852,7 @@
         <v>44596</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>44795</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>44489</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>44648</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15095,7 +15095,7 @@
         <v>44734</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15152,7 +15152,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15214,7 +15214,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15271,7 +15271,7 @@
         <v>44248</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15328,7 +15328,7 @@
         <v>44671</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15385,7 +15385,7 @@
         <v>44116</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15442,7 +15442,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15504,7 +15504,7 @@
         <v>44238</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15561,7 +15561,7 @@
         <v>44299</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15618,7 +15618,7 @@
         <v>44313</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15675,7 +15675,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15737,7 +15737,7 @@
         <v>44566</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15794,7 +15794,7 @@
         <v>44566</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -15851,7 +15851,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -15913,7 +15913,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -15975,7 +15975,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16032,7 +16032,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16089,7 +16089,7 @@
         <v>45105</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16151,7 +16151,7 @@
         <v>45068</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16208,7 +16208,7 @@
         <v>44833</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16265,7 +16265,7 @@
         <v>44274</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16322,7 +16322,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16379,7 +16379,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16441,7 +16441,7 @@
         <v>44480</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16498,7 +16498,7 @@
         <v>45358</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16555,7 +16555,7 @@
         <v>45356</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16612,7 +16612,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16674,7 +16674,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16736,7 +16736,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16793,7 +16793,7 @@
         <v>45771</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -16850,7 +16850,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -16907,7 +16907,7 @@
         <v>44211</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
         <v>44489</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17021,7 +17021,7 @@
         <v>45672</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17078,7 +17078,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17140,7 +17140,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17197,7 +17197,7 @@
         <v>44908</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17254,7 +17254,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17311,7 +17311,7 @@
         <v>45099</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17368,7 +17368,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17430,7 +17430,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17492,7 +17492,7 @@
         <v>45764</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17549,7 +17549,7 @@
         <v>45764</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17606,7 +17606,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17663,7 +17663,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17720,7 +17720,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17777,7 +17777,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -17834,7 +17834,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -17891,7 +17891,7 @@
         <v>45397</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -17948,7 +17948,7 @@
         <v>45397</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>45642</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18062,7 +18062,7 @@
         <v>45301</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18124,7 +18124,7 @@
         <v>45254</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18181,7 +18181,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18238,7 +18238,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18295,7 +18295,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18357,7 +18357,7 @@
         <v>45778</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18476,7 +18476,7 @@
         <v>45110</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18538,7 +18538,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18595,7 +18595,7 @@
         <v>44529</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18652,7 +18652,7 @@
         <v>45370</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18709,7 +18709,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18766,7 +18766,7 @@
         <v>45429</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18823,7 +18823,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -18885,7 +18885,7 @@
         <v>44477</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -18942,7 +18942,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -18999,7 +18999,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19056,7 +19056,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19118,7 +19118,7 @@
         <v>45574</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19299,7 +19299,7 @@
         <v>44529</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19356,7 +19356,7 @@
         <v>44558</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19413,7 +19413,7 @@
         <v>44333</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19470,7 +19470,7 @@
         <v>45156</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19527,7 +19527,7 @@
         <v>44983</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19584,7 +19584,7 @@
         <v>44883</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19646,7 +19646,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19708,7 +19708,7 @@
         <v>45786</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19770,7 +19770,7 @@
         <v>45149</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19827,7 +19827,7 @@
         <v>45152</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -19884,7 +19884,7 @@
         <v>44441</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -19941,7 +19941,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -19998,7 +19998,7 @@
         <v>44378</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20055,7 +20055,7 @@
         <v>44565</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20112,7 +20112,7 @@
         <v>44735</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20174,7 +20174,7 @@
         <v>44439</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20231,7 +20231,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20288,7 +20288,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20345,7 +20345,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20402,7 +20402,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20459,7 +20459,7 @@
         <v>45419</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20516,7 +20516,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20573,7 +20573,7 @@
         <v>45591</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20635,7 +20635,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20697,7 +20697,7 @@
         <v>44609</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20754,7 +20754,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -20816,7 +20816,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -20878,7 +20878,7 @@
         <v>45379</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -20935,7 +20935,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -20997,7 +20997,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21059,7 +21059,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21121,7 +21121,7 @@
         <v>44356</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21178,7 +21178,7 @@
         <v>45161</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21240,7 +21240,7 @@
         <v>45161</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21302,7 +21302,7 @@
         <v>45516</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21364,7 +21364,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21426,7 +21426,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21488,7 +21488,7 @@
         <v>45758</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21545,7 +21545,7 @@
         <v>44391</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21602,7 +21602,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21664,7 +21664,7 @@
         <v>44374</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21721,7 +21721,7 @@
         <v>44635</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21783,7 +21783,7 @@
         <v>44795</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -21840,7 +21840,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -21897,7 +21897,7 @@
         <v>45483</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -21954,7 +21954,7 @@
         <v>44127</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22016,7 +22016,7 @@
         <v>45589</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22078,7 +22078,7 @@
         <v>45216</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22140,7 +22140,7 @@
         <v>45596</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22197,7 +22197,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22254,7 +22254,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22311,7 +22311,7 @@
         <v>45793</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22373,7 +22373,7 @@
         <v>44120</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22430,7 +22430,7 @@
         <v>44120</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22487,7 +22487,7 @@
         <v>44566</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22544,7 +22544,7 @@
         <v>45590</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22601,7 +22601,7 @@
         <v>45590</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22658,7 +22658,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22720,7 +22720,7 @@
         <v>45793</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22782,7 +22782,7 @@
         <v>45645</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -22844,7 +22844,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -22906,7 +22906,7 @@
         <v>44573</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -22968,7 +22968,7 @@
         <v>45643</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23030,7 +23030,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23092,7 +23092,7 @@
         <v>45798</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23154,7 +23154,7 @@
         <v>45797</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23216,7 +23216,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23278,7 +23278,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23335,7 +23335,7 @@
         <v>45478</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23392,7 +23392,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23454,7 +23454,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23516,7 +23516,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23573,7 +23573,7 @@
         <v>45411</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23630,7 +23630,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23692,7 +23692,7 @@
         <v>44908</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23749,7 +23749,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23811,7 +23811,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45803</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>45646</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24101,7 +24101,7 @@
         <v>45429</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24158,7 +24158,7 @@
         <v>45429</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24215,7 +24215,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24272,7 +24272,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24334,7 +24334,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24391,7 +24391,7 @@
         <v>45682</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24453,7 +24453,7 @@
         <v>45804</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24510,7 +24510,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24567,7 +24567,7 @@
         <v>45590</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24624,7 +24624,7 @@
         <v>44628</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24681,7 +24681,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24738,7 +24738,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24795,7 +24795,7 @@
         <v>45448</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>45608</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>45608</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>44994</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25090,7 +25090,7 @@
         <v>44110</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25147,7 +25147,7 @@
         <v>45608</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45583</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25385,7 +25385,7 @@
         <v>44648</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25447,7 +25447,7 @@
         <v>45205</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25509,7 +25509,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25566,7 +25566,7 @@
         <v>45204</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25623,7 +25623,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25685,7 +25685,7 @@
         <v>44110</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25747,7 +25747,7 @@
         <v>44151</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25809,7 +25809,7 @@
         <v>44889</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -25866,7 +25866,7 @@
         <v>45212</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -25928,7 +25928,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -25985,7 +25985,7 @@
         <v>44901</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26042,7 +26042,7 @@
         <v>45687</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26099,7 +26099,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26156,7 +26156,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26218,7 +26218,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26275,7 +26275,7 @@
         <v>44529</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26332,7 +26332,7 @@
         <v>44529</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26389,7 +26389,7 @@
         <v>45770</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26446,7 +26446,7 @@
         <v>45518</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26503,7 +26503,7 @@
         <v>45546</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26565,7 +26565,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45464</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26689,7 +26689,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26746,7 +26746,7 @@
         <v>44881</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26803,7 +26803,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -26860,7 +26860,7 @@
         <v>45429</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -26917,7 +26917,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -26979,7 +26979,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27041,7 +27041,7 @@
         <v>45750</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27103,7 +27103,7 @@
         <v>45132</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27160,7 +27160,7 @@
         <v>45013</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27217,7 +27217,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27279,7 +27279,7 @@
         <v>45813</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27341,7 +27341,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27403,7 +27403,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45813</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27527,7 +27527,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27589,7 +27589,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27646,7 +27646,7 @@
         <v>45685</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27703,7 +27703,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27765,7 +27765,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27822,7 +27822,7 @@
         <v>45505</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -27884,7 +27884,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>45639</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28003,7 +28003,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28060,7 +28060,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28122,7 +28122,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28184,7 +28184,7 @@
         <v>45704</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28241,7 +28241,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28303,7 +28303,7 @@
         <v>45653</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28360,7 +28360,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28417,7 +28417,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28474,7 +28474,7 @@
         <v>45446</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>45653</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28588,7 +28588,7 @@
         <v>45226</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28650,7 +28650,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28774,7 +28774,7 @@
         <v>45818</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28836,7 +28836,7 @@
         <v>45232</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -28898,7 +28898,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -28955,7 +28955,7 @@
         <v>45460</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29136,7 +29136,7 @@
         <v>45818</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29198,7 +29198,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29280,7 +29280,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29337,7 +29337,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29399,7 +29399,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29461,7 +29461,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29523,7 +29523,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29580,7 +29580,7 @@
         <v>44445</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29637,7 +29637,7 @@
         <v>45152</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29694,7 +29694,7 @@
         <v>45237</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29751,7 +29751,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29813,7 +29813,7 @@
         <v>45824</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -29870,7 +29870,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -29932,7 +29932,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -29989,7 +29989,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30051,7 +30051,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30113,7 +30113,7 @@
         <v>45824</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30170,7 +30170,7 @@
         <v>45764</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30227,7 +30227,7 @@
         <v>45824</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30284,7 +30284,7 @@
         <v>44755</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30346,7 +30346,7 @@
         <v>45161</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30403,7 +30403,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30465,7 +30465,7 @@
         <v>45826</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30527,7 +30527,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30589,7 +30589,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30646,7 +30646,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30703,7 +30703,7 @@
         <v>44164</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -30936,7 +30936,7 @@
         <v>45301</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -30993,7 +30993,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31050,7 +31050,7 @@
         <v>45827</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31112,7 +31112,7 @@
         <v>45827</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45827</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31298,7 +31298,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>44642</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31417,7 +31417,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>44490</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45054</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45448</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31774,7 +31774,7 @@
         <v>44963</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31831,7 +31831,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -31888,7 +31888,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -31950,7 +31950,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32012,7 +32012,7 @@
         <v>45246</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32069,7 +32069,7 @@
         <v>45414</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45831</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45762</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32359,7 +32359,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32416,7 +32416,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32473,7 +32473,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32535,7 +32535,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32597,7 +32597,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32654,7 +32654,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32716,7 +32716,7 @@
         <v>45833</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32773,7 +32773,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32830,7 +32830,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32892,7 +32892,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -32949,7 +32949,7 @@
         <v>45314</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33006,7 +33006,7 @@
         <v>45256</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33063,7 +33063,7 @@
         <v>44484</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33120,7 +33120,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33182,7 +33182,7 @@
         <v>45764</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33239,7 +33239,7 @@
         <v>45764</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33296,7 +33296,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33353,7 +33353,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33410,7 +33410,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33472,7 +33472,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33534,7 +33534,7 @@
         <v>44657</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33591,7 +33591,7 @@
         <v>44657</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33648,7 +33648,7 @@
         <v>44994</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33705,7 +33705,7 @@
         <v>44673</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33762,7 +33762,7 @@
         <v>45562</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33824,7 +33824,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33881,7 +33881,7 @@
         <v>45589</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -33943,7 +33943,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34005,7 +34005,7 @@
         <v>45589</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34067,7 +34067,7 @@
         <v>45803</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34124,7 +34124,7 @@
         <v>45254</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34181,7 +34181,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34238,7 +34238,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34295,7 +34295,7 @@
         <v>45770</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34352,7 +34352,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34414,7 +34414,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34476,7 +34476,7 @@
         <v>44648</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34538,7 +34538,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34600,7 +34600,7 @@
         <v>45264</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34662,7 +34662,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34719,7 +34719,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34781,7 +34781,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34843,7 +34843,7 @@
         <v>45625</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34905,7 +34905,7 @@
         <v>45323</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -34962,7 +34962,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35019,7 +35019,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35076,7 +35076,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35133,7 +35133,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35190,7 +35190,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35247,7 +35247,7 @@
         <v>45356</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35304,7 +35304,7 @@
         <v>44903</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35361,7 +35361,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35418,7 +35418,7 @@
         <v>45645</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45212</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44474</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35656,7 +35656,7 @@
         <v>45840</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35713,7 +35713,7 @@
         <v>45300</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35770,7 +35770,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35827,7 +35827,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35884,7 +35884,7 @@
         <v>45260</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -35941,7 +35941,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45161</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>45840</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36127,7 +36127,7 @@
         <v>44994</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36184,7 +36184,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36241,7 +36241,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36298,7 +36298,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36355,7 +36355,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36417,7 +36417,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36474,7 +36474,7 @@
         <v>45114</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36531,7 +36531,7 @@
         <v>44796</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36588,7 +36588,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36645,7 +36645,7 @@
         <v>44573</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36707,7 +36707,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36764,7 +36764,7 @@
         <v>45345</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36821,7 +36821,7 @@
         <v>45085</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36878,7 +36878,7 @@
         <v>45483</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -36935,7 +36935,7 @@
         <v>45285</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -36992,7 +36992,7 @@
         <v>45153</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37049,7 +37049,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37106,7 +37106,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37168,7 +37168,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37225,7 +37225,7 @@
         <v>45149</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37282,7 +37282,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37339,7 +37339,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>45323</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44970</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37624,7 +37624,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37681,7 +37681,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37738,7 +37738,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37795,7 +37795,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37852,7 +37852,7 @@
         <v>44823</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -37914,7 +37914,7 @@
         <v>45882</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -37971,7 +37971,7 @@
         <v>44568</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38028,7 +38028,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38085,7 +38085,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38142,7 +38142,7 @@
         <v>44648</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38204,7 +38204,7 @@
         <v>44386</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38261,7 +38261,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38323,7 +38323,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38380,7 +38380,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38442,7 +38442,7 @@
         <v>45840</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38504,7 +38504,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38561,7 +38561,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38623,7 +38623,7 @@
         <v>45764</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38680,7 +38680,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38742,7 +38742,7 @@
         <v>44445</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38799,7 +38799,7 @@
         <v>45672</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38856,7 +38856,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -38913,7 +38913,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45752</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45582</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45748</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44524</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45761</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39669,7 +39669,7 @@
         <v>45110</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39731,7 +39731,7 @@
         <v>44642</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39788,7 +39788,7 @@
         <v>44900</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39850,7 +39850,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -39907,7 +39907,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -39964,7 +39964,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40021,7 +40021,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40078,7 +40078,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40135,7 +40135,7 @@
         <v>45772</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40192,7 +40192,7 @@
         <v>44298</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40249,7 +40249,7 @@
         <v>45589</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40311,7 +40311,7 @@
         <v>45210</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40373,7 +40373,7 @@
         <v>44110</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40430,7 +40430,7 @@
         <v>44887</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40492,7 +40492,7 @@
         <v>44565</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40549,7 +40549,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40668,7 +40668,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40725,7 +40725,7 @@
         <v>45085</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40782,7 +40782,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>44438</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -40901,7 +40901,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>44529</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41020,7 +41020,7 @@
         <v>45070</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41077,7 +41077,7 @@
         <v>44356</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41134,7 +41134,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41258,7 +41258,7 @@
         <v>44248</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41315,7 +41315,7 @@
         <v>45882</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45882</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41491,7 +41491,7 @@
         <v>45077</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>44812</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45079</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41719,7 +41719,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41776,7 +41776,7 @@
         <v>45593</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41838,7 +41838,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -41895,7 +41895,7 @@
         <v>45887</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -41957,7 +41957,7 @@
         <v>44127</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42014,7 +42014,7 @@
         <v>44143</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42071,7 +42071,7 @@
         <v>45338</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42128,7 +42128,7 @@
         <v>44910</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45887</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42252,7 +42252,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42314,7 +42314,7 @@
         <v>44292</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42371,7 +42371,7 @@
         <v>45232</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42433,7 +42433,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42490,7 +42490,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42547,7 +42547,7 @@
         <v>45769</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42604,7 +42604,7 @@
         <v>45406</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42661,7 +42661,7 @@
         <v>45561</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42718,7 +42718,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42775,7 +42775,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42832,7 +42832,7 @@
         <v>44747</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>44706</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>44423</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43065,7 +43065,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43122,7 +43122,7 @@
         <v>45893.46916666667</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43184,7 +43184,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43241,7 +43241,7 @@
         <v>44979</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43303,7 +43303,7 @@
         <v>44931</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43360,7 +43360,7 @@
         <v>45894.36493055556</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43479,7 +43479,7 @@
         <v>45893</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>44216</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43598,7 +43598,7 @@
         <v>45586</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43660,7 +43660,7 @@
         <v>45895.44861111111</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43717,7 +43717,7 @@
         <v>45187</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43779,7 +43779,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45600</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>45591</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44022,7 +44022,7 @@
         <v>45897.48153935185</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44079,7 +44079,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44136,7 +44136,7 @@
         <v>44925</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44193,7 +44193,7 @@
         <v>44378</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>45091</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44307,7 +44307,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44364,7 +44364,7 @@
         <v>45897.48422453704</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44421,7 +44421,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44478,7 +44478,7 @@
         <v>45001</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44535,7 +44535,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44592,7 +44592,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44654,7 +44654,7 @@
         <v>45901.65390046296</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44716,7 +44716,7 @@
         <v>45896</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44778,7 +44778,7 @@
         <v>45901.41519675926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44840,7 +44840,7 @@
         <v>45902.32747685185</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45901</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>45894</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45021,7 +45021,7 @@
         <v>45901.65690972222</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45083,7 +45083,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45145,7 +45145,7 @@
         <v>45901.37751157407</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45902.40394675926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45269,7 +45269,7 @@
         <v>45901.62032407407</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45331,7 +45331,7 @@
         <v>45901.64849537037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45393,7 +45393,7 @@
         <v>45895</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45455,7 +45455,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45512,7 +45512,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45574,7 +45574,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45631,7 +45631,7 @@
         <v>44585</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45688,7 +45688,7 @@
         <v>45674</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45745,7 +45745,7 @@
         <v>45902</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45807,7 +45807,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45864,7 +45864,7 @@
         <v>45875</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -45921,7 +45921,7 @@
         <v>44124</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45874</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>45774</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46102,7 +46102,7 @@
         <v>44847</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46221,7 +46221,7 @@
         <v>45903</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46283,7 +46283,7 @@
         <v>45902</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46345,7 +46345,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46407,7 +46407,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46469,7 +46469,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46526,7 +46526,7 @@
         <v>45906.71304398148</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46583,7 +46583,7 @@
         <v>45906.71729166667</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46640,7 +46640,7 @@
         <v>45874</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46717,7 +46717,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46779,7 +46779,7 @@
         <v>45905.42783564814</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46841,7 +46841,7 @@
         <v>45906.68483796297</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46898,7 +46898,7 @@
         <v>45907.34451388889</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -46960,7 +46960,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47022,7 +47022,7 @@
         <v>44392</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47079,7 +47079,7 @@
         <v>45316</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47136,7 +47136,7 @@
         <v>44552</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47193,7 +47193,7 @@
         <v>45761</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47255,7 +47255,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47312,7 +47312,7 @@
         <v>45470</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>45587</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>45910.44831018519</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47493,7 +47493,7 @@
         <v>45114</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47550,7 +47550,7 @@
         <v>45910.63275462963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47612,7 +47612,7 @@
         <v>45910.64707175926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47674,7 +47674,7 @@
         <v>44566</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47731,7 +47731,7 @@
         <v>45910.65401620371</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47793,7 +47793,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47850,7 +47850,7 @@
         <v>45685</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47907,7 +47907,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -47964,7 +47964,7 @@
         <v>45912.63472222222</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48026,7 +48026,7 @@
         <v>45912.40695601852</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>45912.42748842593</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>45894</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48202,7 +48202,7 @@
         <v>45834</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48259,7 +48259,7 @@
         <v>45894</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48316,7 +48316,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48373,7 +48373,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48430,7 +48430,7 @@
         <v>45890</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48492,7 +48492,7 @@
         <v>45868</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48554,7 +48554,7 @@
         <v>45870</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48616,7 +48616,7 @@
         <v>45870</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48678,7 +48678,7 @@
         <v>45456</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48735,7 +48735,7 @@
         <v>45884</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48797,7 +48797,7 @@
         <v>45891</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48859,7 +48859,7 @@
         <v>45246</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48916,7 +48916,7 @@
         <v>45912.40694444445</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -48973,7 +48973,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45911.3857175926</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>45762</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45453</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45639</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49434,7 +49434,7 @@
         <v>45099</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49491,7 +49491,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49548,7 +49548,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49605,7 +49605,7 @@
         <v>45770</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49662,7 +49662,7 @@
         <v>45454</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49719,7 +49719,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49776,7 +49776,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49838,7 +49838,7 @@
         <v>45425</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49895,7 +49895,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -49952,7 +49952,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50014,7 +50014,7 @@
         <v>45625</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50071,7 +50071,7 @@
         <v>45646</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50128,7 +50128,7 @@
         <v>45766</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50190,7 +50190,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50304,7 +50304,7 @@
         <v>45649</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50361,7 +50361,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50418,7 +50418,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50475,7 +50475,7 @@
         <v>44529</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50532,7 +50532,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50589,7 +50589,7 @@
         <v>44657</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50646,7 +50646,7 @@
         <v>45264</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50708,7 +50708,7 @@
         <v>44330</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50765,7 +50765,7 @@
         <v>45350</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50822,7 +50822,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -50879,7 +50879,7 @@
         <v>45379</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -50936,7 +50936,7 @@
         <v>44484</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -50998,7 +50998,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51055,7 +51055,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51112,7 +51112,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51169,7 +51169,7 @@
         <v>45596</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51226,7 +51226,7 @@
         <v>45723</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51283,7 +51283,7 @@
         <v>45723</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51340,7 +51340,7 @@
         <v>45749</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51397,7 +51397,7 @@
         <v>45035</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51454,7 +51454,7 @@
         <v>45341</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51516,7 +51516,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51578,7 +51578,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51635,7 +51635,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51692,7 +51692,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51749,7 +51749,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -51806,7 +51806,7 @@
         <v>44833</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -51863,7 +51863,7 @@
         <v>45152</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -51920,7 +51920,7 @@
         <v>45254</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -51977,7 +51977,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52034,7 +52034,7 @@
         <v>44935</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52091,7 +52091,7 @@
         <v>45244</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52153,7 +52153,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52210,7 +52210,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52267,7 +52267,7 @@
         <v>45351</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52324,7 +52324,7 @@
         <v>45732</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>44853</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>44169</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44964</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>44859</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44124</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1844,7 +1844,7 @@
         <v>45212</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>45819</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>44889</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45295</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45645</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45622</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>45771</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44795</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45049</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3004,7 +3004,7 @@
         <v>45819</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>45512</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3294,7 +3294,7 @@
         <v>44869</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3392,7 +3392,7 @@
         <v>45912.40692129629</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>45307</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3578,7 +3578,7 @@
         <v>44158</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3666,7 +3666,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3859,7 +3859,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3951,7 +3951,7 @@
         <v>45428</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>44904</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4133,7 +4133,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4229,7 +4229,7 @@
         <v>44130</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>45917.61134259259</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4413,7 +4413,7 @@
         <v>45893</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4509,7 +4509,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
         <v>44322</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>44166</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>44804</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4863,7 +4863,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4954,7 +4954,7 @@
         <v>44165</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5045,7 +5045,7 @@
         <v>45714</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5136,7 +5136,7 @@
         <v>45341</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5227,7 +5227,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5318,7 +5318,7 @@
         <v>45517</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5409,7 +5409,7 @@
         <v>45137</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5504,7 +5504,7 @@
         <v>44489</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
         <v>45155</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5685,7 +5685,7 @@
         <v>45301</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5775,7 +5775,7 @@
         <v>45559</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5866,7 +5866,7 @@
         <v>45842</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5957,7 +5957,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6052,7 +6052,7 @@
         <v>45701</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6138,7 +6138,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6233,7 +6233,7 @@
         <v>44830</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6323,7 +6323,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6414,7 +6414,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6595,7 +6595,7 @@
         <v>45072</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6690,7 +6690,7 @@
         <v>45526</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6781,7 +6781,7 @@
         <v>45910.65401620371</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6872,7 +6872,7 @@
         <v>44678</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6963,7 +6963,7 @@
         <v>45922.52559027778</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7054,7 +7054,7 @@
         <v>44648</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7144,7 +7144,7 @@
         <v>44853</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7238,7 +7238,7 @@
         <v>44840</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7328,7 +7328,7 @@
         <v>44421</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7418,7 +7418,7 @@
         <v>44796</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7507,7 +7507,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7766,7 +7766,7 @@
         <v>45645</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7856,7 +7856,7 @@
         <v>45205</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>44365</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8129,7 +8129,7 @@
         <v>45803.67</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8219,7 +8219,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8309,7 +8309,7 @@
         <v>45611</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>44692</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8579,7 +8579,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8669,7 +8669,7 @@
         <v>45594</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8759,7 +8759,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8853,7 +8853,7 @@
         <v>45586</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8943,7 +8943,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9028,7 +9028,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9118,7 +9118,7 @@
         <v>45901.40067129629</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         <v>45538</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9298,7 +9298,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9388,7 +9388,7 @@
         <v>45773</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9478,7 +9478,7 @@
         <v>45513</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9563,7 +9563,7 @@
         <v>44217</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9620,7 +9620,7 @@
         <v>44207</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9677,7 +9677,7 @@
         <v>44158</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9734,7 +9734,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
         <v>44158</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9848,7 +9848,7 @@
         <v>44509</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         <v>44677</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9962,7 +9962,7 @@
         <v>44215</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10019,7 +10019,7 @@
         <v>44274</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10076,7 +10076,7 @@
         <v>44577</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10133,7 +10133,7 @@
         <v>44414</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10190,7 +10190,7 @@
         <v>44414</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10247,7 +10247,7 @@
         <v>44350</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10304,7 +10304,7 @@
         <v>44217</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10361,7 +10361,7 @@
         <v>44671</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10418,7 +10418,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10475,7 +10475,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10537,7 +10537,7 @@
         <v>44852</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10599,7 +10599,7 @@
         <v>44120</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10656,7 +10656,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10718,7 +10718,7 @@
         <v>44313</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10775,7 +10775,7 @@
         <v>44216</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10832,7 +10832,7 @@
         <v>44350</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>44414</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -10946,7 +10946,7 @@
         <v>44414</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11003,7 +11003,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11065,7 +11065,7 @@
         <v>44809</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11127,7 +11127,7 @@
         <v>44414</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11184,7 +11184,7 @@
         <v>44414</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11241,7 +11241,7 @@
         <v>44815</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11303,7 +11303,7 @@
         <v>44648</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11365,7 +11365,7 @@
         <v>44130</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11422,7 +11422,7 @@
         <v>44138</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11484,7 +11484,7 @@
         <v>44165</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11541,7 +11541,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11598,7 +11598,7 @@
         <v>44187</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11655,7 +11655,7 @@
         <v>44168</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11712,7 +11712,7 @@
         <v>44274</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11769,7 +11769,7 @@
         <v>44286</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11826,7 +11826,7 @@
         <v>44617</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11883,7 +11883,7 @@
         <v>44274</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -11940,7 +11940,7 @@
         <v>44648</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12002,7 +12002,7 @@
         <v>44439</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12059,7 +12059,7 @@
         <v>44284</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12121,7 +12121,7 @@
         <v>44464</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12178,7 +12178,7 @@
         <v>44865</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12240,7 +12240,7 @@
         <v>44204</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12297,7 +12297,7 @@
         <v>44223</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12354,7 +12354,7 @@
         <v>44609</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12411,7 +12411,7 @@
         <v>44609</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12468,7 +12468,7 @@
         <v>44110</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12530,7 +12530,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12587,7 +12587,7 @@
         <v>44158</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12644,7 +12644,7 @@
         <v>44671</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12701,7 +12701,7 @@
         <v>44182</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12758,7 +12758,7 @@
         <v>44125</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12820,7 +12820,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12877,7 +12877,7 @@
         <v>44313</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12934,7 +12934,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -12991,7 +12991,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13053,7 +13053,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13115,7 +13115,7 @@
         <v>44313</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13172,7 +13172,7 @@
         <v>44313</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13229,7 +13229,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13291,7 +13291,7 @@
         <v>44721</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13348,7 +13348,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13405,7 +13405,7 @@
         <v>44358</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13462,7 +13462,7 @@
         <v>44378</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13519,7 +13519,7 @@
         <v>44174</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13581,7 +13581,7 @@
         <v>44749</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13638,7 +13638,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13695,7 +13695,7 @@
         <v>44722</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13752,7 +13752,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13814,7 +13814,7 @@
         <v>44182</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13871,7 +13871,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13928,7 +13928,7 @@
         <v>44438</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -13985,7 +13985,7 @@
         <v>44217</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14042,7 +14042,7 @@
         <v>44530</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14099,7 +14099,7 @@
         <v>44238</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14156,7 +14156,7 @@
         <v>44480</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14213,7 +14213,7 @@
         <v>44313</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14270,7 +14270,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14332,7 +14332,7 @@
         <v>44414</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14389,7 +14389,7 @@
         <v>44648</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14451,7 +14451,7 @@
         <v>44565</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14508,7 +14508,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14570,7 +14570,7 @@
         <v>44473</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14632,7 +14632,7 @@
         <v>44566</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14689,7 +14689,7 @@
         <v>44480</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14746,7 +14746,7 @@
         <v>44182</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14803,7 +14803,7 @@
         <v>44617</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14860,7 +14860,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14922,7 +14922,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -14979,7 +14979,7 @@
         <v>44596</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15041,7 +15041,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15098,7 +15098,7 @@
         <v>44529</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15155,7 +15155,7 @@
         <v>44648</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15217,7 +15217,7 @@
         <v>44734</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15274,7 +15274,7 @@
         <v>44248</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15331,7 +15331,7 @@
         <v>44796</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15388,7 +15388,7 @@
         <v>44796</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15445,7 +15445,7 @@
         <v>44116</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15502,7 +15502,7 @@
         <v>44565</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15559,7 +15559,7 @@
         <v>44439</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15616,7 +15616,7 @@
         <v>44566</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15673,7 +15673,7 @@
         <v>44566</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15730,7 +15730,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15792,7 +15792,7 @@
         <v>44356</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15849,7 +15849,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15906,7 +15906,7 @@
         <v>44635</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -15968,7 +15968,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16030,7 +16030,7 @@
         <v>44274</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16087,7 +16087,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16144,7 +16144,7 @@
         <v>44484</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16206,7 +16206,7 @@
         <v>44609</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16263,7 +16263,7 @@
         <v>45091</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16320,7 +16320,7 @@
         <v>45646.6669212963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16377,7 +16377,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16434,7 +16434,7 @@
         <v>45338</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16491,7 +16491,7 @@
         <v>45453</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16548,7 +16548,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16605,7 +16605,7 @@
         <v>45646.6295949074</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16662,7 +16662,7 @@
         <v>44963</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16719,7 +16719,7 @@
         <v>45478</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16776,7 +16776,7 @@
         <v>45370</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16833,7 +16833,7 @@
         <v>44881</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16890,7 +16890,7 @@
         <v>44441</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -16947,7 +16947,7 @@
         <v>45505</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17009,7 +17009,7 @@
         <v>45391.93160879629</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17066,7 +17066,7 @@
         <v>44330</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17123,7 +17123,7 @@
         <v>45764.45171296296</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17180,7 +17180,7 @@
         <v>44979</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17242,7 +17242,7 @@
         <v>45643</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17304,7 +17304,7 @@
         <v>45682</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17366,7 +17366,7 @@
         <v>44374</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17423,7 +17423,7 @@
         <v>45778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17485,7 +17485,7 @@
         <v>44298</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17542,7 +17542,7 @@
         <v>45470</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17604,7 +17604,7 @@
         <v>45782.40684027778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17661,7 +17661,7 @@
         <v>44362.48555555556</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17718,7 +17718,7 @@
         <v>45653</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17775,7 +17775,7 @@
         <v>44783.85420138889</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17832,7 +17832,7 @@
         <v>44248</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17889,7 +17889,7 @@
         <v>45646.63835648148</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -17946,7 +17946,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18008,7 +18008,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18065,7 +18065,7 @@
         <v>45125.95043981481</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18127,7 +18127,7 @@
         <v>44529</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18184,7 +18184,7 @@
         <v>45574</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18246,7 +18246,7 @@
         <v>44392</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18303,7 +18303,7 @@
         <v>44489</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18360,7 +18360,7 @@
         <v>45600.3993287037</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18417,7 +18417,7 @@
         <v>45600.40488425926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18474,7 +18474,7 @@
         <v>45635.41479166667</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18531,7 +18531,7 @@
         <v>45764</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18588,7 +18588,7 @@
         <v>45419</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18645,7 +18645,7 @@
         <v>45600</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18702,7 +18702,7 @@
         <v>44211</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18759,7 +18759,7 @@
         <v>45014.54700231482</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18816,7 +18816,7 @@
         <v>45596</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18873,7 +18873,7 @@
         <v>45254</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -18930,7 +18930,7 @@
         <v>45114</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -18987,7 +18987,7 @@
         <v>45149</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19044,7 +19044,7 @@
         <v>44642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19101,7 +19101,7 @@
         <v>44881.9272337963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19158,7 +19158,7 @@
         <v>45786</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19220,7 +19220,7 @@
         <v>45161</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19282,7 +19282,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19344,7 +19344,7 @@
         <v>45589</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19406,7 +19406,7 @@
         <v>45582</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19463,7 +19463,7 @@
         <v>44964.94435185185</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19525,7 +19525,7 @@
         <v>45077</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19582,7 +19582,7 @@
         <v>45770.63423611111</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19639,7 +19639,7 @@
         <v>45254</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19696,7 +19696,7 @@
         <v>44377.49069444444</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19753,7 +19753,7 @@
         <v>44796</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19810,7 +19810,7 @@
         <v>45448</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19872,7 +19872,7 @@
         <v>45237</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -19929,7 +19929,7 @@
         <v>45791.61200231482</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -19991,7 +19991,7 @@
         <v>45345</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20048,7 +20048,7 @@
         <v>45589.34527777778</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20110,7 +20110,7 @@
         <v>44182</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20167,7 +20167,7 @@
         <v>45694.65678240741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20229,7 +20229,7 @@
         <v>45791.615625</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20291,7 +20291,7 @@
         <v>45791.34467592592</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20353,7 +20353,7 @@
         <v>45379</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20410,7 +20410,7 @@
         <v>45764.45273148148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20467,7 +20467,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20524,7 +20524,7 @@
         <v>45791.61981481482</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20586,7 +20586,7 @@
         <v>45791.59711805556</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20648,7 +20648,7 @@
         <v>45600.38277777778</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20705,7 +20705,7 @@
         <v>44293</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20767,7 +20767,7 @@
         <v>44356</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20824,7 +20824,7 @@
         <v>45792.34626157407</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20886,7 +20886,7 @@
         <v>45523.38938657408</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -20948,7 +20948,7 @@
         <v>45512.53328703704</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21005,7 +21005,7 @@
         <v>45149</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21062,7 +21062,7 @@
         <v>44558</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21119,7 +21119,7 @@
         <v>45793</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21181,7 +21181,7 @@
         <v>45054</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21238,7 +21238,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21295,7 +21295,7 @@
         <v>45429</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -21352,7 +21352,7 @@
         <v>45793.4693287037</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -21414,7 +21414,7 @@
         <v>45792.58290509259</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -21476,7 +21476,7 @@
         <v>45766</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -21538,7 +21538,7 @@
         <v>45085</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -21595,7 +21595,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -21652,7 +21652,7 @@
         <v>44795</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -21714,7 +21714,7 @@
         <v>45772.35642361111</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -21771,7 +21771,7 @@
         <v>44489</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -21828,7 +21828,7 @@
         <v>44164</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -21890,7 +21890,7 @@
         <v>45793</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -21952,7 +21952,7 @@
         <v>45792.69864583333</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -22014,7 +22014,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -22071,7 +22071,7 @@
         <v>44386</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -22128,7 +22128,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -22190,7 +22190,7 @@
         <v>45205</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -22252,7 +22252,7 @@
         <v>45226</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -22314,7 +22314,7 @@
         <v>45590</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -22371,7 +22371,7 @@
         <v>45590</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -22428,7 +22428,7 @@
         <v>45281.57570601852</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -22490,7 +22490,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -22547,7 +22547,7 @@
         <v>45639</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -22604,7 +22604,7 @@
         <v>45583</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -22666,7 +22666,7 @@
         <v>45583.69863425926</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44903.92694444444</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>44529</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>44529</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45210</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -22961,7 +22961,7 @@
         <v>44833</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -23018,7 +23018,7 @@
         <v>44524</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -23075,7 +23075,7 @@
         <v>45797</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -23137,7 +23137,7 @@
         <v>45796.63600694444</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -23199,7 +23199,7 @@
         <v>44445</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -23256,7 +23256,7 @@
         <v>45212</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>44671</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45799.34436342592</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -23437,7 +23437,7 @@
         <v>45799.34511574074</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -23499,7 +23499,7 @@
         <v>44970</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>45232</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -23618,7 +23618,7 @@
         <v>44706</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -23675,7 +23675,7 @@
         <v>45798.44548611111</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -23737,7 +23737,7 @@
         <v>45285</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -23794,7 +23794,7 @@
         <v>44747</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -23851,7 +23851,7 @@
         <v>45798</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -23913,7 +23913,7 @@
         <v>44673</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -23970,7 +23970,7 @@
         <v>44910</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -24032,7 +24032,7 @@
         <v>45604.69282407407</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -24089,7 +24089,7 @@
         <v>44862.66424768518</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -24146,7 +24146,7 @@
         <v>45798.71922453704</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>44441.35422453703</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -24270,7 +24270,7 @@
         <v>44333</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -24327,7 +24327,7 @@
         <v>45624.4886574074</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -24384,7 +24384,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -24441,7 +24441,7 @@
         <v>44657</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44657</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>45803</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -24612,7 +24612,7 @@
         <v>45803.61491898148</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>45803.66424768518</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -24736,7 +24736,7 @@
         <v>45310.9390162037</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -24798,7 +24798,7 @@
         <v>45397</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -24855,7 +24855,7 @@
         <v>45397</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -24912,7 +24912,7 @@
         <v>44463.40267361111</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -24974,7 +24974,7 @@
         <v>45764</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -25031,7 +25031,7 @@
         <v>45804.34440972222</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -25093,7 +25093,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -25155,7 +25155,7 @@
         <v>45608</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -25212,7 +25212,7 @@
         <v>45608</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -25269,7 +25269,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -25326,7 +25326,7 @@
         <v>44983</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -25383,7 +25383,7 @@
         <v>45692.91950231481</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -25440,7 +25440,7 @@
         <v>44423</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -25497,7 +25497,7 @@
         <v>45411</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -25554,7 +25554,7 @@
         <v>45608</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -25611,7 +25611,7 @@
         <v>44966.95085648148</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -25673,7 +25673,7 @@
         <v>44110</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -25730,7 +25730,7 @@
         <v>45590</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -25787,7 +25787,7 @@
         <v>45804</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -25844,7 +25844,7 @@
         <v>45804.45221064815</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -25901,7 +25901,7 @@
         <v>45645</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -25963,7 +25963,7 @@
         <v>44474.65423611111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -26020,7 +26020,7 @@
         <v>45758</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -26077,7 +26077,7 @@
         <v>45674.63210648148</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -26134,7 +26134,7 @@
         <v>45691.56939814815</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -26191,7 +26191,7 @@
         <v>45764.46482638889</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -26248,7 +26248,7 @@
         <v>45429</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -26305,7 +26305,7 @@
         <v>45649.45567129629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -26362,7 +26362,7 @@
         <v>45464</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -26424,7 +26424,7 @@
         <v>45544.59535879629</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -26486,7 +26486,7 @@
         <v>45645.46262731482</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -26543,7 +26543,7 @@
         <v>45772.35878472222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -26600,7 +26600,7 @@
         <v>45772.3677662037</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -26657,7 +26657,7 @@
         <v>45301</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -26714,7 +26714,7 @@
         <v>45593</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45763.5946412037</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44833</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45546</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>44127</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45260</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45527.50440972222</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>44484</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -27185,7 +27185,7 @@
         <v>45544.57657407408</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -27242,7 +27242,7 @@
         <v>45264</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -27304,7 +27304,7 @@
         <v>45264</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -27366,7 +27366,7 @@
         <v>45243.48854166667</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -27423,7 +27423,7 @@
         <v>45518</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -27480,7 +27480,7 @@
         <v>45813.53178240741</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -27537,7 +27537,7 @@
         <v>45813.42753472222</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -27599,7 +27599,7 @@
         <v>45813</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -27661,7 +27661,7 @@
         <v>45813</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -27723,7 +27723,7 @@
         <v>45813.49092592593</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -27785,7 +27785,7 @@
         <v>45813.46928240741</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -27847,7 +27847,7 @@
         <v>45516</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>45516.94962962963</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -27971,7 +27971,7 @@
         <v>45429</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -28028,7 +28028,7 @@
         <v>45429</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>45085</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45813.42777777778</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -28204,7 +28204,7 @@
         <v>45316.44841435185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -28261,7 +28261,7 @@
         <v>44935</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -28318,7 +28318,7 @@
         <v>44529</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -28375,7 +28375,7 @@
         <v>44552</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -28432,7 +28432,7 @@
         <v>45589</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>45408.96730324074</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45481.95275462963</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -28613,7 +28613,7 @@
         <v>44900</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -28675,7 +28675,7 @@
         <v>45766.71910879629</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -28737,7 +28737,7 @@
         <v>45818.60010416667</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -28799,7 +28799,7 @@
         <v>45446</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -28856,7 +28856,7 @@
         <v>45427.93494212963</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -28913,7 +28913,7 @@
         <v>45543.34873842593</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -28970,7 +28970,7 @@
         <v>45544.4128125</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -29027,7 +29027,7 @@
         <v>45483</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -29084,7 +29084,7 @@
         <v>45818.34452546296</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45709.64082175926</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -29208,7 +29208,7 @@
         <v>45818.52607638889</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -29265,7 +29265,7 @@
         <v>45818</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -29327,7 +29327,7 @@
         <v>45574.51377314814</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -29389,7 +29389,7 @@
         <v>45818.56925925926</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -29451,7 +29451,7 @@
         <v>45153</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -29508,7 +29508,7 @@
         <v>45818</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -29570,7 +29570,7 @@
         <v>45818.43130787037</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -29652,7 +29652,7 @@
         <v>45714.69826388889</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -29714,7 +29714,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -29771,7 +29771,7 @@
         <v>45560.44918981481</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -29833,7 +29833,7 @@
         <v>45246</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -29890,7 +29890,7 @@
         <v>44880.59427083333</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -29947,7 +29947,7 @@
         <v>45414</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -30004,7 +30004,7 @@
         <v>45414.95038194444</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -30061,7 +30061,7 @@
         <v>45256</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -30118,7 +30118,7 @@
         <v>45762</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -30175,7 +30175,7 @@
         <v>45022.44041666666</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -30232,7 +30232,7 @@
         <v>45562</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -30294,7 +30294,7 @@
         <v>45653.46015046296</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -30351,7 +30351,7 @@
         <v>45653.51605324074</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -30408,7 +30408,7 @@
         <v>45448</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -30470,7 +30470,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -30532,7 +30532,7 @@
         <v>45194.40387731481</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -30594,7 +30594,7 @@
         <v>44788.65809027778</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -30651,7 +30651,7 @@
         <v>45586.44344907408</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -30708,7 +30708,7 @@
         <v>45247.58217592593</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -30765,7 +30765,7 @@
         <v>45483</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -30822,7 +30822,7 @@
         <v>45770.54408564815</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -30879,7 +30879,7 @@
         <v>44490</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -30941,7 +30941,7 @@
         <v>45244</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -31003,7 +31003,7 @@
         <v>45499.63932870371</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -31060,7 +31060,7 @@
         <v>44143</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -31117,7 +31117,7 @@
         <v>45748</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -31174,7 +31174,7 @@
         <v>45791.67759259259</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -31236,7 +31236,7 @@
         <v>45156</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -31293,7 +31293,7 @@
         <v>44755</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -31355,7 +31355,7 @@
         <v>45630.65877314815</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -31412,7 +31412,7 @@
         <v>45110</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -31474,7 +31474,7 @@
         <v>44642</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -31536,7 +31536,7 @@
         <v>45110</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -31598,7 +31598,7 @@
         <v>45070</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -31655,7 +31655,7 @@
         <v>44901</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -31712,7 +31712,7 @@
         <v>45103.92518518519</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -31769,7 +31769,7 @@
         <v>45646</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -31826,7 +31826,7 @@
         <v>45744.46895833333</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -31883,7 +31883,7 @@
         <v>45070.92538194444</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -31940,7 +31940,7 @@
         <v>44648</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -32002,7 +32002,7 @@
         <v>45195.94517361111</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -32064,7 +32064,7 @@
         <v>45232</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -32126,7 +32126,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -32183,7 +32183,7 @@
         <v>45300</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -32240,7 +32240,7 @@
         <v>45672</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -32297,7 +32297,7 @@
         <v>45764</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -32354,7 +32354,7 @@
         <v>45649.39115740741</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -32411,7 +32411,7 @@
         <v>45649.40401620371</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -32468,7 +32468,7 @@
         <v>45649.45635416666</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -32525,7 +32525,7 @@
         <v>45649</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -32582,7 +32582,7 @@
         <v>45625</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -32639,7 +32639,7 @@
         <v>45254</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -32696,7 +32696,7 @@
         <v>45646.62667824074</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -32753,7 +32753,7 @@
         <v>45646.62850694444</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -32810,7 +32810,7 @@
         <v>45589</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -32872,7 +32872,7 @@
         <v>45589.34494212963</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -32934,7 +32934,7 @@
         <v>45589</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -32996,7 +32996,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -33053,7 +33053,7 @@
         <v>45824</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -33110,7 +33110,7 @@
         <v>45476.69083333333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -33167,7 +33167,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -33229,7 +33229,7 @@
         <v>45460</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -33291,7 +33291,7 @@
         <v>45707.5637037037</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -33348,7 +33348,7 @@
         <v>45667.37363425926</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -33405,7 +33405,7 @@
         <v>45667.39547453704</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -33462,7 +33462,7 @@
         <v>45350</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -33519,7 +33519,7 @@
         <v>45824</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -33576,7 +33576,7 @@
         <v>44732.92724537037</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -33633,7 +33633,7 @@
         <v>45635.41770833333</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -33690,7 +33690,7 @@
         <v>45677.44833333333</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -33752,7 +33752,7 @@
         <v>44484.36106481482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -33809,7 +33809,7 @@
         <v>44628</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -33866,7 +33866,7 @@
         <v>44908</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -33923,7 +33923,7 @@
         <v>45161</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -33985,7 +33985,7 @@
         <v>45161</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -34047,7 +34047,7 @@
         <v>45718.80024305556</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -34104,7 +34104,7 @@
         <v>45646.64119212963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -34161,7 +34161,7 @@
         <v>45246</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -34218,7 +34218,7 @@
         <v>45216</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -34280,7 +34280,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -34337,7 +34337,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -34394,7 +34394,7 @@
         <v>44421.25067129629</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -34456,7 +34456,7 @@
         <v>44566</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -34513,7 +34513,7 @@
         <v>45356</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -34570,7 +34570,7 @@
         <v>44299</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -34627,7 +34627,7 @@
         <v>44841.66430555555</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -34689,7 +34689,7 @@
         <v>45358</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -34746,7 +34746,7 @@
         <v>45102.92748842593</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -34803,7 +34803,7 @@
         <v>45316</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -34860,7 +34860,7 @@
         <v>45356</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -34917,7 +34917,7 @@
         <v>45770</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -34974,7 +34974,7 @@
         <v>44529</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -35031,7 +35031,7 @@
         <v>45114</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -35088,7 +35088,7 @@
         <v>44648</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -35150,7 +35150,7 @@
         <v>45152</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -35207,7 +35207,7 @@
         <v>45824</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -35264,7 +35264,7 @@
         <v>45212</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -35321,7 +35321,7 @@
         <v>45323</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -35378,7 +35378,7 @@
         <v>44438</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -35435,7 +35435,7 @@
         <v>45827</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -35497,7 +35497,7 @@
         <v>45827</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -35559,7 +35559,7 @@
         <v>45476.58649305555</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -35616,7 +35616,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -35673,7 +35673,7 @@
         <v>45653.59047453704</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -35730,7 +35730,7 @@
         <v>45722.38607638889</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -35787,7 +35787,7 @@
         <v>44474</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44566</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>45551.34525462963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -35963,7 +35963,7 @@
         <v>45770.56699074074</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>45544.39978009259</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -36134,7 +36134,7 @@
         <v>44795</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -36191,7 +36191,7 @@
         <v>45560.44894675926</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -36253,7 +36253,7 @@
         <v>44477</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -36310,7 +36310,7 @@
         <v>45132</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -36367,7 +36367,7 @@
         <v>45161</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -36424,7 +36424,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -36481,7 +36481,7 @@
         <v>45826.46918981482</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -36543,7 +36543,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -36600,7 +36600,7 @@
         <v>45770</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -36657,7 +36657,7 @@
         <v>45827</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -36719,7 +36719,7 @@
         <v>45704</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -36776,7 +36776,7 @@
         <v>45826</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -36838,7 +36838,7 @@
         <v>45826.49025462963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -36900,7 +36900,7 @@
         <v>45831</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -36957,7 +36957,7 @@
         <v>45643.40710648148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -37014,7 +37014,7 @@
         <v>45831.60569444444</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -37076,7 +37076,7 @@
         <v>45831.54939814815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -37138,7 +37138,7 @@
         <v>45105.92532407407</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -37195,7 +37195,7 @@
         <v>45764.44585648148</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -37252,7 +37252,7 @@
         <v>45201.64971064815</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -37309,7 +37309,7 @@
         <v>45099</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -37366,7 +37366,7 @@
         <v>44994</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -37423,7 +37423,7 @@
         <v>44486.60745370371</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -37480,7 +37480,7 @@
         <v>45728.4180324074</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -37542,7 +37542,7 @@
         <v>45068</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -37599,7 +37599,7 @@
         <v>45546.34584490741</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>45453.28876157408</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>45194.40741898148</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -37780,7 +37780,7 @@
         <v>44908</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45831.5465625</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -37899,7 +37899,7 @@
         <v>45358.95780092593</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -37956,7 +37956,7 @@
         <v>45772</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -38013,7 +38013,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -38075,7 +38075,7 @@
         <v>45833.43721064815</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45832.68653935185</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>44151</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -38256,7 +38256,7 @@
         <v>44445</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -38313,7 +38313,7 @@
         <v>45680.4482175926</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -38375,7 +38375,7 @@
         <v>45680.48986111111</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -38437,7 +38437,7 @@
         <v>45833</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -38494,7 +38494,7 @@
         <v>45341</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -38556,7 +38556,7 @@
         <v>45832.6991087963</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -38613,7 +38613,7 @@
         <v>45832.69638888889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -38670,7 +38670,7 @@
         <v>45832.67101851852</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -38727,7 +38727,7 @@
         <v>45561.5891087963</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -38784,7 +38784,7 @@
         <v>45833.61671296296</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -38846,7 +38846,7 @@
         <v>45834.59451388889</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -38908,7 +38908,7 @@
         <v>45835.74189814815</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -38970,7 +38970,7 @@
         <v>45187</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45834.59415509259</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -39094,7 +39094,7 @@
         <v>45834.59708333333</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -39151,7 +39151,7 @@
         <v>45835.44276620371</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -39213,7 +39213,7 @@
         <v>45257.80766203703</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -39270,7 +39270,7 @@
         <v>44887</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -39332,7 +39332,7 @@
         <v>45166.83878472223</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -39394,7 +39394,7 @@
         <v>45446.68098379629</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -39456,7 +39456,7 @@
         <v>45803</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -39513,7 +39513,7 @@
         <v>44522.9206712963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -39570,7 +39570,7 @@
         <v>45211.44008101852</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -39632,7 +39632,7 @@
         <v>45653</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -39689,7 +39689,7 @@
         <v>45596</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -39746,7 +39746,7 @@
         <v>45174.4406712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -39803,7 +39803,7 @@
         <v>45351</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -39860,7 +39860,7 @@
         <v>45839.46466435185</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -39917,7 +39917,7 @@
         <v>45841.5124537037</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -39974,7 +39974,7 @@
         <v>45841.69828703703</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -40031,7 +40031,7 @@
         <v>45840</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -40088,7 +40088,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -40145,7 +40145,7 @@
         <v>45840.50157407407</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -40207,7 +40207,7 @@
         <v>45841.5196875</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -40264,7 +40264,7 @@
         <v>45323</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -40321,7 +40321,7 @@
         <v>45769.49768518518</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -40378,7 +40378,7 @@
         <v>45840</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -40440,7 +40440,7 @@
         <v>44931</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -40497,7 +40497,7 @@
         <v>45840.39109953704</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -40554,7 +40554,7 @@
         <v>45840.39805555555</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -40611,7 +40611,7 @@
         <v>45645</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -40673,7 +40673,7 @@
         <v>45840.37375</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -40730,7 +40730,7 @@
         <v>45840.37756944444</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -40787,7 +40787,7 @@
         <v>45747.57071759259</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -40844,7 +40844,7 @@
         <v>45840</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -40906,7 +40906,7 @@
         <v>45685</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -40963,7 +40963,7 @@
         <v>45843.34435185185</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -41025,7 +41025,7 @@
         <v>45001</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -41082,7 +41082,7 @@
         <v>44378</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -41139,7 +41139,7 @@
         <v>45732</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -41196,7 +41196,7 @@
         <v>45772.35200231482</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -41253,7 +41253,7 @@
         <v>45772.37400462963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -41310,7 +41310,7 @@
         <v>44110</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -41372,7 +41372,7 @@
         <v>45770.56481481482</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -41429,7 +41429,7 @@
         <v>44994</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -41486,7 +41486,7 @@
         <v>45708.36651620371</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -41548,7 +41548,7 @@
         <v>45685</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -41605,7 +41605,7 @@
         <v>45646.61649305555</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -41662,7 +41662,7 @@
         <v>45884.46990740741</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -41724,7 +41724,7 @@
         <v>45884.46996527778</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -41848,7 +41848,7 @@
         <v>44110</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -41905,7 +41905,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>44889</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45887</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -42081,7 +42081,7 @@
         <v>45406</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -42138,7 +42138,7 @@
         <v>44735</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -42200,7 +42200,7 @@
         <v>45771.68158564815</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -42257,7 +42257,7 @@
         <v>45105</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -42319,7 +42319,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -42376,7 +42376,7 @@
         <v>44881.55375</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -42438,7 +42438,7 @@
         <v>45035</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -42495,7 +42495,7 @@
         <v>44356</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -42552,7 +42552,7 @@
         <v>45476.58195601852</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -42609,7 +42609,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -42671,7 +42671,7 @@
         <v>45152</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -42728,7 +42728,7 @@
         <v>44883</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -42790,7 +42790,7 @@
         <v>45686.42653935185</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -42847,7 +42847,7 @@
         <v>45747.56618055556</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -42904,7 +42904,7 @@
         <v>45771</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -42961,7 +42961,7 @@
         <v>45587</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -43018,7 +43018,7 @@
         <v>45893.46916666667</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -43080,7 +43080,7 @@
         <v>45529.93233796296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -43137,7 +43137,7 @@
         <v>45248.94667824074</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -43194,7 +43194,7 @@
         <v>45099</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -43251,7 +43251,7 @@
         <v>44484</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -43308,7 +43308,7 @@
         <v>45603.75905092592</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -43365,7 +43365,7 @@
         <v>45561</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -43422,7 +43422,7 @@
         <v>44573</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -43484,7 +43484,7 @@
         <v>45649.45255787037</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -43541,7 +43541,7 @@
         <v>45691.49005787037</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -43603,7 +43603,7 @@
         <v>44648</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -43665,7 +43665,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -43722,7 +43722,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -43784,7 +43784,7 @@
         <v>44565</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -43841,7 +43841,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -43903,7 +43903,7 @@
         <v>45454</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -43960,7 +43960,7 @@
         <v>44614.40652777778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -44017,7 +44017,7 @@
         <v>44216</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -44074,7 +44074,7 @@
         <v>45642</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -44131,7 +44131,7 @@
         <v>45079</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -44188,7 +44188,7 @@
         <v>45901.37751157407</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -44250,7 +44250,7 @@
         <v>45265.27829861111</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -44312,7 +44312,7 @@
         <v>45649.38344907408</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -44369,7 +44369,7 @@
         <v>45895</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -44431,7 +44431,7 @@
         <v>45646.65767361111</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -44488,7 +44488,7 @@
         <v>45762</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -44545,7 +44545,7 @@
         <v>45574.46930555555</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -44607,7 +44607,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -44669,7 +44669,7 @@
         <v>45674</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -44726,7 +44726,7 @@
         <v>45902.32747685185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -44788,7 +44788,7 @@
         <v>45646</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -44845,7 +44845,7 @@
         <v>45901</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -44902,7 +44902,7 @@
         <v>45205.37278935185</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -44959,7 +44959,7 @@
         <v>44124</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -45016,7 +45016,7 @@
         <v>45301</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -45078,7 +45078,7 @@
         <v>45894</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -45140,7 +45140,7 @@
         <v>45761</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -45197,7 +45197,7 @@
         <v>45233.95826388889</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -45259,7 +45259,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45903</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -45383,7 +45383,7 @@
         <v>45774</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -45445,7 +45445,7 @@
         <v>45750</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -45507,7 +45507,7 @@
         <v>44292</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -45564,7 +45564,7 @@
         <v>45769</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -45621,7 +45621,7 @@
         <v>45646.66561342592</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -45678,7 +45678,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -45735,7 +45735,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -45797,7 +45797,7 @@
         <v>45902.40394675926</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -45859,7 +45859,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -45916,7 +45916,7 @@
         <v>45761</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -45978,7 +45978,7 @@
         <v>45863.56016203704</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -46040,7 +46040,7 @@
         <v>44378</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -46097,7 +46097,7 @@
         <v>45863.6125</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -46159,7 +46159,7 @@
         <v>45863.67741898148</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -46216,7 +46216,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -46278,7 +46278,7 @@
         <v>45379</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -46335,7 +46335,7 @@
         <v>45264.48927083334</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -46392,7 +46392,7 @@
         <v>45906.71729166667</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -46449,7 +46449,7 @@
         <v>45614.81146990741</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -46506,7 +46506,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -46563,7 +46563,7 @@
         <v>45906.68483796297</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -46620,7 +46620,7 @@
         <v>45907.34451388889</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -46682,7 +46682,7 @@
         <v>44994</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -46739,7 +46739,7 @@
         <v>45639</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -46796,7 +46796,7 @@
         <v>45891</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -46858,7 +46858,7 @@
         <v>45910.63275462963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -46920,7 +46920,7 @@
         <v>45890</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -46982,7 +46982,7 @@
         <v>44903</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -47039,7 +47039,7 @@
         <v>44568</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -47096,7 +47096,7 @@
         <v>45770</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -47153,7 +47153,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -47215,7 +47215,7 @@
         <v>45764</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -47272,7 +47272,7 @@
         <v>45764</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -47329,7 +47329,7 @@
         <v>45618.43688657408</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -47391,7 +47391,7 @@
         <v>45672</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -47448,7 +47448,7 @@
         <v>45099.9296412037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -47505,7 +47505,7 @@
         <v>44127</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -47567,7 +47567,7 @@
         <v>45752</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -47624,7 +47624,7 @@
         <v>45590.64114583333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -47686,7 +47686,7 @@
         <v>45591</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -47748,7 +47748,7 @@
         <v>45591</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -47810,7 +47810,7 @@
         <v>45911.3857175926</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -47867,7 +47867,7 @@
         <v>45586</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -47929,7 +47929,7 @@
         <v>45425</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -47986,7 +47986,7 @@
         <v>45912.63472222222</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -48048,7 +48048,7 @@
         <v>45894</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -48105,7 +48105,7 @@
         <v>45915.38821759259</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -48162,7 +48162,7 @@
         <v>45915.4071412037</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -48224,7 +48224,7 @@
         <v>45456</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -48281,7 +48281,7 @@
         <v>44812</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -48338,7 +48338,7 @@
         <v>45870</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -48400,7 +48400,7 @@
         <v>45912.40694444445</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -48457,7 +48457,7 @@
         <v>44823</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -48519,7 +48519,7 @@
         <v>44657</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -48576,7 +48576,7 @@
         <v>45369.48284722222</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -48633,7 +48633,7 @@
         <v>45834</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -48690,7 +48690,7 @@
         <v>45915.40732638889</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -48752,7 +48752,7 @@
         <v>45646.57136574074</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -48809,7 +48809,7 @@
         <v>45915.69679398148</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -48871,7 +48871,7 @@
         <v>45870</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -48933,7 +48933,7 @@
         <v>45625</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -48995,7 +48995,7 @@
         <v>45653.3677662037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -49052,7 +49052,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -49109,7 +49109,7 @@
         <v>45723</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -49166,7 +49166,7 @@
         <v>45723</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -49223,7 +49223,7 @@
         <v>45838.5983912037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -49280,7 +49280,7 @@
         <v>45912.40695601852</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -49337,7 +49337,7 @@
         <v>44856.89673611111</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -49394,7 +49394,7 @@
         <v>45152</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -49451,7 +49451,7 @@
         <v>44847</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -49508,7 +49508,7 @@
         <v>45013</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -49565,7 +49565,7 @@
         <v>45210.53141203704</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -49627,7 +49627,7 @@
         <v>44585</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -49684,7 +49684,7 @@
         <v>45874.42918981481</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -49746,7 +49746,7 @@
         <v>45896</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -49808,7 +49808,7 @@
         <v>45875.45590277778</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -49870,7 +49870,7 @@
         <v>45897.48153935185</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -49927,7 +49927,7 @@
         <v>45875</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -49984,7 +49984,7 @@
         <v>45901.65690972222</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -50046,7 +50046,7 @@
         <v>45874</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -50123,7 +50123,7 @@
         <v>45868</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -50185,7 +50185,7 @@
         <v>45893</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -50247,7 +50247,7 @@
         <v>44573</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -50309,7 +50309,7 @@
         <v>45618.43729166667</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -50371,7 +50371,7 @@
         <v>45635.41246527778</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -50428,7 +50428,7 @@
         <v>44859.95792824074</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -50490,7 +50490,7 @@
         <v>45356.96387731482</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -50547,7 +50547,7 @@
         <v>44925</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -50604,7 +50604,7 @@
         <v>45749</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -50661,7 +50661,7 @@
         <v>45874</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -50723,7 +50723,7 @@
         <v>45895.44861111111</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -50780,7 +50780,7 @@
         <v>45544.58453703704</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -50837,7 +50837,7 @@
         <v>45910</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -50899,7 +50899,7 @@
         <v>45314</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -50956,7 +50956,7 @@
         <v>45429.92297453704</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -51013,7 +51013,7 @@
         <v>45204</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -51070,7 +51070,7 @@
         <v>45901.65390046296</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -51132,7 +51132,7 @@
         <v>45687</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -51189,7 +51189,7 @@
         <v>45902</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -51251,7 +51251,7 @@
         <v>45894</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -51313,7 +51313,7 @@
         <v>45901.41519675926</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -51375,7 +51375,7 @@
         <v>45897</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -51432,7 +51432,7 @@
         <v>45906</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -51489,7 +51489,7 @@
         <v>45902</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -51551,7 +51551,7 @@
         <v>45901.64849537037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -51613,7 +51613,7 @@
         <v>45667.37811342593</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -51670,7 +51670,7 @@
         <v>45901.62032407407</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -51732,7 +51732,7 @@
         <v>45877.44846064815</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -51794,7 +51794,7 @@
         <v>45917</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -51876,7 +51876,7 @@
         <v>45919.56777777777</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -51938,7 +51938,7 @@
         <v>45894</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -52000,7 +52000,7 @@
         <v>45905.42783564814</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -52062,7 +52062,7 @@
         <v>44120</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -52119,7 +52119,7 @@
         <v>44120</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -52176,7 +52176,7 @@
         <v>45764</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -52233,7 +52233,7 @@
         <v>45919.57042824074</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -52295,7 +52295,7 @@
         <v>45910</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -52357,7 +52357,7 @@
         <v>44391</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -52414,7 +52414,7 @@
         <v>45922.59516203704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -52496,7 +52496,7 @@
         <v>45922.59851851852</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -52558,7 +52558,7 @@
         <v>45915</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -52615,7 +52615,7 @@
         <v>45922</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -52677,7 +52677,7 @@
         <v>45880.49046296296</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -52739,7 +52739,7 @@
         <v>45922</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -52796,7 +52796,7 @@
         <v>45923.39789351852</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -52858,7 +52858,7 @@
         <v>45884</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -52920,7 +52920,7 @@
         <v>45922</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -52977,7 +52977,7 @@
         <v>45922.62408564815</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -53034,7 +53034,7 @@
         <v>45912</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -53096,7 +53096,7 @@
         <v>45922.39398148148</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -53153,7 +53153,7 @@
         <v>45887</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -53215,7 +53215,7 @@
         <v>45881.45475694445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -53272,7 +53272,7 @@
         <v>45882</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -53329,7 +53329,7 @@
         <v>45924</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -53386,7 +53386,7 @@
         <v>45924</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -53443,7 +53443,7 @@
         <v>45894</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -53500,7 +53500,7 @@
         <v>45882</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -53557,7 +53557,7 @@
         <v>45882</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -53614,7 +53614,7 @@
         <v>45925.65686342592</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -53671,7 +53671,7 @@
         <v>45925.65679398148</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>

--- a/Översikt BODEN.xlsx
+++ b/Översikt BODEN.xlsx
@@ -567,7 +567,7 @@
         <v>45586</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
         <v>45763</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,7 +812,7 @@
         <v>45506</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -926,7 +926,7 @@
         <v>45607.52168981481</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1040,7 +1040,7 @@
         <v>45709.34450231482</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>44853</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,7 +1247,7 @@
         <v>44169</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1345,7 +1345,7 @@
         <v>44964</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1448,7 +1448,7 @@
         <v>45790.67758101852</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1550,7 +1550,7 @@
         <v>45237</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1647,7 +1647,7 @@
         <v>44859</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1748,7 +1748,7 @@
         <v>44889</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1845,7 +1845,7 @@
         <v>45589.34458333333</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1946,7 +1946,7 @@
         <v>45212</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45819</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44124</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2240,7 +2240,7 @@
         <v>45295</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2335,7 +2335,7 @@
         <v>44151</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2430,7 +2430,7 @@
         <v>45622</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2525,7 +2525,7 @@
         <v>45645</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2620,7 +2620,7 @@
         <v>45771</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2719,7 +2719,7 @@
         <v>44795</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44433.55907407407</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2915,7 +2915,7 @@
         <v>45912.40692129629</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3008,7 +3008,7 @@
         <v>45512</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>45049</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
         <v>45819</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>45832.53813657408</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3387,7 +3387,7 @@
         <v>44869</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>45698.34423611111</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44158</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3670,7 +3670,7 @@
         <v>44158</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3758,7 +3758,7 @@
         <v>45307</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3851,7 +3851,7 @@
         <v>44904</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3942,7 +3942,7 @@
         <v>45917.61134259259</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4034,7 +4034,7 @@
         <v>45893</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4130,7 +4130,7 @@
         <v>45834</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45428</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>45820.34439814815</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4408,7 +4408,7 @@
         <v>45684.44825231482</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4500,7 +4500,7 @@
         <v>44463.40674768519</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4596,7 +4596,7 @@
         <v>44130</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4688,7 +4688,7 @@
         <v>44487.66532407407</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>44322</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4865,7 +4865,7 @@
         <v>44166</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
         <v>44735.63122685185</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5042,7 +5042,7 @@
         <v>44489</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5128,7 +5128,7 @@
         <v>44165</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5219,7 +5219,7 @@
         <v>44804</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5310,7 +5310,7 @@
         <v>45701</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5396,7 +5396,7 @@
         <v>45526</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5487,7 +5487,7 @@
         <v>45910.65401620371</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>45922.52559027778</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>45137</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5764,7 +5764,7 @@
         <v>44830</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5854,7 +5854,7 @@
         <v>45559</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5945,7 +5945,7 @@
         <v>45072</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>45341</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6131,7 +6131,7 @@
         <v>45791.34502314815</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6222,7 +6222,7 @@
         <v>44678</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6313,7 +6313,7 @@
         <v>45155</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6408,7 +6408,7 @@
         <v>45301</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6498,7 +6498,7 @@
         <v>45842</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6589,7 +6589,7 @@
         <v>45818.56559027778</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6684,7 +6684,7 @@
         <v>45820.60171296296</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6779,7 +6779,7 @@
         <v>45714</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6870,7 +6870,7 @@
         <v>45638.43048611111</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6956,7 +6956,7 @@
         <v>45833.43407407407</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7047,7 +7047,7 @@
         <v>45834.41993055555</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7142,7 +7142,7 @@
         <v>45517</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7233,7 +7233,7 @@
         <v>44648</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7323,7 +7323,7 @@
         <v>44853</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7417,7 +7417,7 @@
         <v>44446.60008101852</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7506,7 +7506,7 @@
         <v>44365</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7596,7 +7596,7 @@
         <v>45763.60056712963</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44840</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
         <v>44421</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7861,7 +7861,7 @@
         <v>44796</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7950,7 +7950,7 @@
         <v>45832.58524305555</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8040,7 +8040,7 @@
         <v>45901.40067129629</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>45863.57627314814</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8220,7 +8220,7 @@
         <v>45313.6253125</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8305,7 +8305,7 @@
         <v>45205</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8399,7 +8399,7 @@
         <v>45538</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>45513</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
         <v>45773</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8664,7 +8664,7 @@
         <v>45586</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>45406.96350694444</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8843,7 +8843,7 @@
         <v>45803.66833333333</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8933,7 +8933,7 @@
         <v>45803.67</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -9023,7 +9023,7 @@
         <v>45611</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -9113,7 +9113,7 @@
         <v>45645</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9203,7 +9203,7 @@
         <v>45833.57443287037</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9293,7 +9293,7 @@
         <v>45835.49065972222</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9383,7 +9383,7 @@
         <v>45848.4612037037</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9477,7 +9477,7 @@
         <v>45891.3190625</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>45594</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44692</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9742,7 +9742,7 @@
         <v>44217</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9799,7 +9799,7 @@
         <v>44207</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
         <v>44158</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9913,7 +9913,7 @@
         <v>44279.30587962963</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9970,7 +9970,7 @@
         <v>44158</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -10027,7 +10027,7 @@
         <v>44509</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>44677</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10141,7 +10141,7 @@
         <v>44215</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10198,7 +10198,7 @@
         <v>44274</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10255,7 +10255,7 @@
         <v>44577</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10312,7 +10312,7 @@
         <v>44414</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10369,7 +10369,7 @@
         <v>44414</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10426,7 +10426,7 @@
         <v>44350</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10483,7 +10483,7 @@
         <v>44217</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10540,7 +10540,7 @@
         <v>44354.25563657407</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10602,7 +10602,7 @@
         <v>44671</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10659,7 +10659,7 @@
         <v>44659.6078587963</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -10716,7 +10716,7 @@
         <v>44489.94650462963</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -10778,7 +10778,7 @@
         <v>44120</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -10835,7 +10835,7 @@
         <v>44852</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -10897,7 +10897,7 @@
         <v>44216</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -10954,7 +10954,7 @@
         <v>44313</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11011,7 +11011,7 @@
         <v>44350</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11068,7 +11068,7 @@
         <v>44463.27165509259</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11130,7 +11130,7 @@
         <v>44414</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11187,7 +11187,7 @@
         <v>44414</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11244,7 +11244,7 @@
         <v>44809</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11306,7 +11306,7 @@
         <v>44414</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11363,7 +11363,7 @@
         <v>44414</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -11420,7 +11420,7 @@
         <v>44815</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -11482,7 +11482,7 @@
         <v>44648</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>44138</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -11606,7 +11606,7 @@
         <v>44130</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -11663,7 +11663,7 @@
         <v>44462.92758101852</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -11720,7 +11720,7 @@
         <v>44165</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -11777,7 +11777,7 @@
         <v>44187</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -11834,7 +11834,7 @@
         <v>44168</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -11891,7 +11891,7 @@
         <v>44274</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -11948,7 +11948,7 @@
         <v>44286</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12005,7 +12005,7 @@
         <v>44617</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -12062,7 +12062,7 @@
         <v>44274</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -12119,7 +12119,7 @@
         <v>44648</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -12181,7 +12181,7 @@
         <v>44439</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -12238,7 +12238,7 @@
         <v>44284</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -12300,7 +12300,7 @@
         <v>44464</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -12357,7 +12357,7 @@
         <v>44865</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -12419,7 +12419,7 @@
         <v>44204</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -12476,7 +12476,7 @@
         <v>44609</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -12533,7 +12533,7 @@
         <v>44609</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -12590,7 +12590,7 @@
         <v>44223</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -12647,7 +12647,7 @@
         <v>44110</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -12709,7 +12709,7 @@
         <v>44158</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -12766,7 +12766,7 @@
         <v>44389.38752314815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -12823,7 +12823,7 @@
         <v>44671</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -12880,7 +12880,7 @@
         <v>44182</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -12937,7 +12937,7 @@
         <v>44461.62384259259</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -12994,7 +12994,7 @@
         <v>44125</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -13056,7 +13056,7 @@
         <v>44887.95318287037</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>44721</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -13175,7 +13175,7 @@
         <v>44543.62024305556</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -13232,7 +13232,7 @@
         <v>44378</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -13289,7 +13289,7 @@
         <v>44174</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -13351,7 +13351,7 @@
         <v>44238</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -13408,7 +13408,7 @@
         <v>44313</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -13465,7 +13465,7 @@
         <v>44873.32177083333</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -13527,7 +13527,7 @@
         <v>44371.60706018518</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -13589,7 +13589,7 @@
         <v>44438</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -13646,7 +13646,7 @@
         <v>44182</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -13703,7 +13703,7 @@
         <v>44217</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -13760,7 +13760,7 @@
         <v>44530.47554398148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -13817,7 +13817,7 @@
         <v>44480</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -13874,7 +13874,7 @@
         <v>44530</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -13931,7 +13931,7 @@
         <v>44480</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -13988,7 +13988,7 @@
         <v>44182</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -14045,7 +14045,7 @@
         <v>44414</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -14102,7 +14102,7 @@
         <v>44565</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -14159,7 +14159,7 @@
         <v>44573.46630787037</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -14221,7 +14221,7 @@
         <v>44648</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -14283,7 +14283,7 @@
         <v>44529</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -14340,7 +14340,7 @@
         <v>44566</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -14397,7 +14397,7 @@
         <v>44293</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -14459,7 +14459,7 @@
         <v>44473</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -14521,7 +14521,7 @@
         <v>44356</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -14578,7 +14578,7 @@
         <v>44182</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -14635,7 +14635,7 @@
         <v>44795</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -14697,7 +14697,7 @@
         <v>44489</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -14754,7 +14754,7 @@
         <v>44617</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -14811,7 +14811,7 @@
         <v>44820.29530092593</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -14873,7 +14873,7 @@
         <v>44625.78322916666</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -14930,7 +14930,7 @@
         <v>44596</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -14992,7 +14992,7 @@
         <v>44565</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -15049,7 +15049,7 @@
         <v>44439</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -15106,7 +15106,7 @@
         <v>44648</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -15168,7 +15168,7 @@
         <v>44812.44233796297</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -15225,7 +15225,7 @@
         <v>44734</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -15282,7 +15282,7 @@
         <v>44671</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -15339,7 +15339,7 @@
         <v>44356</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -15396,7 +15396,7 @@
         <v>44635</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -15458,7 +15458,7 @@
         <v>44248</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -15515,7 +15515,7 @@
         <v>45771</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -15572,7 +15572,7 @@
         <v>44116</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -15629,7 +15629,7 @@
         <v>45715.34438657408</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -15691,7 +15691,7 @@
         <v>44428.58703703704</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -15748,7 +15748,7 @@
         <v>44831.94553240741</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -15810,7 +15810,7 @@
         <v>44566</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -15867,7 +15867,7 @@
         <v>44566</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -15924,7 +15924,7 @@
         <v>44600.31258101852</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -15986,7 +15986,7 @@
         <v>44299</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -16043,7 +16043,7 @@
         <v>44417.69528935185</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -16100,7 +16100,7 @@
         <v>45572.48857638889</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -16162,7 +16162,7 @@
         <v>44734.56864583334</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -16219,7 +16219,7 @@
         <v>45105</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -16281,7 +16281,7 @@
         <v>44797.36959490741</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -16338,7 +16338,7 @@
         <v>45068</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -16395,7 +16395,7 @@
         <v>44833</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -16452,7 +16452,7 @@
         <v>44274</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -16509,7 +16509,7 @@
         <v>44796</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -16566,7 +16566,7 @@
         <v>44796</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -16623,7 +16623,7 @@
         <v>45770.63237268518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -16680,7 +16680,7 @@
         <v>45232.44363425926</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -16742,7 +16742,7 @@
         <v>45358</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -16799,7 +16799,7 @@
         <v>45356</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -16856,7 +16856,7 @@
         <v>44484</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -16918,7 +16918,7 @@
         <v>45089.37991898148</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -16980,7 +16980,7 @@
         <v>45763.6009375</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -17037,7 +17037,7 @@
         <v>44313</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -17094,7 +17094,7 @@
         <v>44301.66649305556</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -17151,7 +17151,7 @@
         <v>44279.38570601852</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -17208,7 +17208,7 @@
         <v>44211</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -17265,7 +17265,7 @@
         <v>44799.94413194444</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -17327,7 +17327,7 @@
         <v>44799.94417824074</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -17389,7 +17389,7 @@
         <v>44313</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -17446,7 +17446,7 @@
         <v>44313</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -17503,7 +17503,7 @@
         <v>45702.63587962963</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -17565,7 +17565,7 @@
         <v>44445</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -17622,7 +17622,7 @@
         <v>44358</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -17679,7 +17679,7 @@
         <v>44749</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -17736,7 +17736,7 @@
         <v>44743.43572916667</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -17793,7 +17793,7 @@
         <v>44722</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -17850,7 +17850,7 @@
         <v>44935.46053240741</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -17907,7 +17907,7 @@
         <v>45419.6787962963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -17964,7 +17964,7 @@
         <v>45301</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -18026,7 +18026,7 @@
         <v>44970</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -18083,7 +18083,7 @@
         <v>45254</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -18140,7 +18140,7 @@
         <v>45463.58862268519</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -18197,7 +18197,7 @@
         <v>45891.37986111111</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -18254,7 +18254,7 @@
         <v>45093.68881944445</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -18316,7 +18316,7 @@
         <v>45587.49114583333</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -18373,7 +18373,7 @@
         <v>45583.69834490741</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -18435,7 +18435,7 @@
         <v>45210.46891203704</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -18497,7 +18497,7 @@
         <v>45408.96738425926</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -18554,7 +18554,7 @@
         <v>45574.5735300926</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -18616,7 +18616,7 @@
         <v>45692.92622685185</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -18673,7 +18673,7 @@
         <v>45649.38905092593</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -18730,7 +18730,7 @@
         <v>45370</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -18787,7 +18787,7 @@
         <v>45649.4091550926</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -18844,7 +18844,7 @@
         <v>45509.43402777778</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>45582</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -18958,7 +18958,7 @@
         <v>45630.69038194444</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -19015,7 +19015,7 @@
         <v>45856.53160879629</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -19077,7 +19077,7 @@
         <v>45707.53890046296</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -19134,7 +19134,7 @@
         <v>45427.93548611111</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -19191,7 +19191,7 @@
         <v>45897.48924768518</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -19253,7 +19253,7 @@
         <v>45440.84460648148</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -19310,7 +19310,7 @@
         <v>45429</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -19367,7 +19367,7 @@
         <v>45589</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -19429,7 +19429,7 @@
         <v>45646.61572916667</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -19486,7 +19486,7 @@
         <v>44477</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -19543,7 +19543,7 @@
         <v>45537.27357638889</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -19605,7 +19605,7 @@
         <v>44726.48164351852</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -19662,7 +19662,7 @@
         <v>44356</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -19719,7 +19719,7 @@
         <v>45897.33677083333</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -19776,7 +19776,7 @@
         <v>44964.94416666667</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -19838,7 +19838,7 @@
         <v>45512.36836805556</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -19895,7 +19895,7 @@
         <v>45902.32747685185</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -19957,7 +19957,7 @@
         <v>45901</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -20014,7 +20014,7 @@
         <v>45894</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -20076,7 +20076,7 @@
         <v>44558</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -20133,7 +20133,7 @@
         <v>44642</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -20195,7 +20195,7 @@
         <v>45548.41165509259</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -20252,7 +20252,7 @@
         <v>45860.67740740741</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -20314,7 +20314,7 @@
         <v>45901.37751157407</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44490</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45054</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>45539.52540509259</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45902.40394675926</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
         <v>45895</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>45448</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -20738,7 +20738,7 @@
         <v>44963</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -20795,7 +20795,7 @@
         <v>44143</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -20852,7 +20852,7 @@
         <v>45238.9265625</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -20909,7 +20909,7 @@
         <v>45860.59417824074</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -20971,7 +20971,7 @@
         <v>44333</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -21028,7 +21028,7 @@
         <v>45674</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -21085,7 +21085,7 @@
         <v>45596.7612962963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -21142,7 +21142,7 @@
         <v>44292</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -21199,7 +21199,7 @@
         <v>44124</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -21256,7 +21256,7 @@
         <v>45774</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -21318,7 +21318,7 @@
         <v>44883</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45928</v>
+        <v>45929</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -21380,7 +21380,7 @@
         <v>45796.51097222222</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45928</v>
+        <v